--- a/DFS_Card_Grader_Kit.xlsx
+++ b/DFS_Card_Grader_Kit.xlsx
@@ -17,19 +17,16 @@
     <sheet name="DcSports87 May 2026" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="DcSports87 — Normal Batch" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="Inventory &amp; Aging" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="FB Cards — HeyStack Priority" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="BB Cards — HeyStack Priority" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="BK Cards — HeyStack Priority" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Lot Evaluator" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Channel Fees" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="Capital Velocity" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="Helper ROI" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="Path to $40k" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="Stale Action — Market Comps" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="PSA Fee Schedule" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="Grading ROI Calculator" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="Grading Tracker" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="Grading Candidates" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="Lot Evaluator" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Channel Fees" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Capital Velocity" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Helper ROI" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Path to $40k" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Stale Action — Market Comps" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="PSA Fee Schedule" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Grading ROI Calculator" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Grading Tracker" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Grading Candidates" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -2877,12 +2874,6 @@
           <t xml:space="preserve">  ▸  What margin are you targeting?</t>
         </is>
       </c>
-      <c r="C12" s="410" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Most resellers target 30–50% net margin after fees and shipping. The Channel Fees tab shows you exactly what each platform costs per sale so you can price accordingly.</t>
-        </is>
-      </c>
-      <c r="D12" s="412" t="inlineStr"/>
     </row>
     <row r="13" ht="20" customHeight="1" s="230">
       <c r="B13" s="411" t="inlineStr">
@@ -2937,12 +2928,6 @@
           <t xml:space="preserve">  ▸  Know what's costing you money</t>
         </is>
       </c>
-      <c r="C18" s="410" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Stale inventory is tied-up capital. Every dollar sitting in an unsold card is a dollar not flipping into profit. The Capital Velocity tab quantifies exactly how much this costs you.</t>
-        </is>
-      </c>
-      <c r="D18" s="412" t="inlineStr"/>
     </row>
     <row r="19" ht="20" customHeight="1" s="230">
       <c r="B19" s="411" t="inlineStr">
@@ -3010,12 +2995,6 @@
           <t xml:space="preserve">  ▸  Build a grading pipeline</t>
         </is>
       </c>
-      <c r="C25" s="410" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  The best resellers submit cards in batches to save on shipping and reduce per-card costs. Use the Grading Candidates tab to build your next batch before committing.</t>
-        </is>
-      </c>
-      <c r="D25" s="412" t="inlineStr"/>
     </row>
     <row r="26" ht="10" customHeight="1" s="230"/>
     <row r="27" ht="22" customHeight="1" s="230">
@@ -3070,12 +3049,6 @@
           <t xml:space="preserve">  ▸  HeyStack priority scoring</t>
         </is>
       </c>
-      <c r="C31" s="410" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Use the FB/BB/BK HeyStack Priority tabs to rank your cards by sell-through potential. Score is based on days listed, watchers, player tier, and recent market sales. High score = relist or reprice first.</t>
-        </is>
-      </c>
-      <c r="D31" s="412" t="inlineStr"/>
     </row>
     <row r="32" ht="10" customHeight="1" s="230"/>
     <row r="33" ht="22" customHeight="1" s="230">
@@ -3115,11 +3088,6 @@
           <t xml:space="preserve">  ☐</t>
         </is>
       </c>
-      <c r="C36" s="410" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Add your current inventory to the Inventory &amp; Aging tab</t>
-        </is>
-      </c>
     </row>
     <row r="37" ht="20" customHeight="1" s="230">
       <c r="B37" s="413" t="inlineStr">
@@ -3197,11 +3165,6 @@
       <c r="B43" s="413" t="inlineStr">
         <is>
           <t xml:space="preserve">  ☐</t>
-        </is>
-      </c>
-      <c r="C43" s="410" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Review your actual vs. expected ROI in Grading Tracker after each batch</t>
         </is>
       </c>
     </row>
@@ -15682,5664 +15645,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M133"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" style="230" min="1" max="1"/>
-    <col width="36" customWidth="1" style="230" min="2" max="2"/>
-    <col width="16" customWidth="1" style="230" min="3" max="3"/>
-    <col width="10" customWidth="1" style="230" min="4" max="4"/>
-    <col width="9" customWidth="1" style="230" min="5" max="5"/>
-    <col width="28" customWidth="1" style="230" min="6" max="6"/>
-    <col width="7" customWidth="1" style="230" min="7" max="7"/>
-    <col width="9" customWidth="1" style="230" min="8" max="8"/>
-    <col width="10" customWidth="1" style="230" min="9" max="9"/>
-    <col width="9" customWidth="1" style="230" min="10" max="10"/>
-    <col width="14" customWidth="1" style="230" min="11" max="11"/>
-    <col width="22" customWidth="1" style="230" min="12" max="12"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1" s="230">
-      <c r="A1" s="229" t="inlineStr">
-        <is>
-          <t>🏠 Start Here</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="283" t="inlineStr">
-        <is>
-          <t>Scored by player tier + auto/patch/print run/PSA/price/watchers | Today: May 03, 2026 | 233 total Football cards in inventory</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="169" t="inlineStr">
-        <is>
-          <t>PRIORITY ACTIONS</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1" s="230">
-      <c r="A4" s="133" t="inlineStr">
-        <is>
-          <t>Rank</t>
-        </is>
-      </c>
-      <c r="B4" s="133" t="inlineStr">
-        <is>
-          <t>Priority Action</t>
-        </is>
-      </c>
-      <c r="C4" s="133" t="inlineStr">
-        <is>
-          <t>Card Description</t>
-        </is>
-      </c>
-      <c r="D4" s="133" t="inlineStr">
-        <is>
-          <t>SKU</t>
-        </is>
-      </c>
-      <c r="E4" s="133" t="inlineStr">
-        <is>
-          <t>Price ($)</t>
-        </is>
-      </c>
-      <c r="F4" s="133" t="inlineStr">
-        <is>
-          <t>Score</t>
-        </is>
-      </c>
-      <c r="G4" s="133" t="inlineStr">
-        <is>
-          <t>Player Tier</t>
-        </is>
-      </c>
-      <c r="H4" s="133" t="inlineStr">
-        <is>
-          <t>Days Listed</t>
-        </is>
-      </c>
-      <c r="I4" s="133" t="inlineStr">
-        <is>
-          <t>Aging Status</t>
-        </is>
-      </c>
-      <c r="J4" s="133" t="inlineStr">
-        <is>
-          <t>Watchers</t>
-        </is>
-      </c>
-      <c r="K4" s="133" t="inlineStr">
-        <is>
-          <t>Has 90d Sales?</t>
-        </is>
-      </c>
-      <c r="L4" s="133" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="125" t="n"/>
-      <c r="B5" s="125" t="n"/>
-      <c r="C5" s="125" t="n"/>
-      <c r="D5" s="125" t="n"/>
-      <c r="E5" s="126" t="n"/>
-      <c r="F5" s="125" t="n"/>
-      <c r="G5" s="125" t="n"/>
-      <c r="H5" s="125" t="n"/>
-      <c r="I5" s="134" t="n"/>
-      <c r="J5" s="125" t="n"/>
-      <c r="K5" s="125" t="n"/>
-      <c r="L5" s="125" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="125" t="n"/>
-      <c r="B6" s="125" t="n"/>
-      <c r="C6" s="125" t="n"/>
-      <c r="D6" s="125" t="n"/>
-      <c r="E6" s="126" t="n"/>
-      <c r="F6" s="125" t="n"/>
-      <c r="G6" s="125" t="n"/>
-      <c r="H6" s="125" t="n"/>
-      <c r="I6" s="134" t="n"/>
-      <c r="J6" s="125" t="n"/>
-      <c r="K6" s="125" t="n"/>
-      <c r="L6" s="125" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="125" t="n"/>
-      <c r="B7" s="125" t="n"/>
-      <c r="C7" s="125" t="n"/>
-      <c r="D7" s="125" t="n"/>
-      <c r="E7" s="126" t="n"/>
-      <c r="F7" s="125" t="n"/>
-      <c r="G7" s="125" t="n"/>
-      <c r="H7" s="125" t="n"/>
-      <c r="I7" s="134" t="n"/>
-      <c r="J7" s="125" t="n"/>
-      <c r="K7" s="125" t="n"/>
-      <c r="L7" s="125" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="125" t="n"/>
-      <c r="B8" s="125" t="n"/>
-      <c r="C8" s="125" t="n"/>
-      <c r="D8" s="125" t="n"/>
-      <c r="E8" s="126" t="n"/>
-      <c r="F8" s="125" t="n"/>
-      <c r="G8" s="125" t="n"/>
-      <c r="H8" s="125" t="n"/>
-      <c r="I8" s="134" t="n"/>
-      <c r="J8" s="125" t="n"/>
-      <c r="K8" s="125" t="n"/>
-      <c r="L8" s="125" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="125" t="n"/>
-      <c r="B9" s="125" t="n"/>
-      <c r="C9" s="125" t="n"/>
-      <c r="D9" s="125" t="n"/>
-      <c r="E9" s="126" t="n"/>
-      <c r="F9" s="125" t="n"/>
-      <c r="G9" s="125" t="n"/>
-      <c r="H9" s="125" t="n"/>
-      <c r="I9" s="134" t="n"/>
-      <c r="J9" s="125" t="n"/>
-      <c r="K9" s="125" t="n"/>
-      <c r="L9" s="125" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="125" t="n"/>
-      <c r="B10" s="125" t="n"/>
-      <c r="C10" s="125" t="n"/>
-      <c r="D10" s="125" t="n"/>
-      <c r="E10" s="126" t="n"/>
-      <c r="F10" s="125" t="n"/>
-      <c r="G10" s="125" t="n"/>
-      <c r="H10" s="125" t="n"/>
-      <c r="I10" s="134" t="n"/>
-      <c r="J10" s="125" t="n"/>
-      <c r="K10" s="125" t="n"/>
-      <c r="L10" s="125" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="125" t="n"/>
-      <c r="B11" s="125" t="n"/>
-      <c r="C11" s="125" t="n"/>
-      <c r="D11" s="125" t="n"/>
-      <c r="E11" s="126" t="n"/>
-      <c r="F11" s="125" t="n"/>
-      <c r="G11" s="125" t="n"/>
-      <c r="H11" s="125" t="n"/>
-      <c r="I11" s="134" t="n"/>
-      <c r="J11" s="125" t="n"/>
-      <c r="K11" s="125" t="n"/>
-      <c r="L11" s="125" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="125" t="n"/>
-      <c r="B12" s="125" t="n"/>
-      <c r="C12" s="125" t="n"/>
-      <c r="D12" s="125" t="n"/>
-      <c r="E12" s="126" t="n"/>
-      <c r="F12" s="125" t="n"/>
-      <c r="G12" s="125" t="n"/>
-      <c r="H12" s="125" t="n"/>
-      <c r="I12" s="134" t="n"/>
-      <c r="J12" s="125" t="n"/>
-      <c r="K12" s="125" t="n"/>
-      <c r="L12" s="125" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="125" t="n"/>
-      <c r="B13" s="125" t="n"/>
-      <c r="C13" s="125" t="n"/>
-      <c r="D13" s="125" t="n"/>
-      <c r="E13" s="126" t="n"/>
-      <c r="F13" s="125" t="n"/>
-      <c r="G13" s="125" t="n"/>
-      <c r="H13" s="125" t="n"/>
-      <c r="I13" s="125" t="n"/>
-      <c r="J13" s="125" t="n"/>
-      <c r="K13" s="125" t="n"/>
-      <c r="L13" s="125" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="125" t="n"/>
-      <c r="B14" s="125" t="n"/>
-      <c r="C14" s="125" t="n"/>
-      <c r="D14" s="125" t="n"/>
-      <c r="E14" s="126" t="n"/>
-      <c r="F14" s="125" t="n"/>
-      <c r="G14" s="125" t="n"/>
-      <c r="H14" s="125" t="n"/>
-      <c r="I14" s="134" t="n"/>
-      <c r="J14" s="125" t="n"/>
-      <c r="K14" s="125" t="n"/>
-      <c r="L14" s="125" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="125" t="n"/>
-      <c r="B15" s="125" t="n"/>
-      <c r="C15" s="125" t="n"/>
-      <c r="D15" s="125" t="n"/>
-      <c r="E15" s="126" t="n"/>
-      <c r="F15" s="125" t="n"/>
-      <c r="G15" s="125" t="n"/>
-      <c r="H15" s="125" t="n"/>
-      <c r="I15" s="134" t="n"/>
-      <c r="J15" s="125" t="n"/>
-      <c r="K15" s="125" t="n"/>
-      <c r="L15" s="125" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="125" t="n"/>
-      <c r="B16" s="125" t="n"/>
-      <c r="C16" s="125" t="n"/>
-      <c r="D16" s="125" t="n"/>
-      <c r="E16" s="126" t="n"/>
-      <c r="F16" s="125" t="n"/>
-      <c r="G16" s="125" t="n"/>
-      <c r="H16" s="125" t="n"/>
-      <c r="I16" s="134" t="n"/>
-      <c r="J16" s="125" t="n"/>
-      <c r="K16" s="125" t="n"/>
-      <c r="L16" s="125" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="125" t="n"/>
-      <c r="B17" s="125" t="n"/>
-      <c r="C17" s="125" t="n"/>
-      <c r="D17" s="125" t="n"/>
-      <c r="E17" s="126" t="n"/>
-      <c r="F17" s="125" t="n"/>
-      <c r="G17" s="125" t="n"/>
-      <c r="H17" s="125" t="n"/>
-      <c r="I17" s="134" t="n"/>
-      <c r="J17" s="125" t="n"/>
-      <c r="K17" s="125" t="n"/>
-      <c r="L17" s="125" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="125" t="n"/>
-      <c r="B18" s="125" t="n"/>
-      <c r="C18" s="125" t="n"/>
-      <c r="D18" s="125" t="n"/>
-      <c r="E18" s="126" t="n"/>
-      <c r="F18" s="125" t="n"/>
-      <c r="G18" s="125" t="n"/>
-      <c r="H18" s="125" t="n"/>
-      <c r="I18" s="134" t="n"/>
-      <c r="J18" s="125" t="n"/>
-      <c r="K18" s="125" t="n"/>
-      <c r="L18" s="125" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="125" t="n"/>
-      <c r="B19" s="125" t="n"/>
-      <c r="C19" s="125" t="n"/>
-      <c r="D19" s="125" t="n"/>
-      <c r="E19" s="126" t="n"/>
-      <c r="F19" s="125" t="n"/>
-      <c r="G19" s="125" t="n"/>
-      <c r="H19" s="125" t="n"/>
-      <c r="I19" s="134" t="n"/>
-      <c r="J19" s="125" t="n"/>
-      <c r="K19" s="125" t="n"/>
-      <c r="L19" s="125" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="125" t="n"/>
-      <c r="B20" s="125" t="n"/>
-      <c r="C20" s="125" t="n"/>
-      <c r="D20" s="125" t="n"/>
-      <c r="E20" s="126" t="n"/>
-      <c r="F20" s="125" t="n"/>
-      <c r="G20" s="125" t="n"/>
-      <c r="H20" s="125" t="n"/>
-      <c r="I20" s="134" t="n"/>
-      <c r="J20" s="125" t="n"/>
-      <c r="K20" s="125" t="n"/>
-      <c r="L20" s="125" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="125" t="n"/>
-      <c r="B21" s="125" t="n"/>
-      <c r="C21" s="125" t="n"/>
-      <c r="D21" s="125" t="n"/>
-      <c r="E21" s="126" t="n"/>
-      <c r="F21" s="125" t="n"/>
-      <c r="G21" s="125" t="n"/>
-      <c r="H21" s="125" t="n"/>
-      <c r="I21" s="134" t="n"/>
-      <c r="J21" s="125" t="n"/>
-      <c r="K21" s="125" t="n"/>
-      <c r="L21" s="125" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="125" t="n"/>
-      <c r="B22" s="125" t="n"/>
-      <c r="C22" s="125" t="n"/>
-      <c r="D22" s="125" t="n"/>
-      <c r="E22" s="126" t="n"/>
-      <c r="F22" s="125" t="n"/>
-      <c r="G22" s="125" t="n"/>
-      <c r="H22" s="125" t="n"/>
-      <c r="I22" s="134" t="n"/>
-      <c r="J22" s="125" t="n"/>
-      <c r="K22" s="125" t="n"/>
-      <c r="L22" s="125" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="125" t="n"/>
-      <c r="B23" s="125" t="n"/>
-      <c r="C23" s="125" t="n"/>
-      <c r="D23" s="125" t="n"/>
-      <c r="E23" s="126" t="n"/>
-      <c r="F23" s="125" t="n"/>
-      <c r="G23" s="125" t="n"/>
-      <c r="H23" s="125" t="n"/>
-      <c r="I23" s="134" t="n"/>
-      <c r="J23" s="125" t="n"/>
-      <c r="K23" s="125" t="n"/>
-      <c r="L23" s="125" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="125" t="n"/>
-      <c r="B24" s="125" t="n"/>
-      <c r="C24" s="125" t="n"/>
-      <c r="D24" s="125" t="n"/>
-      <c r="E24" s="126" t="n"/>
-      <c r="F24" s="125" t="n"/>
-      <c r="G24" s="125" t="n"/>
-      <c r="H24" s="125" t="n"/>
-      <c r="I24" s="134" t="n"/>
-      <c r="J24" s="125" t="n"/>
-      <c r="K24" s="125" t="n"/>
-      <c r="L24" s="125" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="125" t="n"/>
-      <c r="B25" s="125" t="n"/>
-      <c r="C25" s="125" t="n"/>
-      <c r="D25" s="125" t="n"/>
-      <c r="E25" s="126" t="n"/>
-      <c r="F25" s="125" t="n"/>
-      <c r="G25" s="125" t="n"/>
-      <c r="H25" s="125" t="n"/>
-      <c r="I25" s="134" t="n"/>
-      <c r="J25" s="125" t="n"/>
-      <c r="K25" s="125" t="n"/>
-      <c r="L25" s="125" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="125" t="n"/>
-      <c r="B26" s="125" t="n"/>
-      <c r="C26" s="125" t="n"/>
-      <c r="D26" s="125" t="n"/>
-      <c r="E26" s="126" t="n"/>
-      <c r="F26" s="125" t="n"/>
-      <c r="G26" s="125" t="n"/>
-      <c r="H26" s="125" t="n"/>
-      <c r="I26" s="134" t="n"/>
-      <c r="J26" s="125" t="n"/>
-      <c r="K26" s="125" t="n"/>
-      <c r="L26" s="125" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="125" t="n"/>
-      <c r="B27" s="125" t="n"/>
-      <c r="C27" s="125" t="n"/>
-      <c r="D27" s="125" t="n"/>
-      <c r="E27" s="126" t="n"/>
-      <c r="F27" s="125" t="n"/>
-      <c r="G27" s="125" t="n"/>
-      <c r="H27" s="125" t="n"/>
-      <c r="I27" s="134" t="n"/>
-      <c r="J27" s="125" t="n"/>
-      <c r="K27" s="125" t="n"/>
-      <c r="L27" s="125" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="125" t="n"/>
-      <c r="B28" s="125" t="n"/>
-      <c r="C28" s="125" t="n"/>
-      <c r="D28" s="125" t="n"/>
-      <c r="E28" s="126" t="n"/>
-      <c r="F28" s="125" t="n"/>
-      <c r="G28" s="125" t="n"/>
-      <c r="H28" s="125" t="n"/>
-      <c r="I28" s="134" t="n"/>
-      <c r="J28" s="125" t="n"/>
-      <c r="K28" s="125" t="n"/>
-      <c r="L28" s="125" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="125" t="n"/>
-      <c r="B29" s="125" t="n"/>
-      <c r="C29" s="125" t="n"/>
-      <c r="D29" s="125" t="n"/>
-      <c r="E29" s="126" t="n"/>
-      <c r="F29" s="125" t="n"/>
-      <c r="G29" s="125" t="n"/>
-      <c r="H29" s="125" t="n"/>
-      <c r="I29" s="134" t="n"/>
-      <c r="J29" s="125" t="n"/>
-      <c r="K29" s="125" t="n"/>
-      <c r="L29" s="125" t="n"/>
-    </row>
-    <row r="32" ht="16" customHeight="1" s="230">
-      <c r="A32" s="282" t="n"/>
-    </row>
-    <row r="33" ht="22" customHeight="1" s="230">
-      <c r="A33" s="170" t="n"/>
-      <c r="B33" s="170" t="n"/>
-      <c r="C33" s="170" t="n"/>
-      <c r="D33" s="170" t="n"/>
-      <c r="E33" s="170" t="n"/>
-      <c r="F33" s="170" t="n"/>
-      <c r="G33" s="170" t="n"/>
-      <c r="H33" s="170" t="n"/>
-      <c r="I33" s="170" t="n"/>
-      <c r="J33" s="170" t="n"/>
-      <c r="K33" s="170" t="n"/>
-      <c r="L33" s="170" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="125" t="n"/>
-      <c r="B34" s="125" t="n"/>
-      <c r="C34" s="125" t="n"/>
-      <c r="D34" s="126" t="n"/>
-      <c r="E34" s="125" t="n"/>
-      <c r="F34" s="134" t="n"/>
-      <c r="G34" s="125" t="n"/>
-      <c r="H34" s="125" t="n"/>
-      <c r="I34" s="125" t="n"/>
-      <c r="J34" s="125" t="n"/>
-      <c r="K34" s="125" t="n"/>
-      <c r="L34" s="125" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="129" t="n"/>
-      <c r="B35" s="129" t="n"/>
-      <c r="C35" s="129" t="n"/>
-      <c r="D35" s="130" t="n"/>
-      <c r="E35" s="129" t="n"/>
-      <c r="F35" s="134" t="n"/>
-      <c r="G35" s="129" t="n"/>
-      <c r="H35" s="129" t="n"/>
-      <c r="I35" s="129" t="n"/>
-      <c r="J35" s="129" t="n"/>
-      <c r="K35" s="129" t="n"/>
-      <c r="L35" s="129" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="125" t="n"/>
-      <c r="B36" s="125" t="n"/>
-      <c r="C36" s="125" t="n"/>
-      <c r="D36" s="126" t="n"/>
-      <c r="E36" s="125" t="n"/>
-      <c r="F36" s="134" t="n"/>
-      <c r="G36" s="125" t="n"/>
-      <c r="H36" s="125" t="n"/>
-      <c r="I36" s="125" t="n"/>
-      <c r="J36" s="125" t="n"/>
-      <c r="K36" s="125" t="n"/>
-      <c r="L36" s="125" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="129" t="n"/>
-      <c r="B37" s="129" t="n"/>
-      <c r="C37" s="129" t="n"/>
-      <c r="D37" s="130" t="n"/>
-      <c r="E37" s="129" t="n"/>
-      <c r="F37" s="134" t="n"/>
-      <c r="G37" s="129" t="n"/>
-      <c r="H37" s="129" t="n"/>
-      <c r="I37" s="129" t="n"/>
-      <c r="J37" s="129" t="n"/>
-      <c r="K37" s="129" t="n"/>
-      <c r="L37" s="129" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="125" t="n"/>
-      <c r="B38" s="125" t="n"/>
-      <c r="C38" s="125" t="n"/>
-      <c r="D38" s="126" t="n"/>
-      <c r="E38" s="125" t="n"/>
-      <c r="F38" s="134" t="n"/>
-      <c r="G38" s="125" t="n"/>
-      <c r="H38" s="125" t="n"/>
-      <c r="I38" s="125" t="n"/>
-      <c r="J38" s="125" t="n"/>
-      <c r="K38" s="125" t="n"/>
-      <c r="L38" s="125" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="129" t="n"/>
-      <c r="B39" s="129" t="n"/>
-      <c r="C39" s="129" t="n"/>
-      <c r="D39" s="130" t="n"/>
-      <c r="E39" s="129" t="n"/>
-      <c r="F39" s="134" t="n"/>
-      <c r="G39" s="129" t="n"/>
-      <c r="H39" s="129" t="n"/>
-      <c r="I39" s="129" t="n"/>
-      <c r="J39" s="129" t="n"/>
-      <c r="K39" s="129" t="n"/>
-      <c r="L39" s="129" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="125" t="n"/>
-      <c r="B40" s="125" t="n"/>
-      <c r="C40" s="125" t="n"/>
-      <c r="D40" s="126" t="n"/>
-      <c r="E40" s="125" t="n"/>
-      <c r="F40" s="134" t="n"/>
-      <c r="G40" s="125" t="n"/>
-      <c r="H40" s="125" t="n"/>
-      <c r="I40" s="125" t="n"/>
-      <c r="J40" s="125" t="n"/>
-      <c r="K40" s="125" t="n"/>
-      <c r="L40" s="125" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="129" t="n"/>
-      <c r="B41" s="129" t="n"/>
-      <c r="C41" s="129" t="n"/>
-      <c r="D41" s="130" t="n"/>
-      <c r="E41" s="129" t="n"/>
-      <c r="F41" s="134" t="n"/>
-      <c r="G41" s="129" t="n"/>
-      <c r="H41" s="129" t="n"/>
-      <c r="I41" s="129" t="n"/>
-      <c r="J41" s="129" t="n"/>
-      <c r="K41" s="129" t="n"/>
-      <c r="L41" s="129" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="125" t="n"/>
-      <c r="B42" s="125" t="n"/>
-      <c r="C42" s="125" t="n"/>
-      <c r="D42" s="126" t="n"/>
-      <c r="E42" s="125" t="n"/>
-      <c r="F42" s="158" t="n"/>
-      <c r="G42" s="125" t="n"/>
-      <c r="H42" s="125" t="n"/>
-      <c r="I42" s="125" t="n"/>
-      <c r="J42" s="125" t="n"/>
-      <c r="K42" s="125" t="n"/>
-      <c r="L42" s="125" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="129" t="n"/>
-      <c r="B43" s="129" t="n"/>
-      <c r="C43" s="129" t="n"/>
-      <c r="D43" s="130" t="n"/>
-      <c r="E43" s="129" t="n"/>
-      <c r="F43" s="134" t="n"/>
-      <c r="G43" s="129" t="n"/>
-      <c r="H43" s="129" t="n"/>
-      <c r="I43" s="129" t="n"/>
-      <c r="J43" s="129" t="n"/>
-      <c r="K43" s="129" t="n"/>
-      <c r="L43" s="129" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="125" t="n"/>
-      <c r="B44" s="125" t="n"/>
-      <c r="C44" s="125" t="n"/>
-      <c r="D44" s="126" t="n"/>
-      <c r="E44" s="125" t="n"/>
-      <c r="F44" s="134" t="n"/>
-      <c r="G44" s="125" t="n"/>
-      <c r="H44" s="125" t="n"/>
-      <c r="I44" s="125" t="n"/>
-      <c r="J44" s="125" t="n"/>
-      <c r="K44" s="125" t="n"/>
-      <c r="L44" s="125" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="129" t="n"/>
-      <c r="B45" s="129" t="n"/>
-      <c r="C45" s="129" t="n"/>
-      <c r="D45" s="130" t="n"/>
-      <c r="E45" s="129" t="n"/>
-      <c r="F45" s="134" t="n"/>
-      <c r="G45" s="129" t="n"/>
-      <c r="H45" s="129" t="n"/>
-      <c r="I45" s="129" t="n"/>
-      <c r="J45" s="129" t="n"/>
-      <c r="K45" s="129" t="n"/>
-      <c r="L45" s="129" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="125" t="n"/>
-      <c r="B46" s="125" t="n"/>
-      <c r="C46" s="125" t="n"/>
-      <c r="D46" s="126" t="n"/>
-      <c r="E46" s="125" t="n"/>
-      <c r="F46" s="134" t="n"/>
-      <c r="G46" s="125" t="n"/>
-      <c r="H46" s="125" t="n"/>
-      <c r="I46" s="125" t="n"/>
-      <c r="J46" s="125" t="n"/>
-      <c r="K46" s="125" t="n"/>
-      <c r="L46" s="125" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="129" t="n"/>
-      <c r="B47" s="129" t="n"/>
-      <c r="C47" s="129" t="n"/>
-      <c r="D47" s="130" t="n"/>
-      <c r="E47" s="129" t="n"/>
-      <c r="F47" s="134" t="n"/>
-      <c r="G47" s="129" t="n"/>
-      <c r="H47" s="129" t="n"/>
-      <c r="I47" s="129" t="n"/>
-      <c r="J47" s="129" t="n"/>
-      <c r="K47" s="129" t="n"/>
-      <c r="L47" s="129" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="125" t="n"/>
-      <c r="B48" s="125" t="n"/>
-      <c r="C48" s="125" t="n"/>
-      <c r="D48" s="126" t="n"/>
-      <c r="E48" s="125" t="n"/>
-      <c r="F48" s="134" t="n"/>
-      <c r="G48" s="125" t="n"/>
-      <c r="H48" s="125" t="n"/>
-      <c r="I48" s="125" t="n"/>
-      <c r="J48" s="125" t="n"/>
-      <c r="K48" s="125" t="n"/>
-      <c r="L48" s="125" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="129" t="n"/>
-      <c r="B49" s="129" t="n"/>
-      <c r="C49" s="129" t="n"/>
-      <c r="D49" s="130" t="n"/>
-      <c r="E49" s="129" t="n"/>
-      <c r="F49" s="134" t="n"/>
-      <c r="G49" s="129" t="n"/>
-      <c r="H49" s="129" t="n"/>
-      <c r="I49" s="129" t="n"/>
-      <c r="J49" s="129" t="n"/>
-      <c r="K49" s="129" t="n"/>
-      <c r="L49" s="129" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="125" t="n"/>
-      <c r="B50" s="125" t="n"/>
-      <c r="C50" s="125" t="n"/>
-      <c r="D50" s="126" t="n"/>
-      <c r="E50" s="125" t="n"/>
-      <c r="F50" s="134" t="n"/>
-      <c r="G50" s="125" t="n"/>
-      <c r="H50" s="125" t="n"/>
-      <c r="I50" s="125" t="n"/>
-      <c r="J50" s="125" t="n"/>
-      <c r="K50" s="125" t="n"/>
-      <c r="L50" s="125" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="129" t="n"/>
-      <c r="B51" s="129" t="n"/>
-      <c r="C51" s="129" t="n"/>
-      <c r="D51" s="130" t="n"/>
-      <c r="E51" s="129" t="n"/>
-      <c r="F51" s="134" t="n"/>
-      <c r="G51" s="129" t="n"/>
-      <c r="H51" s="129" t="n"/>
-      <c r="I51" s="129" t="n"/>
-      <c r="J51" s="129" t="n"/>
-      <c r="K51" s="129" t="n"/>
-      <c r="L51" s="129" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="125" t="n"/>
-      <c r="B52" s="125" t="n"/>
-      <c r="C52" s="125" t="n"/>
-      <c r="D52" s="126" t="n"/>
-      <c r="E52" s="125" t="n"/>
-      <c r="F52" s="134" t="n"/>
-      <c r="G52" s="125" t="n"/>
-      <c r="H52" s="125" t="n"/>
-      <c r="I52" s="125" t="n"/>
-      <c r="J52" s="125" t="n"/>
-      <c r="K52" s="125" t="n"/>
-      <c r="L52" s="125" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="129" t="n"/>
-      <c r="B53" s="129" t="n"/>
-      <c r="C53" s="129" t="n"/>
-      <c r="D53" s="130" t="n"/>
-      <c r="E53" s="129" t="n"/>
-      <c r="F53" s="134" t="n"/>
-      <c r="G53" s="129" t="n"/>
-      <c r="H53" s="129" t="n"/>
-      <c r="I53" s="129" t="n"/>
-      <c r="J53" s="129" t="n"/>
-      <c r="K53" s="129" t="n"/>
-      <c r="L53" s="129" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="125" t="n"/>
-      <c r="B54" s="125" t="n"/>
-      <c r="C54" s="125" t="n"/>
-      <c r="D54" s="126" t="n"/>
-      <c r="E54" s="125" t="n"/>
-      <c r="F54" s="134" t="n"/>
-      <c r="G54" s="125" t="n"/>
-      <c r="H54" s="125" t="n"/>
-      <c r="I54" s="125" t="n"/>
-      <c r="J54" s="125" t="n"/>
-      <c r="K54" s="125" t="n"/>
-      <c r="L54" s="125" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="129" t="n"/>
-      <c r="B55" s="129" t="n"/>
-      <c r="C55" s="129" t="n"/>
-      <c r="D55" s="130" t="n"/>
-      <c r="E55" s="129" t="n"/>
-      <c r="F55" s="134" t="n"/>
-      <c r="G55" s="129" t="n"/>
-      <c r="H55" s="129" t="n"/>
-      <c r="I55" s="129" t="n"/>
-      <c r="J55" s="129" t="n"/>
-      <c r="K55" s="129" t="n"/>
-      <c r="L55" s="129" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="125" t="n"/>
-      <c r="B56" s="125" t="n"/>
-      <c r="C56" s="125" t="n"/>
-      <c r="D56" s="126" t="n"/>
-      <c r="E56" s="125" t="n"/>
-      <c r="F56" s="134" t="n"/>
-      <c r="G56" s="125" t="n"/>
-      <c r="H56" s="125" t="n"/>
-      <c r="I56" s="125" t="n"/>
-      <c r="J56" s="125" t="n"/>
-      <c r="K56" s="125" t="n"/>
-      <c r="L56" s="125" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="129" t="n"/>
-      <c r="B57" s="129" t="n"/>
-      <c r="C57" s="129" t="n"/>
-      <c r="D57" s="130" t="n"/>
-      <c r="E57" s="129" t="n"/>
-      <c r="F57" s="134" t="n"/>
-      <c r="G57" s="129" t="n"/>
-      <c r="H57" s="129" t="n"/>
-      <c r="I57" s="129" t="n"/>
-      <c r="J57" s="129" t="n"/>
-      <c r="K57" s="129" t="n"/>
-      <c r="L57" s="129" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="125" t="n"/>
-      <c r="B58" s="125" t="n"/>
-      <c r="C58" s="125" t="n"/>
-      <c r="D58" s="126" t="n"/>
-      <c r="E58" s="125" t="n"/>
-      <c r="F58" s="134" t="n"/>
-      <c r="G58" s="125" t="n"/>
-      <c r="H58" s="125" t="n"/>
-      <c r="I58" s="125" t="n"/>
-      <c r="J58" s="125" t="n"/>
-      <c r="K58" s="125" t="n"/>
-      <c r="L58" s="125" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="129" t="n"/>
-      <c r="B59" s="129" t="n"/>
-      <c r="C59" s="129" t="n"/>
-      <c r="D59" s="130" t="n"/>
-      <c r="E59" s="129" t="n"/>
-      <c r="F59" s="134" t="n"/>
-      <c r="G59" s="129" t="n"/>
-      <c r="H59" s="129" t="n"/>
-      <c r="I59" s="129" t="n"/>
-      <c r="J59" s="129" t="n"/>
-      <c r="K59" s="129" t="n"/>
-      <c r="L59" s="129" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="125" t="n"/>
-      <c r="B60" s="125" t="n"/>
-      <c r="C60" s="125" t="n"/>
-      <c r="D60" s="126" t="n"/>
-      <c r="E60" s="125" t="n"/>
-      <c r="F60" s="134" t="n"/>
-      <c r="G60" s="125" t="n"/>
-      <c r="H60" s="125" t="n"/>
-      <c r="I60" s="125" t="n"/>
-      <c r="J60" s="125" t="n"/>
-      <c r="K60" s="125" t="n"/>
-      <c r="L60" s="125" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="129" t="n"/>
-      <c r="B61" s="129" t="n"/>
-      <c r="C61" s="129" t="n"/>
-      <c r="D61" s="130" t="n"/>
-      <c r="E61" s="129" t="n"/>
-      <c r="F61" s="134" t="n"/>
-      <c r="G61" s="129" t="n"/>
-      <c r="H61" s="129" t="n"/>
-      <c r="I61" s="129" t="n"/>
-      <c r="J61" s="129" t="n"/>
-      <c r="K61" s="129" t="n"/>
-      <c r="L61" s="129" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="125" t="n"/>
-      <c r="B62" s="125" t="n"/>
-      <c r="C62" s="125" t="n"/>
-      <c r="D62" s="126" t="n"/>
-      <c r="E62" s="125" t="n"/>
-      <c r="F62" s="134" t="n"/>
-      <c r="G62" s="125" t="n"/>
-      <c r="H62" s="125" t="n"/>
-      <c r="I62" s="125" t="n"/>
-      <c r="J62" s="125" t="n"/>
-      <c r="K62" s="125" t="n"/>
-      <c r="L62" s="125" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="129" t="n"/>
-      <c r="B63" s="129" t="n"/>
-      <c r="C63" s="129" t="n"/>
-      <c r="D63" s="130" t="n"/>
-      <c r="E63" s="129" t="n"/>
-      <c r="F63" s="134" t="n"/>
-      <c r="G63" s="129" t="n"/>
-      <c r="H63" s="129" t="n"/>
-      <c r="I63" s="129" t="n"/>
-      <c r="J63" s="129" t="n"/>
-      <c r="K63" s="129" t="n"/>
-      <c r="L63" s="129" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="125" t="n"/>
-      <c r="B64" s="125" t="n"/>
-      <c r="C64" s="125" t="n"/>
-      <c r="D64" s="126" t="n"/>
-      <c r="E64" s="125" t="n"/>
-      <c r="F64" s="134" t="n"/>
-      <c r="G64" s="125" t="n"/>
-      <c r="H64" s="125" t="n"/>
-      <c r="I64" s="125" t="n"/>
-      <c r="J64" s="125" t="n"/>
-      <c r="K64" s="125" t="n"/>
-      <c r="L64" s="125" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="129" t="n"/>
-      <c r="B65" s="129" t="n"/>
-      <c r="C65" s="129" t="n"/>
-      <c r="D65" s="130" t="n"/>
-      <c r="E65" s="129" t="n"/>
-      <c r="F65" s="134" t="n"/>
-      <c r="G65" s="129" t="n"/>
-      <c r="H65" s="129" t="n"/>
-      <c r="I65" s="129" t="n"/>
-      <c r="J65" s="129" t="n"/>
-      <c r="K65" s="129" t="n"/>
-      <c r="L65" s="129" t="n"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="125" t="n"/>
-      <c r="B66" s="125" t="n"/>
-      <c r="C66" s="125" t="n"/>
-      <c r="D66" s="126" t="n"/>
-      <c r="E66" s="125" t="n"/>
-      <c r="F66" s="134" t="n"/>
-      <c r="G66" s="125" t="n"/>
-      <c r="H66" s="125" t="n"/>
-      <c r="I66" s="125" t="n"/>
-      <c r="J66" s="125" t="n"/>
-      <c r="K66" s="125" t="n"/>
-      <c r="L66" s="125" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="129" t="n"/>
-      <c r="B67" s="129" t="n"/>
-      <c r="C67" s="129" t="n"/>
-      <c r="D67" s="130" t="n"/>
-      <c r="E67" s="129" t="n"/>
-      <c r="F67" s="134" t="n"/>
-      <c r="G67" s="129" t="n"/>
-      <c r="H67" s="129" t="n"/>
-      <c r="I67" s="129" t="n"/>
-      <c r="J67" s="129" t="n"/>
-      <c r="K67" s="129" t="n"/>
-      <c r="L67" s="129" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="125" t="n"/>
-      <c r="B68" s="125" t="n"/>
-      <c r="C68" s="125" t="n"/>
-      <c r="D68" s="126" t="n"/>
-      <c r="E68" s="125" t="n"/>
-      <c r="F68" s="134" t="n"/>
-      <c r="G68" s="125" t="n"/>
-      <c r="H68" s="125" t="n"/>
-      <c r="I68" s="125" t="n"/>
-      <c r="J68" s="125" t="n"/>
-      <c r="K68" s="125" t="n"/>
-      <c r="L68" s="125" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="129" t="n"/>
-      <c r="B69" s="129" t="n"/>
-      <c r="C69" s="129" t="n"/>
-      <c r="D69" s="130" t="n"/>
-      <c r="E69" s="129" t="n"/>
-      <c r="F69" s="134" t="n"/>
-      <c r="G69" s="129" t="n"/>
-      <c r="H69" s="129" t="n"/>
-      <c r="I69" s="129" t="n"/>
-      <c r="J69" s="129" t="n"/>
-      <c r="K69" s="129" t="n"/>
-      <c r="L69" s="129" t="n"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="125" t="n"/>
-      <c r="B70" s="125" t="n"/>
-      <c r="C70" s="125" t="n"/>
-      <c r="D70" s="126" t="n"/>
-      <c r="E70" s="125" t="n"/>
-      <c r="F70" s="134" t="n"/>
-      <c r="G70" s="125" t="n"/>
-      <c r="H70" s="125" t="n"/>
-      <c r="I70" s="125" t="n"/>
-      <c r="J70" s="125" t="n"/>
-      <c r="K70" s="125" t="n"/>
-      <c r="L70" s="125" t="n"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="129" t="n"/>
-      <c r="B71" s="129" t="n"/>
-      <c r="C71" s="129" t="n"/>
-      <c r="D71" s="130" t="n"/>
-      <c r="E71" s="129" t="n"/>
-      <c r="F71" s="134" t="n"/>
-      <c r="G71" s="129" t="n"/>
-      <c r="H71" s="129" t="n"/>
-      <c r="I71" s="129" t="n"/>
-      <c r="J71" s="129" t="n"/>
-      <c r="K71" s="129" t="n"/>
-      <c r="L71" s="129" t="n"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="125" t="n"/>
-      <c r="B72" s="125" t="n"/>
-      <c r="C72" s="125" t="n"/>
-      <c r="D72" s="126" t="n"/>
-      <c r="E72" s="125" t="n"/>
-      <c r="F72" s="134" t="n"/>
-      <c r="G72" s="125" t="n"/>
-      <c r="H72" s="125" t="n"/>
-      <c r="I72" s="125" t="n"/>
-      <c r="J72" s="125" t="n"/>
-      <c r="K72" s="125" t="n"/>
-      <c r="L72" s="125" t="n"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="129" t="n"/>
-      <c r="B73" s="129" t="n"/>
-      <c r="C73" s="129" t="n"/>
-      <c r="D73" s="130" t="n"/>
-      <c r="E73" s="129" t="n"/>
-      <c r="F73" s="134" t="n"/>
-      <c r="G73" s="129" t="n"/>
-      <c r="H73" s="129" t="n"/>
-      <c r="I73" s="129" t="n"/>
-      <c r="J73" s="129" t="n"/>
-      <c r="K73" s="129" t="n"/>
-      <c r="L73" s="129" t="n"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="125" t="n"/>
-      <c r="B74" s="125" t="n"/>
-      <c r="C74" s="125" t="n"/>
-      <c r="D74" s="126" t="n"/>
-      <c r="E74" s="125" t="n"/>
-      <c r="F74" s="134" t="n"/>
-      <c r="G74" s="125" t="n"/>
-      <c r="H74" s="125" t="n"/>
-      <c r="I74" s="125" t="n"/>
-      <c r="J74" s="125" t="n"/>
-      <c r="K74" s="125" t="n"/>
-      <c r="L74" s="125" t="n"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="129" t="n"/>
-      <c r="B75" s="129" t="n"/>
-      <c r="C75" s="129" t="n"/>
-      <c r="D75" s="130" t="n"/>
-      <c r="E75" s="129" t="n"/>
-      <c r="F75" s="134" t="n"/>
-      <c r="G75" s="129" t="n"/>
-      <c r="H75" s="129" t="n"/>
-      <c r="I75" s="129" t="n"/>
-      <c r="J75" s="129" t="n"/>
-      <c r="K75" s="129" t="n"/>
-      <c r="L75" s="129" t="n"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="125" t="n"/>
-      <c r="B76" s="125" t="n"/>
-      <c r="C76" s="125" t="n"/>
-      <c r="D76" s="126" t="n"/>
-      <c r="E76" s="125" t="n"/>
-      <c r="F76" s="134" t="n"/>
-      <c r="G76" s="125" t="n"/>
-      <c r="H76" s="125" t="n"/>
-      <c r="I76" s="125" t="n"/>
-      <c r="J76" s="125" t="n"/>
-      <c r="K76" s="125" t="n"/>
-      <c r="L76" s="125" t="n"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="129" t="n"/>
-      <c r="B77" s="129" t="n"/>
-      <c r="C77" s="129" t="n"/>
-      <c r="D77" s="130" t="n"/>
-      <c r="E77" s="129" t="n"/>
-      <c r="F77" s="134" t="n"/>
-      <c r="G77" s="129" t="n"/>
-      <c r="H77" s="129" t="n"/>
-      <c r="I77" s="129" t="n"/>
-      <c r="J77" s="129" t="n"/>
-      <c r="K77" s="129" t="n"/>
-      <c r="L77" s="129" t="n"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="125" t="n"/>
-      <c r="B78" s="125" t="n"/>
-      <c r="C78" s="125" t="n"/>
-      <c r="D78" s="126" t="n"/>
-      <c r="E78" s="125" t="n"/>
-      <c r="F78" s="134" t="n"/>
-      <c r="G78" s="125" t="n"/>
-      <c r="H78" s="125" t="n"/>
-      <c r="I78" s="125" t="n"/>
-      <c r="J78" s="125" t="n"/>
-      <c r="K78" s="125" t="n"/>
-      <c r="L78" s="125" t="n"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="129" t="n"/>
-      <c r="B79" s="129" t="n"/>
-      <c r="C79" s="129" t="n"/>
-      <c r="D79" s="130" t="n"/>
-      <c r="E79" s="129" t="n"/>
-      <c r="F79" s="134" t="n"/>
-      <c r="G79" s="129" t="n"/>
-      <c r="H79" s="129" t="n"/>
-      <c r="I79" s="129" t="n"/>
-      <c r="J79" s="129" t="n"/>
-      <c r="K79" s="129" t="n"/>
-      <c r="L79" s="129" t="n"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="125" t="n"/>
-      <c r="B80" s="125" t="n"/>
-      <c r="C80" s="125" t="n"/>
-      <c r="D80" s="126" t="n"/>
-      <c r="E80" s="125" t="n"/>
-      <c r="F80" s="134" t="n"/>
-      <c r="G80" s="125" t="n"/>
-      <c r="H80" s="125" t="n"/>
-      <c r="I80" s="125" t="n"/>
-      <c r="J80" s="125" t="n"/>
-      <c r="K80" s="125" t="n"/>
-      <c r="L80" s="125" t="n"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="129" t="n"/>
-      <c r="B81" s="129" t="n"/>
-      <c r="C81" s="129" t="n"/>
-      <c r="D81" s="130" t="n"/>
-      <c r="E81" s="129" t="n"/>
-      <c r="F81" s="134" t="n"/>
-      <c r="G81" s="129" t="n"/>
-      <c r="H81" s="129" t="n"/>
-      <c r="I81" s="129" t="n"/>
-      <c r="J81" s="129" t="n"/>
-      <c r="K81" s="129" t="n"/>
-      <c r="L81" s="129" t="n"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="125" t="n"/>
-      <c r="B82" s="125" t="n"/>
-      <c r="C82" s="125" t="n"/>
-      <c r="D82" s="126" t="n"/>
-      <c r="E82" s="125" t="n"/>
-      <c r="F82" s="134" t="n"/>
-      <c r="G82" s="125" t="n"/>
-      <c r="H82" s="125" t="n"/>
-      <c r="I82" s="125" t="n"/>
-      <c r="J82" s="125" t="n"/>
-      <c r="K82" s="125" t="n"/>
-      <c r="L82" s="125" t="n"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="129" t="n"/>
-      <c r="B83" s="129" t="n"/>
-      <c r="C83" s="129" t="n"/>
-      <c r="D83" s="130" t="n"/>
-      <c r="E83" s="129" t="n"/>
-      <c r="F83" s="134" t="n"/>
-      <c r="G83" s="129" t="n"/>
-      <c r="H83" s="129" t="n"/>
-      <c r="I83" s="129" t="n"/>
-      <c r="J83" s="129" t="n"/>
-      <c r="K83" s="129" t="n"/>
-      <c r="L83" s="129" t="n"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="125" t="n"/>
-      <c r="B84" s="125" t="n"/>
-      <c r="C84" s="125" t="n"/>
-      <c r="D84" s="126" t="n"/>
-      <c r="E84" s="125" t="n"/>
-      <c r="F84" s="134" t="n"/>
-      <c r="G84" s="125" t="n"/>
-      <c r="H84" s="125" t="n"/>
-      <c r="I84" s="125" t="n"/>
-      <c r="J84" s="125" t="n"/>
-      <c r="K84" s="125" t="n"/>
-      <c r="L84" s="125" t="n"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="129" t="n"/>
-      <c r="B85" s="129" t="n"/>
-      <c r="C85" s="129" t="n"/>
-      <c r="D85" s="130" t="n"/>
-      <c r="E85" s="129" t="n"/>
-      <c r="F85" s="134" t="n"/>
-      <c r="G85" s="129" t="n"/>
-      <c r="H85" s="129" t="n"/>
-      <c r="I85" s="129" t="n"/>
-      <c r="J85" s="129" t="n"/>
-      <c r="K85" s="129" t="n"/>
-      <c r="L85" s="129" t="n"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="125" t="n"/>
-      <c r="B86" s="125" t="n"/>
-      <c r="C86" s="125" t="n"/>
-      <c r="D86" s="126" t="n"/>
-      <c r="E86" s="125" t="n"/>
-      <c r="F86" s="134" t="n"/>
-      <c r="G86" s="125" t="n"/>
-      <c r="H86" s="125" t="n"/>
-      <c r="I86" s="125" t="n"/>
-      <c r="J86" s="125" t="n"/>
-      <c r="K86" s="125" t="n"/>
-      <c r="L86" s="125" t="n"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="129" t="n"/>
-      <c r="B87" s="129" t="n"/>
-      <c r="C87" s="129" t="n"/>
-      <c r="D87" s="130" t="n"/>
-      <c r="E87" s="129" t="n"/>
-      <c r="F87" s="134" t="n"/>
-      <c r="G87" s="129" t="n"/>
-      <c r="H87" s="129" t="n"/>
-      <c r="I87" s="129" t="n"/>
-      <c r="J87" s="129" t="n"/>
-      <c r="K87" s="129" t="n"/>
-      <c r="L87" s="129" t="n"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="125" t="n"/>
-      <c r="B88" s="125" t="n"/>
-      <c r="C88" s="125" t="n"/>
-      <c r="D88" s="126" t="n"/>
-      <c r="E88" s="125" t="n"/>
-      <c r="F88" s="134" t="n"/>
-      <c r="G88" s="125" t="n"/>
-      <c r="H88" s="125" t="n"/>
-      <c r="I88" s="125" t="n"/>
-      <c r="J88" s="125" t="n"/>
-      <c r="K88" s="125" t="n"/>
-      <c r="L88" s="125" t="n"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="129" t="n"/>
-      <c r="B89" s="129" t="n"/>
-      <c r="C89" s="129" t="n"/>
-      <c r="D89" s="130" t="n"/>
-      <c r="E89" s="129" t="n"/>
-      <c r="F89" s="134" t="n"/>
-      <c r="G89" s="129" t="n"/>
-      <c r="H89" s="129" t="n"/>
-      <c r="I89" s="129" t="n"/>
-      <c r="J89" s="129" t="n"/>
-      <c r="K89" s="129" t="n"/>
-      <c r="L89" s="129" t="n"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="125" t="n"/>
-      <c r="B90" s="125" t="n"/>
-      <c r="C90" s="125" t="n"/>
-      <c r="D90" s="126" t="n"/>
-      <c r="E90" s="125" t="n"/>
-      <c r="F90" s="134" t="n"/>
-      <c r="G90" s="125" t="n"/>
-      <c r="H90" s="125" t="n"/>
-      <c r="I90" s="125" t="n"/>
-      <c r="J90" s="125" t="n"/>
-      <c r="K90" s="125" t="n"/>
-      <c r="L90" s="125" t="n"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="129" t="n"/>
-      <c r="B91" s="129" t="n"/>
-      <c r="C91" s="129" t="n"/>
-      <c r="D91" s="130" t="n"/>
-      <c r="E91" s="129" t="n"/>
-      <c r="F91" s="134" t="n"/>
-      <c r="G91" s="129" t="n"/>
-      <c r="H91" s="129" t="n"/>
-      <c r="I91" s="129" t="n"/>
-      <c r="J91" s="129" t="n"/>
-      <c r="K91" s="129" t="n"/>
-      <c r="L91" s="129" t="n"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="125" t="n"/>
-      <c r="B92" s="125" t="n"/>
-      <c r="C92" s="125" t="n"/>
-      <c r="D92" s="126" t="n"/>
-      <c r="E92" s="125" t="n"/>
-      <c r="F92" s="134" t="n"/>
-      <c r="G92" s="125" t="n"/>
-      <c r="H92" s="125" t="n"/>
-      <c r="I92" s="125" t="n"/>
-      <c r="J92" s="125" t="n"/>
-      <c r="K92" s="125" t="n"/>
-      <c r="L92" s="125" t="n"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="129" t="n"/>
-      <c r="B93" s="129" t="n"/>
-      <c r="C93" s="129" t="n"/>
-      <c r="D93" s="130" t="n"/>
-      <c r="E93" s="129" t="n"/>
-      <c r="F93" s="134" t="n"/>
-      <c r="G93" s="129" t="n"/>
-      <c r="H93" s="129" t="n"/>
-      <c r="I93" s="129" t="n"/>
-      <c r="J93" s="129" t="n"/>
-      <c r="K93" s="129" t="n"/>
-      <c r="L93" s="129" t="n"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="125" t="n"/>
-      <c r="B94" s="125" t="n"/>
-      <c r="C94" s="125" t="n"/>
-      <c r="D94" s="126" t="n"/>
-      <c r="E94" s="125" t="n"/>
-      <c r="F94" s="134" t="n"/>
-      <c r="G94" s="125" t="n"/>
-      <c r="H94" s="125" t="n"/>
-      <c r="I94" s="125" t="n"/>
-      <c r="J94" s="125" t="n"/>
-      <c r="K94" s="125" t="n"/>
-      <c r="L94" s="125" t="n"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="129" t="n"/>
-      <c r="B95" s="129" t="n"/>
-      <c r="C95" s="129" t="n"/>
-      <c r="D95" s="130" t="n"/>
-      <c r="E95" s="129" t="n"/>
-      <c r="F95" s="134" t="n"/>
-      <c r="G95" s="129" t="n"/>
-      <c r="H95" s="129" t="n"/>
-      <c r="I95" s="129" t="n"/>
-      <c r="J95" s="129" t="n"/>
-      <c r="K95" s="129" t="n"/>
-      <c r="L95" s="129" t="n"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="125" t="n"/>
-      <c r="B96" s="125" t="n"/>
-      <c r="C96" s="125" t="n"/>
-      <c r="D96" s="126" t="n"/>
-      <c r="E96" s="125" t="n"/>
-      <c r="F96" s="134" t="n"/>
-      <c r="G96" s="125" t="n"/>
-      <c r="H96" s="125" t="n"/>
-      <c r="I96" s="125" t="n"/>
-      <c r="J96" s="125" t="n"/>
-      <c r="K96" s="125" t="n"/>
-      <c r="L96" s="125" t="n"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="129" t="n"/>
-      <c r="B97" s="129" t="n"/>
-      <c r="C97" s="129" t="n"/>
-      <c r="D97" s="130" t="n"/>
-      <c r="E97" s="129" t="n"/>
-      <c r="F97" s="134" t="n"/>
-      <c r="G97" s="129" t="n"/>
-      <c r="H97" s="129" t="n"/>
-      <c r="I97" s="129" t="n"/>
-      <c r="J97" s="129" t="n"/>
-      <c r="K97" s="129" t="n"/>
-      <c r="L97" s="129" t="n"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="125" t="n"/>
-      <c r="B98" s="125" t="n"/>
-      <c r="C98" s="125" t="n"/>
-      <c r="D98" s="126" t="n"/>
-      <c r="E98" s="125" t="n"/>
-      <c r="F98" s="134" t="n"/>
-      <c r="G98" s="125" t="n"/>
-      <c r="H98" s="125" t="n"/>
-      <c r="I98" s="125" t="n"/>
-      <c r="J98" s="125" t="n"/>
-      <c r="K98" s="125" t="n"/>
-      <c r="L98" s="125" t="n"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="129" t="n"/>
-      <c r="B99" s="129" t="n"/>
-      <c r="C99" s="129" t="n"/>
-      <c r="D99" s="130" t="n"/>
-      <c r="E99" s="129" t="n"/>
-      <c r="F99" s="134" t="n"/>
-      <c r="G99" s="129" t="n"/>
-      <c r="H99" s="129" t="n"/>
-      <c r="I99" s="129" t="n"/>
-      <c r="J99" s="129" t="n"/>
-      <c r="K99" s="129" t="n"/>
-      <c r="L99" s="129" t="n"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="125" t="n"/>
-      <c r="B100" s="125" t="n"/>
-      <c r="C100" s="125" t="n"/>
-      <c r="D100" s="126" t="n"/>
-      <c r="E100" s="125" t="n"/>
-      <c r="F100" s="134" t="n"/>
-      <c r="G100" s="125" t="n"/>
-      <c r="H100" s="125" t="n"/>
-      <c r="I100" s="125" t="n"/>
-      <c r="J100" s="125" t="n"/>
-      <c r="K100" s="125" t="n"/>
-      <c r="L100" s="125" t="n"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="129" t="n"/>
-      <c r="B101" s="129" t="n"/>
-      <c r="C101" s="129" t="n"/>
-      <c r="D101" s="130" t="n"/>
-      <c r="E101" s="129" t="n"/>
-      <c r="F101" s="134" t="n"/>
-      <c r="G101" s="129" t="n"/>
-      <c r="H101" s="129" t="n"/>
-      <c r="I101" s="129" t="n"/>
-      <c r="J101" s="129" t="n"/>
-      <c r="K101" s="129" t="n"/>
-      <c r="L101" s="129" t="n"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="125" t="n"/>
-      <c r="B102" s="125" t="n"/>
-      <c r="C102" s="125" t="n"/>
-      <c r="D102" s="126" t="n"/>
-      <c r="E102" s="125" t="n"/>
-      <c r="F102" s="134" t="n"/>
-      <c r="G102" s="125" t="n"/>
-      <c r="H102" s="125" t="n"/>
-      <c r="I102" s="125" t="n"/>
-      <c r="J102" s="125" t="n"/>
-      <c r="K102" s="125" t="n"/>
-      <c r="L102" s="125" t="n"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="129" t="n"/>
-      <c r="B103" s="129" t="n"/>
-      <c r="C103" s="129" t="n"/>
-      <c r="D103" s="130" t="n"/>
-      <c r="E103" s="129" t="n"/>
-      <c r="F103" s="134" t="n"/>
-      <c r="G103" s="129" t="n"/>
-      <c r="H103" s="129" t="n"/>
-      <c r="I103" s="129" t="n"/>
-      <c r="J103" s="129" t="n"/>
-      <c r="K103" s="129" t="n"/>
-      <c r="L103" s="129" t="n"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="125" t="n"/>
-      <c r="B104" s="125" t="n"/>
-      <c r="C104" s="125" t="n"/>
-      <c r="D104" s="126" t="n"/>
-      <c r="E104" s="125" t="n"/>
-      <c r="F104" s="134" t="n"/>
-      <c r="G104" s="125" t="n"/>
-      <c r="H104" s="125" t="n"/>
-      <c r="I104" s="125" t="n"/>
-      <c r="J104" s="125" t="n"/>
-      <c r="K104" s="125" t="n"/>
-      <c r="L104" s="125" t="n"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="129" t="n"/>
-      <c r="B105" s="129" t="n"/>
-      <c r="C105" s="129" t="n"/>
-      <c r="D105" s="130" t="n"/>
-      <c r="E105" s="129" t="n"/>
-      <c r="F105" s="134" t="n"/>
-      <c r="G105" s="129" t="n"/>
-      <c r="H105" s="129" t="n"/>
-      <c r="I105" s="129" t="n"/>
-      <c r="J105" s="129" t="n"/>
-      <c r="K105" s="129" t="n"/>
-      <c r="L105" s="129" t="n"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="125" t="n"/>
-      <c r="B106" s="125" t="n"/>
-      <c r="C106" s="125" t="n"/>
-      <c r="D106" s="126" t="n"/>
-      <c r="E106" s="125" t="n"/>
-      <c r="F106" s="134" t="n"/>
-      <c r="G106" s="125" t="n"/>
-      <c r="H106" s="125" t="n"/>
-      <c r="I106" s="125" t="n"/>
-      <c r="J106" s="125" t="n"/>
-      <c r="K106" s="125" t="n"/>
-      <c r="L106" s="125" t="n"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="129" t="n"/>
-      <c r="B107" s="129" t="n"/>
-      <c r="C107" s="129" t="n"/>
-      <c r="D107" s="130" t="n"/>
-      <c r="E107" s="129" t="n"/>
-      <c r="F107" s="134" t="n"/>
-      <c r="G107" s="129" t="n"/>
-      <c r="H107" s="129" t="n"/>
-      <c r="I107" s="129" t="n"/>
-      <c r="J107" s="129" t="n"/>
-      <c r="K107" s="129" t="n"/>
-      <c r="L107" s="129" t="n"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="125" t="n"/>
-      <c r="B108" s="125" t="n"/>
-      <c r="C108" s="125" t="n"/>
-      <c r="D108" s="126" t="n"/>
-      <c r="E108" s="125" t="n"/>
-      <c r="F108" s="134" t="n"/>
-      <c r="G108" s="125" t="n"/>
-      <c r="H108" s="125" t="n"/>
-      <c r="I108" s="125" t="n"/>
-      <c r="J108" s="125" t="n"/>
-      <c r="K108" s="125" t="n"/>
-      <c r="L108" s="125" t="n"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="129" t="n"/>
-      <c r="B109" s="129" t="n"/>
-      <c r="C109" s="129" t="n"/>
-      <c r="D109" s="130" t="n"/>
-      <c r="E109" s="129" t="n"/>
-      <c r="F109" s="134" t="n"/>
-      <c r="G109" s="129" t="n"/>
-      <c r="H109" s="129" t="n"/>
-      <c r="I109" s="129" t="n"/>
-      <c r="J109" s="129" t="n"/>
-      <c r="K109" s="129" t="n"/>
-      <c r="L109" s="129" t="n"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="125" t="n"/>
-      <c r="B110" s="125" t="n"/>
-      <c r="C110" s="125" t="n"/>
-      <c r="D110" s="126" t="n"/>
-      <c r="E110" s="125" t="n"/>
-      <c r="F110" s="134" t="n"/>
-      <c r="G110" s="125" t="n"/>
-      <c r="H110" s="125" t="n"/>
-      <c r="I110" s="125" t="n"/>
-      <c r="J110" s="125" t="n"/>
-      <c r="K110" s="125" t="n"/>
-      <c r="L110" s="125" t="n"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="129" t="n"/>
-      <c r="B111" s="129" t="n"/>
-      <c r="C111" s="129" t="n"/>
-      <c r="D111" s="130" t="n"/>
-      <c r="E111" s="129" t="n"/>
-      <c r="F111" s="134" t="n"/>
-      <c r="G111" s="129" t="n"/>
-      <c r="H111" s="129" t="n"/>
-      <c r="I111" s="129" t="n"/>
-      <c r="J111" s="129" t="n"/>
-      <c r="K111" s="129" t="n"/>
-      <c r="L111" s="129" t="n"/>
-    </row>
-    <row r="112">
-      <c r="A112" s="125" t="n"/>
-      <c r="B112" s="125" t="n"/>
-      <c r="C112" s="125" t="n"/>
-      <c r="D112" s="126" t="n"/>
-      <c r="E112" s="125" t="n"/>
-      <c r="F112" s="134" t="n"/>
-      <c r="G112" s="125" t="n"/>
-      <c r="H112" s="125" t="n"/>
-      <c r="I112" s="125" t="n"/>
-      <c r="J112" s="125" t="n"/>
-      <c r="K112" s="125" t="n"/>
-      <c r="L112" s="125" t="n"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="129" t="n"/>
-      <c r="B113" s="129" t="n"/>
-      <c r="C113" s="129" t="n"/>
-      <c r="D113" s="130" t="n"/>
-      <c r="E113" s="129" t="n"/>
-      <c r="F113" s="134" t="n"/>
-      <c r="G113" s="129" t="n"/>
-      <c r="H113" s="129" t="n"/>
-      <c r="I113" s="129" t="n"/>
-      <c r="J113" s="129" t="n"/>
-      <c r="K113" s="129" t="n"/>
-      <c r="L113" s="129" t="n"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="125" t="n"/>
-      <c r="B114" s="125" t="n"/>
-      <c r="C114" s="125" t="n"/>
-      <c r="D114" s="126" t="n"/>
-      <c r="E114" s="125" t="n"/>
-      <c r="F114" s="134" t="n"/>
-      <c r="G114" s="125" t="n"/>
-      <c r="H114" s="125" t="n"/>
-      <c r="I114" s="125" t="n"/>
-      <c r="J114" s="125" t="n"/>
-      <c r="K114" s="125" t="n"/>
-      <c r="L114" s="125" t="n"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="129" t="n"/>
-      <c r="B115" s="129" t="n"/>
-      <c r="C115" s="129" t="n"/>
-      <c r="D115" s="130" t="n"/>
-      <c r="E115" s="129" t="n"/>
-      <c r="F115" s="134" t="n"/>
-      <c r="G115" s="129" t="n"/>
-      <c r="H115" s="129" t="n"/>
-      <c r="I115" s="129" t="n"/>
-      <c r="J115" s="129" t="n"/>
-      <c r="K115" s="129" t="n"/>
-      <c r="L115" s="129" t="n"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="125" t="n"/>
-      <c r="B116" s="125" t="n"/>
-      <c r="C116" s="125" t="n"/>
-      <c r="D116" s="126" t="n"/>
-      <c r="E116" s="125" t="n"/>
-      <c r="F116" s="134" t="n"/>
-      <c r="G116" s="125" t="n"/>
-      <c r="H116" s="125" t="n"/>
-      <c r="I116" s="125" t="n"/>
-      <c r="J116" s="125" t="n"/>
-      <c r="K116" s="125" t="n"/>
-      <c r="L116" s="125" t="n"/>
-    </row>
-    <row r="117">
-      <c r="A117" s="129" t="n"/>
-      <c r="B117" s="129" t="n"/>
-      <c r="C117" s="129" t="n"/>
-      <c r="D117" s="130" t="n"/>
-      <c r="E117" s="129" t="n"/>
-      <c r="F117" s="134" t="n"/>
-      <c r="G117" s="129" t="n"/>
-      <c r="H117" s="129" t="n"/>
-      <c r="I117" s="129" t="n"/>
-      <c r="J117" s="129" t="n"/>
-      <c r="K117" s="129" t="n"/>
-      <c r="L117" s="129" t="n"/>
-    </row>
-    <row r="118">
-      <c r="A118" s="125" t="n"/>
-      <c r="B118" s="125" t="n"/>
-      <c r="C118" s="125" t="n"/>
-      <c r="D118" s="126" t="n"/>
-      <c r="E118" s="125" t="n"/>
-      <c r="F118" s="134" t="n"/>
-      <c r="G118" s="125" t="n"/>
-      <c r="H118" s="125" t="n"/>
-      <c r="I118" s="125" t="n"/>
-      <c r="J118" s="125" t="n"/>
-      <c r="K118" s="125" t="n"/>
-      <c r="L118" s="125" t="n"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="129" t="n"/>
-      <c r="B119" s="129" t="n"/>
-      <c r="C119" s="129" t="n"/>
-      <c r="D119" s="130" t="n"/>
-      <c r="E119" s="129" t="n"/>
-      <c r="F119" s="134" t="n"/>
-      <c r="G119" s="129" t="n"/>
-      <c r="H119" s="129" t="n"/>
-      <c r="I119" s="129" t="n"/>
-      <c r="J119" s="129" t="n"/>
-      <c r="K119" s="129" t="n"/>
-      <c r="L119" s="129" t="n"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="125" t="n"/>
-      <c r="B120" s="125" t="n"/>
-      <c r="C120" s="125" t="n"/>
-      <c r="D120" s="126" t="n"/>
-      <c r="E120" s="125" t="n"/>
-      <c r="F120" s="134" t="n"/>
-      <c r="G120" s="125" t="n"/>
-      <c r="H120" s="125" t="n"/>
-      <c r="I120" s="125" t="n"/>
-      <c r="J120" s="125" t="n"/>
-      <c r="K120" s="125" t="n"/>
-      <c r="L120" s="125" t="n"/>
-    </row>
-    <row r="121">
-      <c r="A121" s="129" t="n"/>
-      <c r="B121" s="129" t="n"/>
-      <c r="C121" s="129" t="n"/>
-      <c r="D121" s="130" t="n"/>
-      <c r="E121" s="129" t="n"/>
-      <c r="F121" s="134" t="n"/>
-      <c r="G121" s="129" t="n"/>
-      <c r="H121" s="129" t="n"/>
-      <c r="I121" s="129" t="n"/>
-      <c r="J121" s="129" t="n"/>
-      <c r="K121" s="129" t="n"/>
-      <c r="L121" s="129" t="n"/>
-    </row>
-    <row r="122">
-      <c r="A122" s="125" t="n"/>
-      <c r="B122" s="125" t="n"/>
-      <c r="C122" s="125" t="n"/>
-      <c r="D122" s="126" t="n"/>
-      <c r="E122" s="125" t="n"/>
-      <c r="F122" s="158" t="n"/>
-      <c r="G122" s="125" t="n"/>
-      <c r="H122" s="125" t="n"/>
-      <c r="I122" s="125" t="n"/>
-      <c r="J122" s="125" t="n"/>
-      <c r="K122" s="125" t="n"/>
-      <c r="L122" s="125" t="n"/>
-    </row>
-    <row r="123">
-      <c r="A123" s="129" t="n"/>
-      <c r="B123" s="129" t="n"/>
-      <c r="C123" s="129" t="n"/>
-      <c r="D123" s="130" t="n"/>
-      <c r="E123" s="129" t="n"/>
-      <c r="F123" s="158" t="n"/>
-      <c r="G123" s="129" t="n"/>
-      <c r="H123" s="129" t="n"/>
-      <c r="I123" s="129" t="n"/>
-      <c r="J123" s="129" t="n"/>
-      <c r="K123" s="129" t="n"/>
-      <c r="L123" s="129" t="n"/>
-    </row>
-    <row r="124">
-      <c r="A124" s="125" t="n"/>
-      <c r="B124" s="125" t="n"/>
-      <c r="C124" s="125" t="n"/>
-      <c r="D124" s="126" t="n"/>
-      <c r="E124" s="125" t="n"/>
-      <c r="F124" s="158" t="n"/>
-      <c r="G124" s="125" t="n"/>
-      <c r="H124" s="125" t="n"/>
-      <c r="I124" s="125" t="n"/>
-      <c r="J124" s="125" t="n"/>
-      <c r="K124" s="125" t="n"/>
-      <c r="L124" s="125" t="n"/>
-    </row>
-    <row r="125">
-      <c r="A125" s="129" t="n"/>
-      <c r="B125" s="129" t="n"/>
-      <c r="C125" s="129" t="n"/>
-      <c r="D125" s="130" t="n"/>
-      <c r="E125" s="129" t="n"/>
-      <c r="F125" s="134" t="n"/>
-      <c r="G125" s="129" t="n"/>
-      <c r="H125" s="129" t="n"/>
-      <c r="I125" s="129" t="n"/>
-      <c r="J125" s="129" t="n"/>
-      <c r="K125" s="129" t="n"/>
-      <c r="L125" s="129" t="n"/>
-    </row>
-    <row r="126">
-      <c r="A126" s="125" t="n"/>
-      <c r="B126" s="125" t="n"/>
-      <c r="C126" s="125" t="n"/>
-      <c r="D126" s="126" t="n"/>
-      <c r="E126" s="125" t="n"/>
-      <c r="F126" s="134" t="n"/>
-      <c r="G126" s="125" t="n"/>
-      <c r="H126" s="125" t="n"/>
-      <c r="I126" s="125" t="n"/>
-      <c r="J126" s="125" t="n"/>
-      <c r="K126" s="125" t="n"/>
-      <c r="L126" s="125" t="n"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="129" t="n"/>
-      <c r="B127" s="129" t="n"/>
-      <c r="C127" s="129" t="n"/>
-      <c r="D127" s="130" t="n"/>
-      <c r="E127" s="129" t="n"/>
-      <c r="F127" s="134" t="n"/>
-      <c r="G127" s="129" t="n"/>
-      <c r="H127" s="129" t="n"/>
-      <c r="I127" s="129" t="n"/>
-      <c r="J127" s="129" t="n"/>
-      <c r="K127" s="129" t="n"/>
-      <c r="L127" s="129" t="n"/>
-    </row>
-    <row r="128">
-      <c r="A128" s="125" t="n"/>
-      <c r="B128" s="125" t="n"/>
-      <c r="C128" s="125" t="n"/>
-      <c r="D128" s="126" t="n"/>
-      <c r="E128" s="125" t="n"/>
-      <c r="F128" s="134" t="n"/>
-      <c r="G128" s="125" t="n"/>
-      <c r="H128" s="125" t="n"/>
-      <c r="I128" s="125" t="n"/>
-      <c r="J128" s="125" t="n"/>
-      <c r="K128" s="125" t="n"/>
-      <c r="L128" s="125" t="n"/>
-    </row>
-    <row r="129">
-      <c r="A129" s="129" t="n"/>
-      <c r="B129" s="129" t="n"/>
-      <c r="C129" s="129" t="n"/>
-      <c r="D129" s="130" t="n"/>
-      <c r="E129" s="129" t="n"/>
-      <c r="F129" s="134" t="n"/>
-      <c r="G129" s="129" t="n"/>
-      <c r="H129" s="129" t="n"/>
-      <c r="I129" s="129" t="n"/>
-      <c r="J129" s="129" t="n"/>
-      <c r="K129" s="129" t="n"/>
-      <c r="L129" s="129" t="n"/>
-    </row>
-    <row r="130">
-      <c r="A130" s="125" t="n"/>
-      <c r="B130" s="125" t="n"/>
-      <c r="C130" s="125" t="n"/>
-      <c r="D130" s="126" t="n"/>
-      <c r="E130" s="125" t="n"/>
-      <c r="F130" s="134" t="n"/>
-      <c r="G130" s="125" t="n"/>
-      <c r="H130" s="125" t="n"/>
-      <c r="I130" s="125" t="n"/>
-      <c r="J130" s="125" t="n"/>
-      <c r="K130" s="125" t="n"/>
-      <c r="L130" s="125" t="n"/>
-    </row>
-    <row r="131">
-      <c r="A131" s="129" t="n"/>
-      <c r="B131" s="129" t="n"/>
-      <c r="C131" s="129" t="n"/>
-      <c r="D131" s="130" t="n"/>
-      <c r="E131" s="129" t="n"/>
-      <c r="F131" s="134" t="n"/>
-      <c r="G131" s="129" t="n"/>
-      <c r="H131" s="129" t="n"/>
-      <c r="I131" s="129" t="n"/>
-      <c r="J131" s="129" t="n"/>
-      <c r="K131" s="129" t="n"/>
-      <c r="L131" s="129" t="n"/>
-    </row>
-    <row r="132">
-      <c r="A132" s="125" t="n"/>
-      <c r="B132" s="125" t="n"/>
-      <c r="C132" s="125" t="n"/>
-      <c r="D132" s="126" t="n"/>
-      <c r="E132" s="125" t="n"/>
-      <c r="F132" s="134" t="n"/>
-      <c r="G132" s="125" t="n"/>
-      <c r="H132" s="125" t="n"/>
-      <c r="I132" s="125" t="n"/>
-      <c r="J132" s="125" t="n"/>
-      <c r="K132" s="125" t="n"/>
-      <c r="L132" s="125" t="n"/>
-    </row>
-    <row r="133">
-      <c r="A133" s="129" t="n"/>
-      <c r="B133" s="129" t="n"/>
-      <c r="C133" s="129" t="n"/>
-      <c r="D133" s="130" t="n"/>
-      <c r="E133" s="129" t="n"/>
-      <c r="F133" s="134" t="n"/>
-      <c r="G133" s="129" t="n"/>
-      <c r="H133" s="129" t="n"/>
-      <c r="I133" s="129" t="n"/>
-      <c r="J133" s="129" t="n"/>
-      <c r="K133" s="129" t="n"/>
-      <c r="L133" s="129" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A32:M32"/>
-    <mergeCell ref="A2:M2"/>
-    <mergeCell ref="A1:M1"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink ref="A1" location="'Start Here'!A1" display="🏠 Start Here"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:M133"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" style="230" min="1" max="1"/>
-    <col width="36" customWidth="1" style="230" min="2" max="2"/>
-    <col width="16" customWidth="1" style="230" min="3" max="3"/>
-    <col width="10" customWidth="1" style="230" min="4" max="4"/>
-    <col width="9" customWidth="1" style="230" min="5" max="5"/>
-    <col width="28" customWidth="1" style="230" min="6" max="6"/>
-    <col width="7" customWidth="1" style="230" min="7" max="7"/>
-    <col width="9" customWidth="1" style="230" min="8" max="8"/>
-    <col width="10" customWidth="1" style="230" min="9" max="9"/>
-    <col width="9" customWidth="1" style="230" min="10" max="10"/>
-    <col width="14" customWidth="1" style="230" min="11" max="11"/>
-    <col width="22" customWidth="1" style="230" min="12" max="12"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1" s="230">
-      <c r="A1" s="229" t="inlineStr">
-        <is>
-          <t>🏠 Start Here</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="283" t="inlineStr">
-        <is>
-          <t>Scored by player tier + auto/patch/print run/PSA/price/watchers | Today: May 03, 2026 | 1643 total Baseball cards in inventory</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="169" t="inlineStr">
-        <is>
-          <t>PRIORITY ACTIONS</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1" s="230">
-      <c r="A4" s="133" t="inlineStr">
-        <is>
-          <t>Rank</t>
-        </is>
-      </c>
-      <c r="B4" s="133" t="inlineStr">
-        <is>
-          <t>Priority Action</t>
-        </is>
-      </c>
-      <c r="C4" s="133" t="inlineStr">
-        <is>
-          <t>Card Description</t>
-        </is>
-      </c>
-      <c r="D4" s="133" t="inlineStr">
-        <is>
-          <t>SKU</t>
-        </is>
-      </c>
-      <c r="E4" s="133" t="inlineStr">
-        <is>
-          <t>Price ($)</t>
-        </is>
-      </c>
-      <c r="F4" s="133" t="inlineStr">
-        <is>
-          <t>Score</t>
-        </is>
-      </c>
-      <c r="G4" s="133" t="inlineStr">
-        <is>
-          <t>Player Tier</t>
-        </is>
-      </c>
-      <c r="H4" s="133" t="inlineStr">
-        <is>
-          <t>Days Listed</t>
-        </is>
-      </c>
-      <c r="I4" s="133" t="inlineStr">
-        <is>
-          <t>Aging Status</t>
-        </is>
-      </c>
-      <c r="J4" s="133" t="inlineStr">
-        <is>
-          <t>Watchers</t>
-        </is>
-      </c>
-      <c r="K4" s="133" t="inlineStr">
-        <is>
-          <t>Has 90d Sales?</t>
-        </is>
-      </c>
-      <c r="L4" s="133" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="125" t="n"/>
-      <c r="B5" s="125" t="n"/>
-      <c r="C5" s="125" t="n"/>
-      <c r="D5" s="125" t="n"/>
-      <c r="E5" s="126" t="n"/>
-      <c r="F5" s="125" t="n"/>
-      <c r="G5" s="125" t="n"/>
-      <c r="H5" s="125" t="n"/>
-      <c r="I5" s="125" t="n"/>
-      <c r="J5" s="125" t="n"/>
-      <c r="K5" s="125" t="n"/>
-      <c r="L5" s="125" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="125" t="n"/>
-      <c r="B6" s="125" t="n"/>
-      <c r="C6" s="125" t="n"/>
-      <c r="D6" s="125" t="n"/>
-      <c r="E6" s="126" t="n"/>
-      <c r="F6" s="125" t="n"/>
-      <c r="G6" s="125" t="n"/>
-      <c r="H6" s="125" t="n"/>
-      <c r="I6" s="171" t="n"/>
-      <c r="J6" s="125" t="n"/>
-      <c r="K6" s="125" t="n"/>
-      <c r="L6" s="125" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="125" t="n"/>
-      <c r="B7" s="125" t="n"/>
-      <c r="C7" s="125" t="n"/>
-      <c r="D7" s="125" t="n"/>
-      <c r="E7" s="126" t="n"/>
-      <c r="F7" s="125" t="n"/>
-      <c r="G7" s="125" t="n"/>
-      <c r="H7" s="125" t="n"/>
-      <c r="I7" s="125" t="n"/>
-      <c r="J7" s="125" t="n"/>
-      <c r="K7" s="125" t="n"/>
-      <c r="L7" s="125" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="125" t="n"/>
-      <c r="B8" s="125" t="n"/>
-      <c r="C8" s="125" t="n"/>
-      <c r="D8" s="125" t="n"/>
-      <c r="E8" s="126" t="n"/>
-      <c r="F8" s="125" t="n"/>
-      <c r="G8" s="125" t="n"/>
-      <c r="H8" s="125" t="n"/>
-      <c r="I8" s="125" t="n"/>
-      <c r="J8" s="125" t="n"/>
-      <c r="K8" s="125" t="n"/>
-      <c r="L8" s="125" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="125" t="n"/>
-      <c r="B9" s="125" t="n"/>
-      <c r="C9" s="125" t="n"/>
-      <c r="D9" s="125" t="n"/>
-      <c r="E9" s="126" t="n"/>
-      <c r="F9" s="125" t="n"/>
-      <c r="G9" s="125" t="n"/>
-      <c r="H9" s="125" t="n"/>
-      <c r="I9" s="171" t="n"/>
-      <c r="J9" s="125" t="n"/>
-      <c r="K9" s="125" t="n"/>
-      <c r="L9" s="125" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="125" t="n"/>
-      <c r="B10" s="125" t="n"/>
-      <c r="C10" s="125" t="n"/>
-      <c r="D10" s="125" t="n"/>
-      <c r="E10" s="126" t="n"/>
-      <c r="F10" s="125" t="n"/>
-      <c r="G10" s="125" t="n"/>
-      <c r="H10" s="125" t="n"/>
-      <c r="I10" s="125" t="n"/>
-      <c r="J10" s="125" t="n"/>
-      <c r="K10" s="125" t="n"/>
-      <c r="L10" s="125" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="125" t="n"/>
-      <c r="B11" s="125" t="n"/>
-      <c r="C11" s="125" t="n"/>
-      <c r="D11" s="125" t="n"/>
-      <c r="E11" s="126" t="n"/>
-      <c r="F11" s="125" t="n"/>
-      <c r="G11" s="125" t="n"/>
-      <c r="H11" s="125" t="n"/>
-      <c r="I11" s="171" t="n"/>
-      <c r="J11" s="125" t="n"/>
-      <c r="K11" s="125" t="n"/>
-      <c r="L11" s="125" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="125" t="n"/>
-      <c r="B12" s="125" t="n"/>
-      <c r="C12" s="125" t="n"/>
-      <c r="D12" s="125" t="n"/>
-      <c r="E12" s="126" t="n"/>
-      <c r="F12" s="125" t="n"/>
-      <c r="G12" s="125" t="n"/>
-      <c r="H12" s="125" t="n"/>
-      <c r="I12" s="125" t="n"/>
-      <c r="J12" s="125" t="n"/>
-      <c r="K12" s="125" t="n"/>
-      <c r="L12" s="125" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="125" t="n"/>
-      <c r="B13" s="125" t="n"/>
-      <c r="C13" s="125" t="n"/>
-      <c r="D13" s="125" t="n"/>
-      <c r="E13" s="126" t="n"/>
-      <c r="F13" s="125" t="n"/>
-      <c r="G13" s="125" t="n"/>
-      <c r="H13" s="125" t="n"/>
-      <c r="I13" s="171" t="n"/>
-      <c r="J13" s="125" t="n"/>
-      <c r="K13" s="125" t="n"/>
-      <c r="L13" s="125" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="125" t="n"/>
-      <c r="B14" s="125" t="n"/>
-      <c r="C14" s="125" t="n"/>
-      <c r="D14" s="125" t="n"/>
-      <c r="E14" s="126" t="n"/>
-      <c r="F14" s="125" t="n"/>
-      <c r="G14" s="125" t="n"/>
-      <c r="H14" s="125" t="n"/>
-      <c r="I14" s="125" t="n"/>
-      <c r="J14" s="125" t="n"/>
-      <c r="K14" s="125" t="n"/>
-      <c r="L14" s="125" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="125" t="n"/>
-      <c r="B15" s="125" t="n"/>
-      <c r="C15" s="125" t="n"/>
-      <c r="D15" s="125" t="n"/>
-      <c r="E15" s="126" t="n"/>
-      <c r="F15" s="125" t="n"/>
-      <c r="G15" s="125" t="n"/>
-      <c r="H15" s="125" t="n"/>
-      <c r="I15" s="171" t="n"/>
-      <c r="J15" s="125" t="n"/>
-      <c r="K15" s="125" t="n"/>
-      <c r="L15" s="125" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="125" t="n"/>
-      <c r="B16" s="125" t="n"/>
-      <c r="C16" s="125" t="n"/>
-      <c r="D16" s="125" t="n"/>
-      <c r="E16" s="126" t="n"/>
-      <c r="F16" s="125" t="n"/>
-      <c r="G16" s="125" t="n"/>
-      <c r="H16" s="125" t="n"/>
-      <c r="I16" s="171" t="n"/>
-      <c r="J16" s="125" t="n"/>
-      <c r="K16" s="125" t="n"/>
-      <c r="L16" s="125" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="125" t="n"/>
-      <c r="B17" s="125" t="n"/>
-      <c r="C17" s="125" t="n"/>
-      <c r="D17" s="125" t="n"/>
-      <c r="E17" s="126" t="n"/>
-      <c r="F17" s="125" t="n"/>
-      <c r="G17" s="125" t="n"/>
-      <c r="H17" s="125" t="n"/>
-      <c r="I17" s="171" t="n"/>
-      <c r="J17" s="125" t="n"/>
-      <c r="K17" s="125" t="n"/>
-      <c r="L17" s="125" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="125" t="n"/>
-      <c r="B18" s="125" t="n"/>
-      <c r="C18" s="125" t="n"/>
-      <c r="D18" s="125" t="n"/>
-      <c r="E18" s="126" t="n"/>
-      <c r="F18" s="125" t="n"/>
-      <c r="G18" s="125" t="n"/>
-      <c r="H18" s="125" t="n"/>
-      <c r="I18" s="125" t="n"/>
-      <c r="J18" s="125" t="n"/>
-      <c r="K18" s="125" t="n"/>
-      <c r="L18" s="125" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="125" t="n"/>
-      <c r="B19" s="125" t="n"/>
-      <c r="C19" s="125" t="n"/>
-      <c r="D19" s="125" t="n"/>
-      <c r="E19" s="126" t="n"/>
-      <c r="F19" s="125" t="n"/>
-      <c r="G19" s="125" t="n"/>
-      <c r="H19" s="125" t="n"/>
-      <c r="I19" s="171" t="n"/>
-      <c r="J19" s="125" t="n"/>
-      <c r="K19" s="125" t="n"/>
-      <c r="L19" s="125" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="125" t="n"/>
-      <c r="B20" s="125" t="n"/>
-      <c r="C20" s="125" t="n"/>
-      <c r="D20" s="125" t="n"/>
-      <c r="E20" s="126" t="n"/>
-      <c r="F20" s="125" t="n"/>
-      <c r="G20" s="125" t="n"/>
-      <c r="H20" s="125" t="n"/>
-      <c r="I20" s="171" t="n"/>
-      <c r="J20" s="125" t="n"/>
-      <c r="K20" s="125" t="n"/>
-      <c r="L20" s="125" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="125" t="n"/>
-      <c r="B21" s="125" t="n"/>
-      <c r="C21" s="125" t="n"/>
-      <c r="D21" s="125" t="n"/>
-      <c r="E21" s="126" t="n"/>
-      <c r="F21" s="125" t="n"/>
-      <c r="G21" s="125" t="n"/>
-      <c r="H21" s="125" t="n"/>
-      <c r="I21" s="171" t="n"/>
-      <c r="J21" s="125" t="n"/>
-      <c r="K21" s="125" t="n"/>
-      <c r="L21" s="125" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="125" t="n"/>
-      <c r="B22" s="125" t="n"/>
-      <c r="C22" s="125" t="n"/>
-      <c r="D22" s="125" t="n"/>
-      <c r="E22" s="126" t="n"/>
-      <c r="F22" s="125" t="n"/>
-      <c r="G22" s="125" t="n"/>
-      <c r="H22" s="125" t="n"/>
-      <c r="I22" s="125" t="n"/>
-      <c r="J22" s="125" t="n"/>
-      <c r="K22" s="125" t="n"/>
-      <c r="L22" s="125" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="125" t="n"/>
-      <c r="B23" s="125" t="n"/>
-      <c r="C23" s="125" t="n"/>
-      <c r="D23" s="125" t="n"/>
-      <c r="E23" s="126" t="n"/>
-      <c r="F23" s="125" t="n"/>
-      <c r="G23" s="125" t="n"/>
-      <c r="H23" s="125" t="n"/>
-      <c r="I23" s="171" t="n"/>
-      <c r="J23" s="125" t="n"/>
-      <c r="K23" s="125" t="n"/>
-      <c r="L23" s="125" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="125" t="n"/>
-      <c r="B24" s="125" t="n"/>
-      <c r="C24" s="125" t="n"/>
-      <c r="D24" s="125" t="n"/>
-      <c r="E24" s="126" t="n"/>
-      <c r="F24" s="125" t="n"/>
-      <c r="G24" s="125" t="n"/>
-      <c r="H24" s="125" t="n"/>
-      <c r="I24" s="171" t="n"/>
-      <c r="J24" s="125" t="n"/>
-      <c r="K24" s="125" t="n"/>
-      <c r="L24" s="125" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="125" t="n"/>
-      <c r="B25" s="125" t="n"/>
-      <c r="C25" s="125" t="n"/>
-      <c r="D25" s="125" t="n"/>
-      <c r="E25" s="126" t="n"/>
-      <c r="F25" s="125" t="n"/>
-      <c r="G25" s="125" t="n"/>
-      <c r="H25" s="125" t="n"/>
-      <c r="I25" s="171" t="n"/>
-      <c r="J25" s="125" t="n"/>
-      <c r="K25" s="125" t="n"/>
-      <c r="L25" s="125" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="125" t="n"/>
-      <c r="B26" s="125" t="n"/>
-      <c r="C26" s="125" t="n"/>
-      <c r="D26" s="125" t="n"/>
-      <c r="E26" s="126" t="n"/>
-      <c r="F26" s="125" t="n"/>
-      <c r="G26" s="125" t="n"/>
-      <c r="H26" s="125" t="n"/>
-      <c r="I26" s="125" t="n"/>
-      <c r="J26" s="125" t="n"/>
-      <c r="K26" s="125" t="n"/>
-      <c r="L26" s="125" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="125" t="n"/>
-      <c r="B27" s="125" t="n"/>
-      <c r="C27" s="125" t="n"/>
-      <c r="D27" s="125" t="n"/>
-      <c r="E27" s="126" t="n"/>
-      <c r="F27" s="125" t="n"/>
-      <c r="G27" s="125" t="n"/>
-      <c r="H27" s="125" t="n"/>
-      <c r="I27" s="125" t="n"/>
-      <c r="J27" s="125" t="n"/>
-      <c r="K27" s="125" t="n"/>
-      <c r="L27" s="125" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="125" t="n"/>
-      <c r="B28" s="125" t="n"/>
-      <c r="C28" s="125" t="n"/>
-      <c r="D28" s="125" t="n"/>
-      <c r="E28" s="126" t="n"/>
-      <c r="F28" s="125" t="n"/>
-      <c r="G28" s="125" t="n"/>
-      <c r="H28" s="125" t="n"/>
-      <c r="I28" s="125" t="n"/>
-      <c r="J28" s="125" t="n"/>
-      <c r="K28" s="125" t="n"/>
-      <c r="L28" s="125" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="125" t="n"/>
-      <c r="B29" s="125" t="n"/>
-      <c r="C29" s="125" t="n"/>
-      <c r="D29" s="125" t="n"/>
-      <c r="E29" s="126" t="n"/>
-      <c r="F29" s="125" t="n"/>
-      <c r="G29" s="125" t="n"/>
-      <c r="H29" s="125" t="n"/>
-      <c r="I29" s="125" t="n"/>
-      <c r="J29" s="125" t="n"/>
-      <c r="K29" s="125" t="n"/>
-      <c r="L29" s="125" t="n"/>
-    </row>
-    <row r="32" ht="16" customHeight="1" s="230">
-      <c r="A32" s="282" t="n"/>
-    </row>
-    <row r="33" ht="22" customHeight="1" s="230">
-      <c r="A33" s="170" t="n"/>
-      <c r="B33" s="170" t="n"/>
-      <c r="C33" s="170" t="n"/>
-      <c r="D33" s="170" t="n"/>
-      <c r="E33" s="170" t="n"/>
-      <c r="F33" s="170" t="n"/>
-      <c r="G33" s="170" t="n"/>
-      <c r="H33" s="170" t="n"/>
-      <c r="I33" s="170" t="n"/>
-      <c r="J33" s="170" t="n"/>
-      <c r="K33" s="170" t="n"/>
-      <c r="L33" s="170" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="125" t="n"/>
-      <c r="B34" s="125" t="n"/>
-      <c r="C34" s="125" t="n"/>
-      <c r="D34" s="126" t="n"/>
-      <c r="E34" s="125" t="n"/>
-      <c r="F34" s="158" t="n"/>
-      <c r="G34" s="125" t="n"/>
-      <c r="H34" s="125" t="n"/>
-      <c r="I34" s="125" t="n"/>
-      <c r="J34" s="125" t="n"/>
-      <c r="K34" s="125" t="n"/>
-      <c r="L34" s="125" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="129" t="n"/>
-      <c r="B35" s="129" t="n"/>
-      <c r="C35" s="129" t="n"/>
-      <c r="D35" s="130" t="n"/>
-      <c r="E35" s="129" t="n"/>
-      <c r="F35" s="171" t="n"/>
-      <c r="G35" s="129" t="n"/>
-      <c r="H35" s="129" t="n"/>
-      <c r="I35" s="129" t="n"/>
-      <c r="J35" s="129" t="n"/>
-      <c r="K35" s="129" t="n"/>
-      <c r="L35" s="129" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="125" t="n"/>
-      <c r="B36" s="125" t="n"/>
-      <c r="C36" s="125" t="n"/>
-      <c r="D36" s="126" t="n"/>
-      <c r="E36" s="125" t="n"/>
-      <c r="F36" s="158" t="n"/>
-      <c r="G36" s="125" t="n"/>
-      <c r="H36" s="125" t="n"/>
-      <c r="I36" s="125" t="n"/>
-      <c r="J36" s="125" t="n"/>
-      <c r="K36" s="125" t="n"/>
-      <c r="L36" s="125" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="129" t="n"/>
-      <c r="B37" s="129" t="n"/>
-      <c r="C37" s="129" t="n"/>
-      <c r="D37" s="130" t="n"/>
-      <c r="E37" s="129" t="n"/>
-      <c r="F37" s="158" t="n"/>
-      <c r="G37" s="129" t="n"/>
-      <c r="H37" s="129" t="n"/>
-      <c r="I37" s="129" t="n"/>
-      <c r="J37" s="129" t="n"/>
-      <c r="K37" s="129" t="n"/>
-      <c r="L37" s="129" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="125" t="n"/>
-      <c r="B38" s="125" t="n"/>
-      <c r="C38" s="125" t="n"/>
-      <c r="D38" s="126" t="n"/>
-      <c r="E38" s="125" t="n"/>
-      <c r="F38" s="134" t="n"/>
-      <c r="G38" s="125" t="n"/>
-      <c r="H38" s="125" t="n"/>
-      <c r="I38" s="125" t="n"/>
-      <c r="J38" s="125" t="n"/>
-      <c r="K38" s="125" t="n"/>
-      <c r="L38" s="125" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="129" t="n"/>
-      <c r="B39" s="129" t="n"/>
-      <c r="C39" s="129" t="n"/>
-      <c r="D39" s="130" t="n"/>
-      <c r="E39" s="129" t="n"/>
-      <c r="F39" s="158" t="n"/>
-      <c r="G39" s="129" t="n"/>
-      <c r="H39" s="129" t="n"/>
-      <c r="I39" s="129" t="n"/>
-      <c r="J39" s="129" t="n"/>
-      <c r="K39" s="129" t="n"/>
-      <c r="L39" s="129" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="125" t="n"/>
-      <c r="B40" s="125" t="n"/>
-      <c r="C40" s="125" t="n"/>
-      <c r="D40" s="126" t="n"/>
-      <c r="E40" s="125" t="n"/>
-      <c r="F40" s="134" t="n"/>
-      <c r="G40" s="125" t="n"/>
-      <c r="H40" s="125" t="n"/>
-      <c r="I40" s="125" t="n"/>
-      <c r="J40" s="125" t="n"/>
-      <c r="K40" s="125" t="n"/>
-      <c r="L40" s="125" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="129" t="n"/>
-      <c r="B41" s="129" t="n"/>
-      <c r="C41" s="129" t="n"/>
-      <c r="D41" s="130" t="n"/>
-      <c r="E41" s="129" t="n"/>
-      <c r="F41" s="158" t="n"/>
-      <c r="G41" s="129" t="n"/>
-      <c r="H41" s="129" t="n"/>
-      <c r="I41" s="129" t="n"/>
-      <c r="J41" s="129" t="n"/>
-      <c r="K41" s="129" t="n"/>
-      <c r="L41" s="129" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="125" t="n"/>
-      <c r="B42" s="125" t="n"/>
-      <c r="C42" s="125" t="n"/>
-      <c r="D42" s="126" t="n"/>
-      <c r="E42" s="125" t="n"/>
-      <c r="F42" s="134" t="n"/>
-      <c r="G42" s="125" t="n"/>
-      <c r="H42" s="125" t="n"/>
-      <c r="I42" s="125" t="n"/>
-      <c r="J42" s="125" t="n"/>
-      <c r="K42" s="125" t="n"/>
-      <c r="L42" s="125" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="129" t="n"/>
-      <c r="B43" s="129" t="n"/>
-      <c r="C43" s="129" t="n"/>
-      <c r="D43" s="130" t="n"/>
-      <c r="E43" s="129" t="n"/>
-      <c r="F43" s="158" t="n"/>
-      <c r="G43" s="129" t="n"/>
-      <c r="H43" s="129" t="n"/>
-      <c r="I43" s="129" t="n"/>
-      <c r="J43" s="129" t="n"/>
-      <c r="K43" s="129" t="n"/>
-      <c r="L43" s="129" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="125" t="n"/>
-      <c r="B44" s="125" t="n"/>
-      <c r="C44" s="125" t="n"/>
-      <c r="D44" s="126" t="n"/>
-      <c r="E44" s="125" t="n"/>
-      <c r="F44" s="134" t="n"/>
-      <c r="G44" s="125" t="n"/>
-      <c r="H44" s="125" t="n"/>
-      <c r="I44" s="125" t="n"/>
-      <c r="J44" s="125" t="n"/>
-      <c r="K44" s="125" t="n"/>
-      <c r="L44" s="125" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="129" t="n"/>
-      <c r="B45" s="129" t="n"/>
-      <c r="C45" s="129" t="n"/>
-      <c r="D45" s="130" t="n"/>
-      <c r="E45" s="129" t="n"/>
-      <c r="F45" s="171" t="n"/>
-      <c r="G45" s="129" t="n"/>
-      <c r="H45" s="129" t="n"/>
-      <c r="I45" s="129" t="n"/>
-      <c r="J45" s="129" t="n"/>
-      <c r="K45" s="129" t="n"/>
-      <c r="L45" s="129" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="125" t="n"/>
-      <c r="B46" s="125" t="n"/>
-      <c r="C46" s="125" t="n"/>
-      <c r="D46" s="126" t="n"/>
-      <c r="E46" s="125" t="n"/>
-      <c r="F46" s="171" t="n"/>
-      <c r="G46" s="125" t="n"/>
-      <c r="H46" s="125" t="n"/>
-      <c r="I46" s="125" t="n"/>
-      <c r="J46" s="125" t="n"/>
-      <c r="K46" s="125" t="n"/>
-      <c r="L46" s="125" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="129" t="n"/>
-      <c r="B47" s="129" t="n"/>
-      <c r="C47" s="129" t="n"/>
-      <c r="D47" s="130" t="n"/>
-      <c r="E47" s="129" t="n"/>
-      <c r="F47" s="158" t="n"/>
-      <c r="G47" s="129" t="n"/>
-      <c r="H47" s="129" t="n"/>
-      <c r="I47" s="129" t="n"/>
-      <c r="J47" s="129" t="n"/>
-      <c r="K47" s="129" t="n"/>
-      <c r="L47" s="129" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="125" t="n"/>
-      <c r="B48" s="125" t="n"/>
-      <c r="C48" s="125" t="n"/>
-      <c r="D48" s="126" t="n"/>
-      <c r="E48" s="125" t="n"/>
-      <c r="F48" s="134" t="n"/>
-      <c r="G48" s="125" t="n"/>
-      <c r="H48" s="125" t="n"/>
-      <c r="I48" s="125" t="n"/>
-      <c r="J48" s="125" t="n"/>
-      <c r="K48" s="125" t="n"/>
-      <c r="L48" s="125" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="129" t="n"/>
-      <c r="B49" s="129" t="n"/>
-      <c r="C49" s="129" t="n"/>
-      <c r="D49" s="130" t="n"/>
-      <c r="E49" s="129" t="n"/>
-      <c r="F49" s="134" t="n"/>
-      <c r="G49" s="129" t="n"/>
-      <c r="H49" s="129" t="n"/>
-      <c r="I49" s="129" t="n"/>
-      <c r="J49" s="129" t="n"/>
-      <c r="K49" s="129" t="n"/>
-      <c r="L49" s="129" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="125" t="n"/>
-      <c r="B50" s="125" t="n"/>
-      <c r="C50" s="125" t="n"/>
-      <c r="D50" s="126" t="n"/>
-      <c r="E50" s="125" t="n"/>
-      <c r="F50" s="134" t="n"/>
-      <c r="G50" s="125" t="n"/>
-      <c r="H50" s="125" t="n"/>
-      <c r="I50" s="125" t="n"/>
-      <c r="J50" s="125" t="n"/>
-      <c r="K50" s="125" t="n"/>
-      <c r="L50" s="125" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="129" t="n"/>
-      <c r="B51" s="129" t="n"/>
-      <c r="C51" s="129" t="n"/>
-      <c r="D51" s="130" t="n"/>
-      <c r="E51" s="129" t="n"/>
-      <c r="F51" s="158" t="n"/>
-      <c r="G51" s="129" t="n"/>
-      <c r="H51" s="129" t="n"/>
-      <c r="I51" s="129" t="n"/>
-      <c r="J51" s="129" t="n"/>
-      <c r="K51" s="129" t="n"/>
-      <c r="L51" s="129" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="125" t="n"/>
-      <c r="B52" s="125" t="n"/>
-      <c r="C52" s="125" t="n"/>
-      <c r="D52" s="126" t="n"/>
-      <c r="E52" s="125" t="n"/>
-      <c r="F52" s="134" t="n"/>
-      <c r="G52" s="125" t="n"/>
-      <c r="H52" s="125" t="n"/>
-      <c r="I52" s="125" t="n"/>
-      <c r="J52" s="125" t="n"/>
-      <c r="K52" s="125" t="n"/>
-      <c r="L52" s="125" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="129" t="n"/>
-      <c r="B53" s="129" t="n"/>
-      <c r="C53" s="129" t="n"/>
-      <c r="D53" s="130" t="n"/>
-      <c r="E53" s="129" t="n"/>
-      <c r="F53" s="171" t="n"/>
-      <c r="G53" s="129" t="n"/>
-      <c r="H53" s="129" t="n"/>
-      <c r="I53" s="129" t="n"/>
-      <c r="J53" s="129" t="n"/>
-      <c r="K53" s="129" t="n"/>
-      <c r="L53" s="129" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="125" t="n"/>
-      <c r="B54" s="125" t="n"/>
-      <c r="C54" s="125" t="n"/>
-      <c r="D54" s="126" t="n"/>
-      <c r="E54" s="125" t="n"/>
-      <c r="F54" s="171" t="n"/>
-      <c r="G54" s="125" t="n"/>
-      <c r="H54" s="125" t="n"/>
-      <c r="I54" s="125" t="n"/>
-      <c r="J54" s="125" t="n"/>
-      <c r="K54" s="125" t="n"/>
-      <c r="L54" s="125" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="129" t="n"/>
-      <c r="B55" s="129" t="n"/>
-      <c r="C55" s="129" t="n"/>
-      <c r="D55" s="130" t="n"/>
-      <c r="E55" s="129" t="n"/>
-      <c r="F55" s="158" t="n"/>
-      <c r="G55" s="129" t="n"/>
-      <c r="H55" s="129" t="n"/>
-      <c r="I55" s="129" t="n"/>
-      <c r="J55" s="129" t="n"/>
-      <c r="K55" s="129" t="n"/>
-      <c r="L55" s="129" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="125" t="n"/>
-      <c r="B56" s="125" t="n"/>
-      <c r="C56" s="125" t="n"/>
-      <c r="D56" s="126" t="n"/>
-      <c r="E56" s="125" t="n"/>
-      <c r="F56" s="158" t="n"/>
-      <c r="G56" s="125" t="n"/>
-      <c r="H56" s="125" t="n"/>
-      <c r="I56" s="125" t="n"/>
-      <c r="J56" s="125" t="n"/>
-      <c r="K56" s="125" t="n"/>
-      <c r="L56" s="125" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="129" t="n"/>
-      <c r="B57" s="129" t="n"/>
-      <c r="C57" s="129" t="n"/>
-      <c r="D57" s="130" t="n"/>
-      <c r="E57" s="129" t="n"/>
-      <c r="F57" s="158" t="n"/>
-      <c r="G57" s="129" t="n"/>
-      <c r="H57" s="129" t="n"/>
-      <c r="I57" s="129" t="n"/>
-      <c r="J57" s="129" t="n"/>
-      <c r="K57" s="129" t="n"/>
-      <c r="L57" s="129" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="125" t="n"/>
-      <c r="B58" s="125" t="n"/>
-      <c r="C58" s="125" t="n"/>
-      <c r="D58" s="126" t="n"/>
-      <c r="E58" s="125" t="n"/>
-      <c r="F58" s="158" t="n"/>
-      <c r="G58" s="125" t="n"/>
-      <c r="H58" s="125" t="n"/>
-      <c r="I58" s="125" t="n"/>
-      <c r="J58" s="125" t="n"/>
-      <c r="K58" s="125" t="n"/>
-      <c r="L58" s="125" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="129" t="n"/>
-      <c r="B59" s="129" t="n"/>
-      <c r="C59" s="129" t="n"/>
-      <c r="D59" s="130" t="n"/>
-      <c r="E59" s="129" t="n"/>
-      <c r="F59" s="134" t="n"/>
-      <c r="G59" s="129" t="n"/>
-      <c r="H59" s="129" t="n"/>
-      <c r="I59" s="129" t="n"/>
-      <c r="J59" s="129" t="n"/>
-      <c r="K59" s="129" t="n"/>
-      <c r="L59" s="129" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="125" t="n"/>
-      <c r="B60" s="125" t="n"/>
-      <c r="C60" s="125" t="n"/>
-      <c r="D60" s="126" t="n"/>
-      <c r="E60" s="125" t="n"/>
-      <c r="F60" s="171" t="n"/>
-      <c r="G60" s="125" t="n"/>
-      <c r="H60" s="125" t="n"/>
-      <c r="I60" s="125" t="n"/>
-      <c r="J60" s="125" t="n"/>
-      <c r="K60" s="125" t="n"/>
-      <c r="L60" s="125" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="129" t="n"/>
-      <c r="B61" s="129" t="n"/>
-      <c r="C61" s="129" t="n"/>
-      <c r="D61" s="130" t="n"/>
-      <c r="E61" s="129" t="n"/>
-      <c r="F61" s="158" t="n"/>
-      <c r="G61" s="129" t="n"/>
-      <c r="H61" s="129" t="n"/>
-      <c r="I61" s="129" t="n"/>
-      <c r="J61" s="129" t="n"/>
-      <c r="K61" s="129" t="n"/>
-      <c r="L61" s="129" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="125" t="n"/>
-      <c r="B62" s="125" t="n"/>
-      <c r="C62" s="125" t="n"/>
-      <c r="D62" s="126" t="n"/>
-      <c r="E62" s="125" t="n"/>
-      <c r="F62" s="158" t="n"/>
-      <c r="G62" s="125" t="n"/>
-      <c r="H62" s="125" t="n"/>
-      <c r="I62" s="125" t="n"/>
-      <c r="J62" s="125" t="n"/>
-      <c r="K62" s="125" t="n"/>
-      <c r="L62" s="125" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="129" t="n"/>
-      <c r="B63" s="129" t="n"/>
-      <c r="C63" s="129" t="n"/>
-      <c r="D63" s="130" t="n"/>
-      <c r="E63" s="129" t="n"/>
-      <c r="F63" s="158" t="n"/>
-      <c r="G63" s="129" t="n"/>
-      <c r="H63" s="129" t="n"/>
-      <c r="I63" s="129" t="n"/>
-      <c r="J63" s="129" t="n"/>
-      <c r="K63" s="129" t="n"/>
-      <c r="L63" s="129" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="125" t="n"/>
-      <c r="B64" s="125" t="n"/>
-      <c r="C64" s="125" t="n"/>
-      <c r="D64" s="126" t="n"/>
-      <c r="E64" s="125" t="n"/>
-      <c r="F64" s="158" t="n"/>
-      <c r="G64" s="125" t="n"/>
-      <c r="H64" s="125" t="n"/>
-      <c r="I64" s="125" t="n"/>
-      <c r="J64" s="125" t="n"/>
-      <c r="K64" s="125" t="n"/>
-      <c r="L64" s="125" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="129" t="n"/>
-      <c r="B65" s="129" t="n"/>
-      <c r="C65" s="129" t="n"/>
-      <c r="D65" s="130" t="n"/>
-      <c r="E65" s="129" t="n"/>
-      <c r="F65" s="158" t="n"/>
-      <c r="G65" s="129" t="n"/>
-      <c r="H65" s="129" t="n"/>
-      <c r="I65" s="129" t="n"/>
-      <c r="J65" s="129" t="n"/>
-      <c r="K65" s="129" t="n"/>
-      <c r="L65" s="129" t="n"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="125" t="n"/>
-      <c r="B66" s="125" t="n"/>
-      <c r="C66" s="125" t="n"/>
-      <c r="D66" s="126" t="n"/>
-      <c r="E66" s="125" t="n"/>
-      <c r="F66" s="134" t="n"/>
-      <c r="G66" s="125" t="n"/>
-      <c r="H66" s="125" t="n"/>
-      <c r="I66" s="125" t="n"/>
-      <c r="J66" s="125" t="n"/>
-      <c r="K66" s="125" t="n"/>
-      <c r="L66" s="125" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="129" t="n"/>
-      <c r="B67" s="129" t="n"/>
-      <c r="C67" s="129" t="n"/>
-      <c r="D67" s="130" t="n"/>
-      <c r="E67" s="129" t="n"/>
-      <c r="F67" s="134" t="n"/>
-      <c r="G67" s="129" t="n"/>
-      <c r="H67" s="129" t="n"/>
-      <c r="I67" s="129" t="n"/>
-      <c r="J67" s="129" t="n"/>
-      <c r="K67" s="129" t="n"/>
-      <c r="L67" s="129" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="125" t="n"/>
-      <c r="B68" s="125" t="n"/>
-      <c r="C68" s="125" t="n"/>
-      <c r="D68" s="126" t="n"/>
-      <c r="E68" s="125" t="n"/>
-      <c r="F68" s="134" t="n"/>
-      <c r="G68" s="125" t="n"/>
-      <c r="H68" s="125" t="n"/>
-      <c r="I68" s="125" t="n"/>
-      <c r="J68" s="125" t="n"/>
-      <c r="K68" s="125" t="n"/>
-      <c r="L68" s="125" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="129" t="n"/>
-      <c r="B69" s="129" t="n"/>
-      <c r="C69" s="129" t="n"/>
-      <c r="D69" s="130" t="n"/>
-      <c r="E69" s="129" t="n"/>
-      <c r="F69" s="134" t="n"/>
-      <c r="G69" s="129" t="n"/>
-      <c r="H69" s="129" t="n"/>
-      <c r="I69" s="129" t="n"/>
-      <c r="J69" s="129" t="n"/>
-      <c r="K69" s="129" t="n"/>
-      <c r="L69" s="129" t="n"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="125" t="n"/>
-      <c r="B70" s="125" t="n"/>
-      <c r="C70" s="125" t="n"/>
-      <c r="D70" s="126" t="n"/>
-      <c r="E70" s="125" t="n"/>
-      <c r="F70" s="134" t="n"/>
-      <c r="G70" s="125" t="n"/>
-      <c r="H70" s="125" t="n"/>
-      <c r="I70" s="125" t="n"/>
-      <c r="J70" s="125" t="n"/>
-      <c r="K70" s="125" t="n"/>
-      <c r="L70" s="125" t="n"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="129" t="n"/>
-      <c r="B71" s="129" t="n"/>
-      <c r="C71" s="129" t="n"/>
-      <c r="D71" s="130" t="n"/>
-      <c r="E71" s="129" t="n"/>
-      <c r="F71" s="134" t="n"/>
-      <c r="G71" s="129" t="n"/>
-      <c r="H71" s="129" t="n"/>
-      <c r="I71" s="129" t="n"/>
-      <c r="J71" s="129" t="n"/>
-      <c r="K71" s="129" t="n"/>
-      <c r="L71" s="129" t="n"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="125" t="n"/>
-      <c r="B72" s="125" t="n"/>
-      <c r="C72" s="125" t="n"/>
-      <c r="D72" s="126" t="n"/>
-      <c r="E72" s="125" t="n"/>
-      <c r="F72" s="134" t="n"/>
-      <c r="G72" s="125" t="n"/>
-      <c r="H72" s="125" t="n"/>
-      <c r="I72" s="125" t="n"/>
-      <c r="J72" s="125" t="n"/>
-      <c r="K72" s="125" t="n"/>
-      <c r="L72" s="125" t="n"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="129" t="n"/>
-      <c r="B73" s="129" t="n"/>
-      <c r="C73" s="129" t="n"/>
-      <c r="D73" s="130" t="n"/>
-      <c r="E73" s="129" t="n"/>
-      <c r="F73" s="134" t="n"/>
-      <c r="G73" s="129" t="n"/>
-      <c r="H73" s="129" t="n"/>
-      <c r="I73" s="129" t="n"/>
-      <c r="J73" s="129" t="n"/>
-      <c r="K73" s="129" t="n"/>
-      <c r="L73" s="129" t="n"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="125" t="n"/>
-      <c r="B74" s="125" t="n"/>
-      <c r="C74" s="125" t="n"/>
-      <c r="D74" s="126" t="n"/>
-      <c r="E74" s="125" t="n"/>
-      <c r="F74" s="134" t="n"/>
-      <c r="G74" s="125" t="n"/>
-      <c r="H74" s="125" t="n"/>
-      <c r="I74" s="125" t="n"/>
-      <c r="J74" s="125" t="n"/>
-      <c r="K74" s="125" t="n"/>
-      <c r="L74" s="125" t="n"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="129" t="n"/>
-      <c r="B75" s="129" t="n"/>
-      <c r="C75" s="129" t="n"/>
-      <c r="D75" s="130" t="n"/>
-      <c r="E75" s="129" t="n"/>
-      <c r="F75" s="134" t="n"/>
-      <c r="G75" s="129" t="n"/>
-      <c r="H75" s="129" t="n"/>
-      <c r="I75" s="129" t="n"/>
-      <c r="J75" s="129" t="n"/>
-      <c r="K75" s="129" t="n"/>
-      <c r="L75" s="129" t="n"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="125" t="n"/>
-      <c r="B76" s="125" t="n"/>
-      <c r="C76" s="125" t="n"/>
-      <c r="D76" s="126" t="n"/>
-      <c r="E76" s="125" t="n"/>
-      <c r="F76" s="134" t="n"/>
-      <c r="G76" s="125" t="n"/>
-      <c r="H76" s="125" t="n"/>
-      <c r="I76" s="125" t="n"/>
-      <c r="J76" s="125" t="n"/>
-      <c r="K76" s="125" t="n"/>
-      <c r="L76" s="125" t="n"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="129" t="n"/>
-      <c r="B77" s="129" t="n"/>
-      <c r="C77" s="129" t="n"/>
-      <c r="D77" s="130" t="n"/>
-      <c r="E77" s="129" t="n"/>
-      <c r="F77" s="134" t="n"/>
-      <c r="G77" s="129" t="n"/>
-      <c r="H77" s="129" t="n"/>
-      <c r="I77" s="129" t="n"/>
-      <c r="J77" s="129" t="n"/>
-      <c r="K77" s="129" t="n"/>
-      <c r="L77" s="129" t="n"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="125" t="n"/>
-      <c r="B78" s="125" t="n"/>
-      <c r="C78" s="125" t="n"/>
-      <c r="D78" s="126" t="n"/>
-      <c r="E78" s="125" t="n"/>
-      <c r="F78" s="134" t="n"/>
-      <c r="G78" s="125" t="n"/>
-      <c r="H78" s="125" t="n"/>
-      <c r="I78" s="125" t="n"/>
-      <c r="J78" s="125" t="n"/>
-      <c r="K78" s="125" t="n"/>
-      <c r="L78" s="125" t="n"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="129" t="n"/>
-      <c r="B79" s="129" t="n"/>
-      <c r="C79" s="129" t="n"/>
-      <c r="D79" s="130" t="n"/>
-      <c r="E79" s="129" t="n"/>
-      <c r="F79" s="134" t="n"/>
-      <c r="G79" s="129" t="n"/>
-      <c r="H79" s="129" t="n"/>
-      <c r="I79" s="129" t="n"/>
-      <c r="J79" s="129" t="n"/>
-      <c r="K79" s="129" t="n"/>
-      <c r="L79" s="129" t="n"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="125" t="n"/>
-      <c r="B80" s="125" t="n"/>
-      <c r="C80" s="125" t="n"/>
-      <c r="D80" s="126" t="n"/>
-      <c r="E80" s="125" t="n"/>
-      <c r="F80" s="134" t="n"/>
-      <c r="G80" s="125" t="n"/>
-      <c r="H80" s="125" t="n"/>
-      <c r="I80" s="125" t="n"/>
-      <c r="J80" s="125" t="n"/>
-      <c r="K80" s="125" t="n"/>
-      <c r="L80" s="125" t="n"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="129" t="n"/>
-      <c r="B81" s="129" t="n"/>
-      <c r="C81" s="129" t="n"/>
-      <c r="D81" s="130" t="n"/>
-      <c r="E81" s="129" t="n"/>
-      <c r="F81" s="171" t="n"/>
-      <c r="G81" s="129" t="n"/>
-      <c r="H81" s="129" t="n"/>
-      <c r="I81" s="129" t="n"/>
-      <c r="J81" s="129" t="n"/>
-      <c r="K81" s="129" t="n"/>
-      <c r="L81" s="129" t="n"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="125" t="n"/>
-      <c r="B82" s="125" t="n"/>
-      <c r="C82" s="125" t="n"/>
-      <c r="D82" s="126" t="n"/>
-      <c r="E82" s="125" t="n"/>
-      <c r="F82" s="171" t="n"/>
-      <c r="G82" s="125" t="n"/>
-      <c r="H82" s="125" t="n"/>
-      <c r="I82" s="125" t="n"/>
-      <c r="J82" s="125" t="n"/>
-      <c r="K82" s="125" t="n"/>
-      <c r="L82" s="125" t="n"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="129" t="n"/>
-      <c r="B83" s="129" t="n"/>
-      <c r="C83" s="129" t="n"/>
-      <c r="D83" s="130" t="n"/>
-      <c r="E83" s="129" t="n"/>
-      <c r="F83" s="171" t="n"/>
-      <c r="G83" s="129" t="n"/>
-      <c r="H83" s="129" t="n"/>
-      <c r="I83" s="129" t="n"/>
-      <c r="J83" s="129" t="n"/>
-      <c r="K83" s="129" t="n"/>
-      <c r="L83" s="129" t="n"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="125" t="n"/>
-      <c r="B84" s="125" t="n"/>
-      <c r="C84" s="125" t="n"/>
-      <c r="D84" s="126" t="n"/>
-      <c r="E84" s="125" t="n"/>
-      <c r="F84" s="171" t="n"/>
-      <c r="G84" s="125" t="n"/>
-      <c r="H84" s="125" t="n"/>
-      <c r="I84" s="125" t="n"/>
-      <c r="J84" s="125" t="n"/>
-      <c r="K84" s="125" t="n"/>
-      <c r="L84" s="125" t="n"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="129" t="n"/>
-      <c r="B85" s="129" t="n"/>
-      <c r="C85" s="129" t="n"/>
-      <c r="D85" s="130" t="n"/>
-      <c r="E85" s="129" t="n"/>
-      <c r="F85" s="171" t="n"/>
-      <c r="G85" s="129" t="n"/>
-      <c r="H85" s="129" t="n"/>
-      <c r="I85" s="129" t="n"/>
-      <c r="J85" s="129" t="n"/>
-      <c r="K85" s="129" t="n"/>
-      <c r="L85" s="129" t="n"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="125" t="n"/>
-      <c r="B86" s="125" t="n"/>
-      <c r="C86" s="125" t="n"/>
-      <c r="D86" s="126" t="n"/>
-      <c r="E86" s="125" t="n"/>
-      <c r="F86" s="171" t="n"/>
-      <c r="G86" s="125" t="n"/>
-      <c r="H86" s="125" t="n"/>
-      <c r="I86" s="125" t="n"/>
-      <c r="J86" s="125" t="n"/>
-      <c r="K86" s="125" t="n"/>
-      <c r="L86" s="125" t="n"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="129" t="n"/>
-      <c r="B87" s="129" t="n"/>
-      <c r="C87" s="129" t="n"/>
-      <c r="D87" s="130" t="n"/>
-      <c r="E87" s="129" t="n"/>
-      <c r="F87" s="158" t="n"/>
-      <c r="G87" s="129" t="n"/>
-      <c r="H87" s="129" t="n"/>
-      <c r="I87" s="129" t="n"/>
-      <c r="J87" s="129" t="n"/>
-      <c r="K87" s="129" t="n"/>
-      <c r="L87" s="129" t="n"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="125" t="n"/>
-      <c r="B88" s="125" t="n"/>
-      <c r="C88" s="125" t="n"/>
-      <c r="D88" s="126" t="n"/>
-      <c r="E88" s="125" t="n"/>
-      <c r="F88" s="158" t="n"/>
-      <c r="G88" s="125" t="n"/>
-      <c r="H88" s="125" t="n"/>
-      <c r="I88" s="125" t="n"/>
-      <c r="J88" s="125" t="n"/>
-      <c r="K88" s="125" t="n"/>
-      <c r="L88" s="125" t="n"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="129" t="n"/>
-      <c r="B89" s="129" t="n"/>
-      <c r="C89" s="129" t="n"/>
-      <c r="D89" s="130" t="n"/>
-      <c r="E89" s="129" t="n"/>
-      <c r="F89" s="158" t="n"/>
-      <c r="G89" s="129" t="n"/>
-      <c r="H89" s="129" t="n"/>
-      <c r="I89" s="129" t="n"/>
-      <c r="J89" s="129" t="n"/>
-      <c r="K89" s="129" t="n"/>
-      <c r="L89" s="129" t="n"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="125" t="n"/>
-      <c r="B90" s="125" t="n"/>
-      <c r="C90" s="125" t="n"/>
-      <c r="D90" s="126" t="n"/>
-      <c r="E90" s="125" t="n"/>
-      <c r="F90" s="158" t="n"/>
-      <c r="G90" s="125" t="n"/>
-      <c r="H90" s="125" t="n"/>
-      <c r="I90" s="125" t="n"/>
-      <c r="J90" s="125" t="n"/>
-      <c r="K90" s="125" t="n"/>
-      <c r="L90" s="125" t="n"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="129" t="n"/>
-      <c r="B91" s="129" t="n"/>
-      <c r="C91" s="129" t="n"/>
-      <c r="D91" s="130" t="n"/>
-      <c r="E91" s="129" t="n"/>
-      <c r="F91" s="158" t="n"/>
-      <c r="G91" s="129" t="n"/>
-      <c r="H91" s="129" t="n"/>
-      <c r="I91" s="129" t="n"/>
-      <c r="J91" s="129" t="n"/>
-      <c r="K91" s="129" t="n"/>
-      <c r="L91" s="129" t="n"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="125" t="n"/>
-      <c r="B92" s="125" t="n"/>
-      <c r="C92" s="125" t="n"/>
-      <c r="D92" s="126" t="n"/>
-      <c r="E92" s="125" t="n"/>
-      <c r="F92" s="158" t="n"/>
-      <c r="G92" s="125" t="n"/>
-      <c r="H92" s="125" t="n"/>
-      <c r="I92" s="125" t="n"/>
-      <c r="J92" s="125" t="n"/>
-      <c r="K92" s="125" t="n"/>
-      <c r="L92" s="125" t="n"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="129" t="n"/>
-      <c r="B93" s="129" t="n"/>
-      <c r="C93" s="129" t="n"/>
-      <c r="D93" s="130" t="n"/>
-      <c r="E93" s="129" t="n"/>
-      <c r="F93" s="158" t="n"/>
-      <c r="G93" s="129" t="n"/>
-      <c r="H93" s="129" t="n"/>
-      <c r="I93" s="129" t="n"/>
-      <c r="J93" s="129" t="n"/>
-      <c r="K93" s="129" t="n"/>
-      <c r="L93" s="129" t="n"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="125" t="n"/>
-      <c r="B94" s="125" t="n"/>
-      <c r="C94" s="125" t="n"/>
-      <c r="D94" s="126" t="n"/>
-      <c r="E94" s="125" t="n"/>
-      <c r="F94" s="134" t="n"/>
-      <c r="G94" s="125" t="n"/>
-      <c r="H94" s="125" t="n"/>
-      <c r="I94" s="125" t="n"/>
-      <c r="J94" s="125" t="n"/>
-      <c r="K94" s="125" t="n"/>
-      <c r="L94" s="125" t="n"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="129" t="n"/>
-      <c r="B95" s="129" t="n"/>
-      <c r="C95" s="129" t="n"/>
-      <c r="D95" s="130" t="n"/>
-      <c r="E95" s="129" t="n"/>
-      <c r="F95" s="134" t="n"/>
-      <c r="G95" s="129" t="n"/>
-      <c r="H95" s="129" t="n"/>
-      <c r="I95" s="129" t="n"/>
-      <c r="J95" s="129" t="n"/>
-      <c r="K95" s="129" t="n"/>
-      <c r="L95" s="129" t="n"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="125" t="n"/>
-      <c r="B96" s="125" t="n"/>
-      <c r="C96" s="125" t="n"/>
-      <c r="D96" s="126" t="n"/>
-      <c r="E96" s="125" t="n"/>
-      <c r="F96" s="134" t="n"/>
-      <c r="G96" s="125" t="n"/>
-      <c r="H96" s="125" t="n"/>
-      <c r="I96" s="125" t="n"/>
-      <c r="J96" s="125" t="n"/>
-      <c r="K96" s="125" t="n"/>
-      <c r="L96" s="125" t="n"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="129" t="n"/>
-      <c r="B97" s="129" t="n"/>
-      <c r="C97" s="129" t="n"/>
-      <c r="D97" s="130" t="n"/>
-      <c r="E97" s="129" t="n"/>
-      <c r="F97" s="134" t="n"/>
-      <c r="G97" s="129" t="n"/>
-      <c r="H97" s="129" t="n"/>
-      <c r="I97" s="129" t="n"/>
-      <c r="J97" s="129" t="n"/>
-      <c r="K97" s="129" t="n"/>
-      <c r="L97" s="129" t="n"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="125" t="n"/>
-      <c r="B98" s="125" t="n"/>
-      <c r="C98" s="125" t="n"/>
-      <c r="D98" s="126" t="n"/>
-      <c r="E98" s="125" t="n"/>
-      <c r="F98" s="134" t="n"/>
-      <c r="G98" s="125" t="n"/>
-      <c r="H98" s="125" t="n"/>
-      <c r="I98" s="125" t="n"/>
-      <c r="J98" s="125" t="n"/>
-      <c r="K98" s="125" t="n"/>
-      <c r="L98" s="125" t="n"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="129" t="n"/>
-      <c r="B99" s="129" t="n"/>
-      <c r="C99" s="129" t="n"/>
-      <c r="D99" s="130" t="n"/>
-      <c r="E99" s="129" t="n"/>
-      <c r="F99" s="134" t="n"/>
-      <c r="G99" s="129" t="n"/>
-      <c r="H99" s="129" t="n"/>
-      <c r="I99" s="129" t="n"/>
-      <c r="J99" s="129" t="n"/>
-      <c r="K99" s="129" t="n"/>
-      <c r="L99" s="129" t="n"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="125" t="n"/>
-      <c r="B100" s="125" t="n"/>
-      <c r="C100" s="125" t="n"/>
-      <c r="D100" s="126" t="n"/>
-      <c r="E100" s="125" t="n"/>
-      <c r="F100" s="134" t="n"/>
-      <c r="G100" s="125" t="n"/>
-      <c r="H100" s="125" t="n"/>
-      <c r="I100" s="125" t="n"/>
-      <c r="J100" s="125" t="n"/>
-      <c r="K100" s="125" t="n"/>
-      <c r="L100" s="125" t="n"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="129" t="n"/>
-      <c r="B101" s="129" t="n"/>
-      <c r="C101" s="129" t="n"/>
-      <c r="D101" s="130" t="n"/>
-      <c r="E101" s="129" t="n"/>
-      <c r="F101" s="134" t="n"/>
-      <c r="G101" s="129" t="n"/>
-      <c r="H101" s="129" t="n"/>
-      <c r="I101" s="129" t="n"/>
-      <c r="J101" s="129" t="n"/>
-      <c r="K101" s="129" t="n"/>
-      <c r="L101" s="129" t="n"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="125" t="n"/>
-      <c r="B102" s="125" t="n"/>
-      <c r="C102" s="125" t="n"/>
-      <c r="D102" s="126" t="n"/>
-      <c r="E102" s="125" t="n"/>
-      <c r="F102" s="134" t="n"/>
-      <c r="G102" s="125" t="n"/>
-      <c r="H102" s="125" t="n"/>
-      <c r="I102" s="125" t="n"/>
-      <c r="J102" s="125" t="n"/>
-      <c r="K102" s="125" t="n"/>
-      <c r="L102" s="125" t="n"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="129" t="n"/>
-      <c r="B103" s="129" t="n"/>
-      <c r="C103" s="129" t="n"/>
-      <c r="D103" s="130" t="n"/>
-      <c r="E103" s="129" t="n"/>
-      <c r="F103" s="134" t="n"/>
-      <c r="G103" s="129" t="n"/>
-      <c r="H103" s="129" t="n"/>
-      <c r="I103" s="129" t="n"/>
-      <c r="J103" s="129" t="n"/>
-      <c r="K103" s="129" t="n"/>
-      <c r="L103" s="129" t="n"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="125" t="n"/>
-      <c r="B104" s="125" t="n"/>
-      <c r="C104" s="125" t="n"/>
-      <c r="D104" s="126" t="n"/>
-      <c r="E104" s="125" t="n"/>
-      <c r="F104" s="134" t="n"/>
-      <c r="G104" s="125" t="n"/>
-      <c r="H104" s="125" t="n"/>
-      <c r="I104" s="125" t="n"/>
-      <c r="J104" s="125" t="n"/>
-      <c r="K104" s="125" t="n"/>
-      <c r="L104" s="125" t="n"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="129" t="n"/>
-      <c r="B105" s="129" t="n"/>
-      <c r="C105" s="129" t="n"/>
-      <c r="D105" s="130" t="n"/>
-      <c r="E105" s="129" t="n"/>
-      <c r="F105" s="134" t="n"/>
-      <c r="G105" s="129" t="n"/>
-      <c r="H105" s="129" t="n"/>
-      <c r="I105" s="129" t="n"/>
-      <c r="J105" s="129" t="n"/>
-      <c r="K105" s="129" t="n"/>
-      <c r="L105" s="129" t="n"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="125" t="n"/>
-      <c r="B106" s="125" t="n"/>
-      <c r="C106" s="125" t="n"/>
-      <c r="D106" s="126" t="n"/>
-      <c r="E106" s="125" t="n"/>
-      <c r="F106" s="134" t="n"/>
-      <c r="G106" s="125" t="n"/>
-      <c r="H106" s="125" t="n"/>
-      <c r="I106" s="125" t="n"/>
-      <c r="J106" s="125" t="n"/>
-      <c r="K106" s="125" t="n"/>
-      <c r="L106" s="125" t="n"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="129" t="n"/>
-      <c r="B107" s="129" t="n"/>
-      <c r="C107" s="129" t="n"/>
-      <c r="D107" s="130" t="n"/>
-      <c r="E107" s="129" t="n"/>
-      <c r="F107" s="134" t="n"/>
-      <c r="G107" s="129" t="n"/>
-      <c r="H107" s="129" t="n"/>
-      <c r="I107" s="129" t="n"/>
-      <c r="J107" s="129" t="n"/>
-      <c r="K107" s="129" t="n"/>
-      <c r="L107" s="129" t="n"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="125" t="n"/>
-      <c r="B108" s="125" t="n"/>
-      <c r="C108" s="125" t="n"/>
-      <c r="D108" s="126" t="n"/>
-      <c r="E108" s="125" t="n"/>
-      <c r="F108" s="134" t="n"/>
-      <c r="G108" s="125" t="n"/>
-      <c r="H108" s="125" t="n"/>
-      <c r="I108" s="125" t="n"/>
-      <c r="J108" s="125" t="n"/>
-      <c r="K108" s="125" t="n"/>
-      <c r="L108" s="125" t="n"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="129" t="n"/>
-      <c r="B109" s="129" t="n"/>
-      <c r="C109" s="129" t="n"/>
-      <c r="D109" s="130" t="n"/>
-      <c r="E109" s="129" t="n"/>
-      <c r="F109" s="134" t="n"/>
-      <c r="G109" s="129" t="n"/>
-      <c r="H109" s="129" t="n"/>
-      <c r="I109" s="129" t="n"/>
-      <c r="J109" s="129" t="n"/>
-      <c r="K109" s="129" t="n"/>
-      <c r="L109" s="129" t="n"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="125" t="n"/>
-      <c r="B110" s="125" t="n"/>
-      <c r="C110" s="125" t="n"/>
-      <c r="D110" s="126" t="n"/>
-      <c r="E110" s="125" t="n"/>
-      <c r="F110" s="134" t="n"/>
-      <c r="G110" s="125" t="n"/>
-      <c r="H110" s="125" t="n"/>
-      <c r="I110" s="125" t="n"/>
-      <c r="J110" s="125" t="n"/>
-      <c r="K110" s="125" t="n"/>
-      <c r="L110" s="125" t="n"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="129" t="n"/>
-      <c r="B111" s="129" t="n"/>
-      <c r="C111" s="129" t="n"/>
-      <c r="D111" s="130" t="n"/>
-      <c r="E111" s="129" t="n"/>
-      <c r="F111" s="134" t="n"/>
-      <c r="G111" s="129" t="n"/>
-      <c r="H111" s="129" t="n"/>
-      <c r="I111" s="129" t="n"/>
-      <c r="J111" s="129" t="n"/>
-      <c r="K111" s="129" t="n"/>
-      <c r="L111" s="129" t="n"/>
-    </row>
-    <row r="112">
-      <c r="A112" s="125" t="n"/>
-      <c r="B112" s="125" t="n"/>
-      <c r="C112" s="125" t="n"/>
-      <c r="D112" s="126" t="n"/>
-      <c r="E112" s="125" t="n"/>
-      <c r="F112" s="134" t="n"/>
-      <c r="G112" s="125" t="n"/>
-      <c r="H112" s="125" t="n"/>
-      <c r="I112" s="125" t="n"/>
-      <c r="J112" s="125" t="n"/>
-      <c r="K112" s="125" t="n"/>
-      <c r="L112" s="125" t="n"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="129" t="n"/>
-      <c r="B113" s="129" t="n"/>
-      <c r="C113" s="129" t="n"/>
-      <c r="D113" s="130" t="n"/>
-      <c r="E113" s="129" t="n"/>
-      <c r="F113" s="134" t="n"/>
-      <c r="G113" s="129" t="n"/>
-      <c r="H113" s="129" t="n"/>
-      <c r="I113" s="129" t="n"/>
-      <c r="J113" s="129" t="n"/>
-      <c r="K113" s="129" t="n"/>
-      <c r="L113" s="129" t="n"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="125" t="n"/>
-      <c r="B114" s="125" t="n"/>
-      <c r="C114" s="125" t="n"/>
-      <c r="D114" s="126" t="n"/>
-      <c r="E114" s="125" t="n"/>
-      <c r="F114" s="134" t="n"/>
-      <c r="G114" s="125" t="n"/>
-      <c r="H114" s="125" t="n"/>
-      <c r="I114" s="125" t="n"/>
-      <c r="J114" s="125" t="n"/>
-      <c r="K114" s="125" t="n"/>
-      <c r="L114" s="125" t="n"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="129" t="n"/>
-      <c r="B115" s="129" t="n"/>
-      <c r="C115" s="129" t="n"/>
-      <c r="D115" s="130" t="n"/>
-      <c r="E115" s="129" t="n"/>
-      <c r="F115" s="134" t="n"/>
-      <c r="G115" s="129" t="n"/>
-      <c r="H115" s="129" t="n"/>
-      <c r="I115" s="129" t="n"/>
-      <c r="J115" s="129" t="n"/>
-      <c r="K115" s="129" t="n"/>
-      <c r="L115" s="129" t="n"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="125" t="n"/>
-      <c r="B116" s="125" t="n"/>
-      <c r="C116" s="125" t="n"/>
-      <c r="D116" s="126" t="n"/>
-      <c r="E116" s="125" t="n"/>
-      <c r="F116" s="134" t="n"/>
-      <c r="G116" s="125" t="n"/>
-      <c r="H116" s="125" t="n"/>
-      <c r="I116" s="125" t="n"/>
-      <c r="J116" s="125" t="n"/>
-      <c r="K116" s="125" t="n"/>
-      <c r="L116" s="125" t="n"/>
-    </row>
-    <row r="117">
-      <c r="A117" s="129" t="n"/>
-      <c r="B117" s="129" t="n"/>
-      <c r="C117" s="129" t="n"/>
-      <c r="D117" s="130" t="n"/>
-      <c r="E117" s="129" t="n"/>
-      <c r="F117" s="134" t="n"/>
-      <c r="G117" s="129" t="n"/>
-      <c r="H117" s="129" t="n"/>
-      <c r="I117" s="129" t="n"/>
-      <c r="J117" s="129" t="n"/>
-      <c r="K117" s="129" t="n"/>
-      <c r="L117" s="129" t="n"/>
-    </row>
-    <row r="118">
-      <c r="A118" s="125" t="n"/>
-      <c r="B118" s="125" t="n"/>
-      <c r="C118" s="125" t="n"/>
-      <c r="D118" s="126" t="n"/>
-      <c r="E118" s="125" t="n"/>
-      <c r="F118" s="134" t="n"/>
-      <c r="G118" s="125" t="n"/>
-      <c r="H118" s="125" t="n"/>
-      <c r="I118" s="125" t="n"/>
-      <c r="J118" s="125" t="n"/>
-      <c r="K118" s="125" t="n"/>
-      <c r="L118" s="125" t="n"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="129" t="n"/>
-      <c r="B119" s="129" t="n"/>
-      <c r="C119" s="129" t="n"/>
-      <c r="D119" s="130" t="n"/>
-      <c r="E119" s="129" t="n"/>
-      <c r="F119" s="134" t="n"/>
-      <c r="G119" s="129" t="n"/>
-      <c r="H119" s="129" t="n"/>
-      <c r="I119" s="129" t="n"/>
-      <c r="J119" s="129" t="n"/>
-      <c r="K119" s="129" t="n"/>
-      <c r="L119" s="129" t="n"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="125" t="n"/>
-      <c r="B120" s="125" t="n"/>
-      <c r="C120" s="125" t="n"/>
-      <c r="D120" s="126" t="n"/>
-      <c r="E120" s="125" t="n"/>
-      <c r="F120" s="134" t="n"/>
-      <c r="G120" s="125" t="n"/>
-      <c r="H120" s="125" t="n"/>
-      <c r="I120" s="125" t="n"/>
-      <c r="J120" s="125" t="n"/>
-      <c r="K120" s="125" t="n"/>
-      <c r="L120" s="125" t="n"/>
-    </row>
-    <row r="121">
-      <c r="A121" s="129" t="n"/>
-      <c r="B121" s="129" t="n"/>
-      <c r="C121" s="129" t="n"/>
-      <c r="D121" s="130" t="n"/>
-      <c r="E121" s="129" t="n"/>
-      <c r="F121" s="134" t="n"/>
-      <c r="G121" s="129" t="n"/>
-      <c r="H121" s="129" t="n"/>
-      <c r="I121" s="129" t="n"/>
-      <c r="J121" s="129" t="n"/>
-      <c r="K121" s="129" t="n"/>
-      <c r="L121" s="129" t="n"/>
-    </row>
-    <row r="122">
-      <c r="A122" s="125" t="n"/>
-      <c r="B122" s="125" t="n"/>
-      <c r="C122" s="125" t="n"/>
-      <c r="D122" s="126" t="n"/>
-      <c r="E122" s="125" t="n"/>
-      <c r="F122" s="134" t="n"/>
-      <c r="G122" s="125" t="n"/>
-      <c r="H122" s="125" t="n"/>
-      <c r="I122" s="125" t="n"/>
-      <c r="J122" s="125" t="n"/>
-      <c r="K122" s="125" t="n"/>
-      <c r="L122" s="125" t="n"/>
-    </row>
-    <row r="123">
-      <c r="A123" s="129" t="n"/>
-      <c r="B123" s="129" t="n"/>
-      <c r="C123" s="129" t="n"/>
-      <c r="D123" s="130" t="n"/>
-      <c r="E123" s="129" t="n"/>
-      <c r="F123" s="134" t="n"/>
-      <c r="G123" s="129" t="n"/>
-      <c r="H123" s="129" t="n"/>
-      <c r="I123" s="129" t="n"/>
-      <c r="J123" s="129" t="n"/>
-      <c r="K123" s="129" t="n"/>
-      <c r="L123" s="129" t="n"/>
-    </row>
-    <row r="124">
-      <c r="A124" s="125" t="n"/>
-      <c r="B124" s="125" t="n"/>
-      <c r="C124" s="125" t="n"/>
-      <c r="D124" s="126" t="n"/>
-      <c r="E124" s="125" t="n"/>
-      <c r="F124" s="171" t="n"/>
-      <c r="G124" s="125" t="n"/>
-      <c r="H124" s="125" t="n"/>
-      <c r="I124" s="125" t="n"/>
-      <c r="J124" s="125" t="n"/>
-      <c r="K124" s="125" t="n"/>
-      <c r="L124" s="125" t="n"/>
-    </row>
-    <row r="125">
-      <c r="A125" s="129" t="n"/>
-      <c r="B125" s="129" t="n"/>
-      <c r="C125" s="129" t="n"/>
-      <c r="D125" s="130" t="n"/>
-      <c r="E125" s="129" t="n"/>
-      <c r="F125" s="171" t="n"/>
-      <c r="G125" s="129" t="n"/>
-      <c r="H125" s="129" t="n"/>
-      <c r="I125" s="129" t="n"/>
-      <c r="J125" s="129" t="n"/>
-      <c r="K125" s="129" t="n"/>
-      <c r="L125" s="129" t="n"/>
-    </row>
-    <row r="126">
-      <c r="A126" s="125" t="n"/>
-      <c r="B126" s="125" t="n"/>
-      <c r="C126" s="125" t="n"/>
-      <c r="D126" s="126" t="n"/>
-      <c r="E126" s="125" t="n"/>
-      <c r="F126" s="171" t="n"/>
-      <c r="G126" s="125" t="n"/>
-      <c r="H126" s="125" t="n"/>
-      <c r="I126" s="125" t="n"/>
-      <c r="J126" s="125" t="n"/>
-      <c r="K126" s="125" t="n"/>
-      <c r="L126" s="125" t="n"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="129" t="n"/>
-      <c r="B127" s="129" t="n"/>
-      <c r="C127" s="129" t="n"/>
-      <c r="D127" s="130" t="n"/>
-      <c r="E127" s="129" t="n"/>
-      <c r="F127" s="171" t="n"/>
-      <c r="G127" s="129" t="n"/>
-      <c r="H127" s="129" t="n"/>
-      <c r="I127" s="129" t="n"/>
-      <c r="J127" s="129" t="n"/>
-      <c r="K127" s="129" t="n"/>
-      <c r="L127" s="129" t="n"/>
-    </row>
-    <row r="128">
-      <c r="A128" s="125" t="n"/>
-      <c r="B128" s="125" t="n"/>
-      <c r="C128" s="125" t="n"/>
-      <c r="D128" s="126" t="n"/>
-      <c r="E128" s="125" t="n"/>
-      <c r="F128" s="171" t="n"/>
-      <c r="G128" s="125" t="n"/>
-      <c r="H128" s="125" t="n"/>
-      <c r="I128" s="125" t="n"/>
-      <c r="J128" s="125" t="n"/>
-      <c r="K128" s="125" t="n"/>
-      <c r="L128" s="125" t="n"/>
-    </row>
-    <row r="129">
-      <c r="A129" s="129" t="n"/>
-      <c r="B129" s="129" t="n"/>
-      <c r="C129" s="129" t="n"/>
-      <c r="D129" s="130" t="n"/>
-      <c r="E129" s="129" t="n"/>
-      <c r="F129" s="171" t="n"/>
-      <c r="G129" s="129" t="n"/>
-      <c r="H129" s="129" t="n"/>
-      <c r="I129" s="129" t="n"/>
-      <c r="J129" s="129" t="n"/>
-      <c r="K129" s="129" t="n"/>
-      <c r="L129" s="129" t="n"/>
-    </row>
-    <row r="130">
-      <c r="A130" s="125" t="n"/>
-      <c r="B130" s="125" t="n"/>
-      <c r="C130" s="125" t="n"/>
-      <c r="D130" s="126" t="n"/>
-      <c r="E130" s="125" t="n"/>
-      <c r="F130" s="158" t="n"/>
-      <c r="G130" s="125" t="n"/>
-      <c r="H130" s="125" t="n"/>
-      <c r="I130" s="125" t="n"/>
-      <c r="J130" s="125" t="n"/>
-      <c r="K130" s="125" t="n"/>
-      <c r="L130" s="125" t="n"/>
-    </row>
-    <row r="131">
-      <c r="A131" s="129" t="n"/>
-      <c r="B131" s="129" t="n"/>
-      <c r="C131" s="129" t="n"/>
-      <c r="D131" s="130" t="n"/>
-      <c r="E131" s="129" t="n"/>
-      <c r="F131" s="158" t="n"/>
-      <c r="G131" s="129" t="n"/>
-      <c r="H131" s="129" t="n"/>
-      <c r="I131" s="129" t="n"/>
-      <c r="J131" s="129" t="n"/>
-      <c r="K131" s="129" t="n"/>
-      <c r="L131" s="129" t="n"/>
-    </row>
-    <row r="132">
-      <c r="A132" s="125" t="n"/>
-      <c r="B132" s="125" t="n"/>
-      <c r="C132" s="125" t="n"/>
-      <c r="D132" s="126" t="n"/>
-      <c r="E132" s="125" t="n"/>
-      <c r="F132" s="158" t="n"/>
-      <c r="G132" s="125" t="n"/>
-      <c r="H132" s="125" t="n"/>
-      <c r="I132" s="125" t="n"/>
-      <c r="J132" s="125" t="n"/>
-      <c r="K132" s="125" t="n"/>
-      <c r="L132" s="125" t="n"/>
-    </row>
-    <row r="133">
-      <c r="A133" s="129" t="n"/>
-      <c r="B133" s="129" t="n"/>
-      <c r="C133" s="129" t="n"/>
-      <c r="D133" s="130" t="n"/>
-      <c r="E133" s="129" t="n"/>
-      <c r="F133" s="158" t="n"/>
-      <c r="G133" s="129" t="n"/>
-      <c r="H133" s="129" t="n"/>
-      <c r="I133" s="129" t="n"/>
-      <c r="J133" s="129" t="n"/>
-      <c r="K133" s="129" t="n"/>
-      <c r="L133" s="129" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A32:M32"/>
-    <mergeCell ref="A2:M2"/>
-    <mergeCell ref="A1:M1"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink ref="A1" location="'Start Here'!A1" display="🏠 Start Here"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:M133"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" style="230" min="1" max="1"/>
-    <col width="36" customWidth="1" style="230" min="2" max="2"/>
-    <col width="16" customWidth="1" style="230" min="3" max="3"/>
-    <col width="10" customWidth="1" style="230" min="4" max="4"/>
-    <col width="9" customWidth="1" style="230" min="5" max="5"/>
-    <col width="28" customWidth="1" style="230" min="6" max="6"/>
-    <col width="7" customWidth="1" style="230" min="7" max="7"/>
-    <col width="9" customWidth="1" style="230" min="8" max="8"/>
-    <col width="10" customWidth="1" style="230" min="9" max="9"/>
-    <col width="9" customWidth="1" style="230" min="10" max="10"/>
-    <col width="14" customWidth="1" style="230" min="11" max="11"/>
-    <col width="22" customWidth="1" style="230" min="12" max="12"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1" s="230">
-      <c r="A1" s="229" t="inlineStr">
-        <is>
-          <t>🏠 Start Here</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="283" t="inlineStr">
-        <is>
-          <t>Scored by player tier + auto/patch/print run/PSA/price/watchers | Today: May 03, 2026 | 137 total Basketball cards in inventory</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="169" t="inlineStr">
-        <is>
-          <t>PRIORITY ACTIONS</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1" s="230">
-      <c r="A4" s="133" t="inlineStr">
-        <is>
-          <t>Rank</t>
-        </is>
-      </c>
-      <c r="B4" s="133" t="inlineStr">
-        <is>
-          <t>Priority Action</t>
-        </is>
-      </c>
-      <c r="C4" s="133" t="inlineStr">
-        <is>
-          <t>Card Description</t>
-        </is>
-      </c>
-      <c r="D4" s="133" t="inlineStr">
-        <is>
-          <t>SKU</t>
-        </is>
-      </c>
-      <c r="E4" s="133" t="inlineStr">
-        <is>
-          <t>Price ($)</t>
-        </is>
-      </c>
-      <c r="F4" s="133" t="inlineStr">
-        <is>
-          <t>Score</t>
-        </is>
-      </c>
-      <c r="G4" s="133" t="inlineStr">
-        <is>
-          <t>Player Tier</t>
-        </is>
-      </c>
-      <c r="H4" s="133" t="inlineStr">
-        <is>
-          <t>Days Listed</t>
-        </is>
-      </c>
-      <c r="I4" s="133" t="inlineStr">
-        <is>
-          <t>Aging Status</t>
-        </is>
-      </c>
-      <c r="J4" s="133" t="inlineStr">
-        <is>
-          <t>Watchers</t>
-        </is>
-      </c>
-      <c r="K4" s="133" t="inlineStr">
-        <is>
-          <t>Has 90d Sales?</t>
-        </is>
-      </c>
-      <c r="L4" s="133" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="125" t="n"/>
-      <c r="B5" s="125" t="n"/>
-      <c r="C5" s="125" t="n"/>
-      <c r="D5" s="125" t="n"/>
-      <c r="E5" s="126" t="n"/>
-      <c r="F5" s="125" t="n"/>
-      <c r="G5" s="125" t="n"/>
-      <c r="H5" s="125" t="n"/>
-      <c r="I5" s="125" t="n"/>
-      <c r="J5" s="125" t="n"/>
-      <c r="K5" s="125" t="n"/>
-      <c r="L5" s="125" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="125" t="n"/>
-      <c r="B6" s="125" t="n"/>
-      <c r="C6" s="125" t="n"/>
-      <c r="D6" s="125" t="n"/>
-      <c r="E6" s="126" t="n"/>
-      <c r="F6" s="125" t="n"/>
-      <c r="G6" s="125" t="n"/>
-      <c r="H6" s="125" t="n"/>
-      <c r="I6" s="125" t="n"/>
-      <c r="J6" s="125" t="n"/>
-      <c r="K6" s="125" t="n"/>
-      <c r="L6" s="125" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="125" t="n"/>
-      <c r="B7" s="125" t="n"/>
-      <c r="C7" s="125" t="n"/>
-      <c r="D7" s="125" t="n"/>
-      <c r="E7" s="126" t="n"/>
-      <c r="F7" s="125" t="n"/>
-      <c r="G7" s="125" t="n"/>
-      <c r="H7" s="125" t="n"/>
-      <c r="I7" s="125" t="n"/>
-      <c r="J7" s="125" t="n"/>
-      <c r="K7" s="125" t="n"/>
-      <c r="L7" s="125" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="125" t="n"/>
-      <c r="B8" s="125" t="n"/>
-      <c r="C8" s="125" t="n"/>
-      <c r="D8" s="125" t="n"/>
-      <c r="E8" s="126" t="n"/>
-      <c r="F8" s="125" t="n"/>
-      <c r="G8" s="125" t="n"/>
-      <c r="H8" s="125" t="n"/>
-      <c r="I8" s="125" t="n"/>
-      <c r="J8" s="125" t="n"/>
-      <c r="K8" s="125" t="n"/>
-      <c r="L8" s="125" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="125" t="n"/>
-      <c r="B9" s="125" t="n"/>
-      <c r="C9" s="125" t="n"/>
-      <c r="D9" s="125" t="n"/>
-      <c r="E9" s="126" t="n"/>
-      <c r="F9" s="125" t="n"/>
-      <c r="G9" s="125" t="n"/>
-      <c r="H9" s="125" t="n"/>
-      <c r="I9" s="125" t="n"/>
-      <c r="J9" s="125" t="n"/>
-      <c r="K9" s="125" t="n"/>
-      <c r="L9" s="125" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="125" t="n"/>
-      <c r="B10" s="125" t="n"/>
-      <c r="C10" s="125" t="n"/>
-      <c r="D10" s="125" t="n"/>
-      <c r="E10" s="126" t="n"/>
-      <c r="F10" s="125" t="n"/>
-      <c r="G10" s="125" t="n"/>
-      <c r="H10" s="125" t="n"/>
-      <c r="I10" s="125" t="n"/>
-      <c r="J10" s="125" t="n"/>
-      <c r="K10" s="125" t="n"/>
-      <c r="L10" s="125" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="125" t="n"/>
-      <c r="B11" s="125" t="n"/>
-      <c r="C11" s="125" t="n"/>
-      <c r="D11" s="125" t="n"/>
-      <c r="E11" s="126" t="n"/>
-      <c r="F11" s="125" t="n"/>
-      <c r="G11" s="125" t="n"/>
-      <c r="H11" s="125" t="n"/>
-      <c r="I11" s="125" t="n"/>
-      <c r="J11" s="125" t="n"/>
-      <c r="K11" s="125" t="n"/>
-      <c r="L11" s="125" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="125" t="n"/>
-      <c r="B12" s="125" t="n"/>
-      <c r="C12" s="125" t="n"/>
-      <c r="D12" s="125" t="n"/>
-      <c r="E12" s="126" t="n"/>
-      <c r="F12" s="125" t="n"/>
-      <c r="G12" s="125" t="n"/>
-      <c r="H12" s="125" t="n"/>
-      <c r="I12" s="134" t="n"/>
-      <c r="J12" s="125" t="n"/>
-      <c r="K12" s="125" t="n"/>
-      <c r="L12" s="125" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="125" t="n"/>
-      <c r="B13" s="125" t="n"/>
-      <c r="C13" s="125" t="n"/>
-      <c r="D13" s="125" t="n"/>
-      <c r="E13" s="126" t="n"/>
-      <c r="F13" s="125" t="n"/>
-      <c r="G13" s="125" t="n"/>
-      <c r="H13" s="125" t="n"/>
-      <c r="I13" s="134" t="n"/>
-      <c r="J13" s="125" t="n"/>
-      <c r="K13" s="125" t="n"/>
-      <c r="L13" s="125" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="125" t="n"/>
-      <c r="B14" s="125" t="n"/>
-      <c r="C14" s="125" t="n"/>
-      <c r="D14" s="125" t="n"/>
-      <c r="E14" s="126" t="n"/>
-      <c r="F14" s="125" t="n"/>
-      <c r="G14" s="125" t="n"/>
-      <c r="H14" s="125" t="n"/>
-      <c r="I14" s="125" t="n"/>
-      <c r="J14" s="125" t="n"/>
-      <c r="K14" s="125" t="n"/>
-      <c r="L14" s="125" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="125" t="n"/>
-      <c r="B15" s="125" t="n"/>
-      <c r="C15" s="125" t="n"/>
-      <c r="D15" s="125" t="n"/>
-      <c r="E15" s="126" t="n"/>
-      <c r="F15" s="125" t="n"/>
-      <c r="G15" s="125" t="n"/>
-      <c r="H15" s="125" t="n"/>
-      <c r="I15" s="125" t="n"/>
-      <c r="J15" s="125" t="n"/>
-      <c r="K15" s="125" t="n"/>
-      <c r="L15" s="125" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="125" t="n"/>
-      <c r="B16" s="125" t="n"/>
-      <c r="C16" s="125" t="n"/>
-      <c r="D16" s="125" t="n"/>
-      <c r="E16" s="126" t="n"/>
-      <c r="F16" s="125" t="n"/>
-      <c r="G16" s="125" t="n"/>
-      <c r="H16" s="125" t="n"/>
-      <c r="I16" s="125" t="n"/>
-      <c r="J16" s="125" t="n"/>
-      <c r="K16" s="125" t="n"/>
-      <c r="L16" s="125" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="125" t="n"/>
-      <c r="B17" s="125" t="n"/>
-      <c r="C17" s="125" t="n"/>
-      <c r="D17" s="125" t="n"/>
-      <c r="E17" s="126" t="n"/>
-      <c r="F17" s="125" t="n"/>
-      <c r="G17" s="125" t="n"/>
-      <c r="H17" s="125" t="n"/>
-      <c r="I17" s="125" t="n"/>
-      <c r="J17" s="125" t="n"/>
-      <c r="K17" s="125" t="n"/>
-      <c r="L17" s="125" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="125" t="n"/>
-      <c r="B18" s="125" t="n"/>
-      <c r="C18" s="125" t="n"/>
-      <c r="D18" s="125" t="n"/>
-      <c r="E18" s="126" t="n"/>
-      <c r="F18" s="125" t="n"/>
-      <c r="G18" s="125" t="n"/>
-      <c r="H18" s="125" t="n"/>
-      <c r="I18" s="134" t="n"/>
-      <c r="J18" s="125" t="n"/>
-      <c r="K18" s="125" t="n"/>
-      <c r="L18" s="125" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="125" t="n"/>
-      <c r="B19" s="125" t="n"/>
-      <c r="C19" s="125" t="n"/>
-      <c r="D19" s="125" t="n"/>
-      <c r="E19" s="126" t="n"/>
-      <c r="F19" s="125" t="n"/>
-      <c r="G19" s="125" t="n"/>
-      <c r="H19" s="125" t="n"/>
-      <c r="I19" s="134" t="n"/>
-      <c r="J19" s="125" t="n"/>
-      <c r="K19" s="125" t="n"/>
-      <c r="L19" s="125" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="125" t="n"/>
-      <c r="B20" s="125" t="n"/>
-      <c r="C20" s="125" t="n"/>
-      <c r="D20" s="125" t="n"/>
-      <c r="E20" s="126" t="n"/>
-      <c r="F20" s="125" t="n"/>
-      <c r="G20" s="125" t="n"/>
-      <c r="H20" s="125" t="n"/>
-      <c r="I20" s="134" t="n"/>
-      <c r="J20" s="125" t="n"/>
-      <c r="K20" s="125" t="n"/>
-      <c r="L20" s="125" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="125" t="n"/>
-      <c r="B21" s="125" t="n"/>
-      <c r="C21" s="125" t="n"/>
-      <c r="D21" s="125" t="n"/>
-      <c r="E21" s="126" t="n"/>
-      <c r="F21" s="125" t="n"/>
-      <c r="G21" s="125" t="n"/>
-      <c r="H21" s="125" t="n"/>
-      <c r="I21" s="134" t="n"/>
-      <c r="J21" s="125" t="n"/>
-      <c r="K21" s="125" t="n"/>
-      <c r="L21" s="125" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="125" t="n"/>
-      <c r="B22" s="125" t="n"/>
-      <c r="C22" s="125" t="n"/>
-      <c r="D22" s="125" t="n"/>
-      <c r="E22" s="126" t="n"/>
-      <c r="F22" s="125" t="n"/>
-      <c r="G22" s="125" t="n"/>
-      <c r="H22" s="125" t="n"/>
-      <c r="I22" s="134" t="n"/>
-      <c r="J22" s="125" t="n"/>
-      <c r="K22" s="125" t="n"/>
-      <c r="L22" s="125" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="125" t="n"/>
-      <c r="B23" s="125" t="n"/>
-      <c r="C23" s="125" t="n"/>
-      <c r="D23" s="125" t="n"/>
-      <c r="E23" s="126" t="n"/>
-      <c r="F23" s="125" t="n"/>
-      <c r="G23" s="125" t="n"/>
-      <c r="H23" s="125" t="n"/>
-      <c r="I23" s="134" t="n"/>
-      <c r="J23" s="125" t="n"/>
-      <c r="K23" s="125" t="n"/>
-      <c r="L23" s="125" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="125" t="n"/>
-      <c r="B24" s="125" t="n"/>
-      <c r="C24" s="125" t="n"/>
-      <c r="D24" s="125" t="n"/>
-      <c r="E24" s="126" t="n"/>
-      <c r="F24" s="125" t="n"/>
-      <c r="G24" s="125" t="n"/>
-      <c r="H24" s="125" t="n"/>
-      <c r="I24" s="134" t="n"/>
-      <c r="J24" s="125" t="n"/>
-      <c r="K24" s="125" t="n"/>
-      <c r="L24" s="125" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="125" t="n"/>
-      <c r="B25" s="125" t="n"/>
-      <c r="C25" s="125" t="n"/>
-      <c r="D25" s="125" t="n"/>
-      <c r="E25" s="126" t="n"/>
-      <c r="F25" s="125" t="n"/>
-      <c r="G25" s="125" t="n"/>
-      <c r="H25" s="125" t="n"/>
-      <c r="I25" s="134" t="n"/>
-      <c r="J25" s="125" t="n"/>
-      <c r="K25" s="125" t="n"/>
-      <c r="L25" s="125" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="125" t="n"/>
-      <c r="B26" s="125" t="n"/>
-      <c r="C26" s="125" t="n"/>
-      <c r="D26" s="125" t="n"/>
-      <c r="E26" s="126" t="n"/>
-      <c r="F26" s="125" t="n"/>
-      <c r="G26" s="125" t="n"/>
-      <c r="H26" s="125" t="n"/>
-      <c r="I26" s="134" t="n"/>
-      <c r="J26" s="125" t="n"/>
-      <c r="K26" s="125" t="n"/>
-      <c r="L26" s="125" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="125" t="n"/>
-      <c r="B27" s="125" t="n"/>
-      <c r="C27" s="125" t="n"/>
-      <c r="D27" s="125" t="n"/>
-      <c r="E27" s="126" t="n"/>
-      <c r="F27" s="125" t="n"/>
-      <c r="G27" s="125" t="n"/>
-      <c r="H27" s="125" t="n"/>
-      <c r="I27" s="134" t="n"/>
-      <c r="J27" s="125" t="n"/>
-      <c r="K27" s="125" t="n"/>
-      <c r="L27" s="125" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="125" t="n"/>
-      <c r="B28" s="125" t="n"/>
-      <c r="C28" s="125" t="n"/>
-      <c r="D28" s="125" t="n"/>
-      <c r="E28" s="126" t="n"/>
-      <c r="F28" s="125" t="n"/>
-      <c r="G28" s="125" t="n"/>
-      <c r="H28" s="125" t="n"/>
-      <c r="I28" s="125" t="n"/>
-      <c r="J28" s="125" t="n"/>
-      <c r="K28" s="125" t="n"/>
-      <c r="L28" s="125" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="125" t="n"/>
-      <c r="B29" s="125" t="n"/>
-      <c r="C29" s="125" t="n"/>
-      <c r="D29" s="125" t="n"/>
-      <c r="E29" s="126" t="n"/>
-      <c r="F29" s="125" t="n"/>
-      <c r="G29" s="125" t="n"/>
-      <c r="H29" s="125" t="n"/>
-      <c r="I29" s="125" t="n"/>
-      <c r="J29" s="125" t="n"/>
-      <c r="K29" s="125" t="n"/>
-      <c r="L29" s="125" t="n"/>
-    </row>
-    <row r="32" ht="16" customHeight="1" s="230">
-      <c r="A32" s="282" t="n"/>
-    </row>
-    <row r="33" ht="22" customHeight="1" s="230">
-      <c r="A33" s="170" t="n"/>
-      <c r="B33" s="170" t="n"/>
-      <c r="C33" s="170" t="n"/>
-      <c r="D33" s="170" t="n"/>
-      <c r="E33" s="170" t="n"/>
-      <c r="F33" s="170" t="n"/>
-      <c r="G33" s="170" t="n"/>
-      <c r="H33" s="170" t="n"/>
-      <c r="I33" s="170" t="n"/>
-      <c r="J33" s="170" t="n"/>
-      <c r="K33" s="170" t="n"/>
-      <c r="L33" s="170" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="125" t="n"/>
-      <c r="B34" s="125" t="n"/>
-      <c r="C34" s="125" t="n"/>
-      <c r="D34" s="126" t="n"/>
-      <c r="E34" s="125" t="n"/>
-      <c r="F34" s="171" t="n"/>
-      <c r="G34" s="125" t="n"/>
-      <c r="H34" s="125" t="n"/>
-      <c r="I34" s="125" t="n"/>
-      <c r="J34" s="125" t="n"/>
-      <c r="K34" s="125" t="n"/>
-      <c r="L34" s="125" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="129" t="n"/>
-      <c r="B35" s="129" t="n"/>
-      <c r="C35" s="129" t="n"/>
-      <c r="D35" s="130" t="n"/>
-      <c r="E35" s="129" t="n"/>
-      <c r="F35" s="158" t="n"/>
-      <c r="G35" s="129" t="n"/>
-      <c r="H35" s="129" t="n"/>
-      <c r="I35" s="129" t="n"/>
-      <c r="J35" s="129" t="n"/>
-      <c r="K35" s="129" t="n"/>
-      <c r="L35" s="129" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="125" t="n"/>
-      <c r="B36" s="125" t="n"/>
-      <c r="C36" s="125" t="n"/>
-      <c r="D36" s="126" t="n"/>
-      <c r="E36" s="125" t="n"/>
-      <c r="F36" s="158" t="n"/>
-      <c r="G36" s="125" t="n"/>
-      <c r="H36" s="125" t="n"/>
-      <c r="I36" s="125" t="n"/>
-      <c r="J36" s="125" t="n"/>
-      <c r="K36" s="125" t="n"/>
-      <c r="L36" s="125" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="129" t="n"/>
-      <c r="B37" s="129" t="n"/>
-      <c r="C37" s="129" t="n"/>
-      <c r="D37" s="130" t="n"/>
-      <c r="E37" s="129" t="n"/>
-      <c r="F37" s="158" t="n"/>
-      <c r="G37" s="129" t="n"/>
-      <c r="H37" s="129" t="n"/>
-      <c r="I37" s="129" t="n"/>
-      <c r="J37" s="129" t="n"/>
-      <c r="K37" s="129" t="n"/>
-      <c r="L37" s="129" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="125" t="n"/>
-      <c r="B38" s="125" t="n"/>
-      <c r="C38" s="125" t="n"/>
-      <c r="D38" s="126" t="n"/>
-      <c r="E38" s="125" t="n"/>
-      <c r="F38" s="158" t="n"/>
-      <c r="G38" s="125" t="n"/>
-      <c r="H38" s="125" t="n"/>
-      <c r="I38" s="125" t="n"/>
-      <c r="J38" s="125" t="n"/>
-      <c r="K38" s="125" t="n"/>
-      <c r="L38" s="125" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="129" t="n"/>
-      <c r="B39" s="129" t="n"/>
-      <c r="C39" s="129" t="n"/>
-      <c r="D39" s="130" t="n"/>
-      <c r="E39" s="129" t="n"/>
-      <c r="F39" s="158" t="n"/>
-      <c r="G39" s="129" t="n"/>
-      <c r="H39" s="129" t="n"/>
-      <c r="I39" s="129" t="n"/>
-      <c r="J39" s="129" t="n"/>
-      <c r="K39" s="129" t="n"/>
-      <c r="L39" s="129" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="125" t="n"/>
-      <c r="B40" s="125" t="n"/>
-      <c r="C40" s="125" t="n"/>
-      <c r="D40" s="126" t="n"/>
-      <c r="E40" s="125" t="n"/>
-      <c r="F40" s="158" t="n"/>
-      <c r="G40" s="125" t="n"/>
-      <c r="H40" s="125" t="n"/>
-      <c r="I40" s="125" t="n"/>
-      <c r="J40" s="125" t="n"/>
-      <c r="K40" s="125" t="n"/>
-      <c r="L40" s="125" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="129" t="n"/>
-      <c r="B41" s="129" t="n"/>
-      <c r="C41" s="129" t="n"/>
-      <c r="D41" s="130" t="n"/>
-      <c r="E41" s="129" t="n"/>
-      <c r="F41" s="134" t="n"/>
-      <c r="G41" s="129" t="n"/>
-      <c r="H41" s="129" t="n"/>
-      <c r="I41" s="129" t="n"/>
-      <c r="J41" s="129" t="n"/>
-      <c r="K41" s="129" t="n"/>
-      <c r="L41" s="129" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="125" t="n"/>
-      <c r="B42" s="125" t="n"/>
-      <c r="C42" s="125" t="n"/>
-      <c r="D42" s="126" t="n"/>
-      <c r="E42" s="125" t="n"/>
-      <c r="F42" s="134" t="n"/>
-      <c r="G42" s="125" t="n"/>
-      <c r="H42" s="125" t="n"/>
-      <c r="I42" s="125" t="n"/>
-      <c r="J42" s="125" t="n"/>
-      <c r="K42" s="125" t="n"/>
-      <c r="L42" s="125" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="129" t="n"/>
-      <c r="B43" s="129" t="n"/>
-      <c r="C43" s="129" t="n"/>
-      <c r="D43" s="130" t="n"/>
-      <c r="E43" s="129" t="n"/>
-      <c r="F43" s="158" t="n"/>
-      <c r="G43" s="129" t="n"/>
-      <c r="H43" s="129" t="n"/>
-      <c r="I43" s="129" t="n"/>
-      <c r="J43" s="129" t="n"/>
-      <c r="K43" s="129" t="n"/>
-      <c r="L43" s="129" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="125" t="n"/>
-      <c r="B44" s="125" t="n"/>
-      <c r="C44" s="125" t="n"/>
-      <c r="D44" s="126" t="n"/>
-      <c r="E44" s="125" t="n"/>
-      <c r="F44" s="158" t="n"/>
-      <c r="G44" s="125" t="n"/>
-      <c r="H44" s="125" t="n"/>
-      <c r="I44" s="125" t="n"/>
-      <c r="J44" s="125" t="n"/>
-      <c r="K44" s="125" t="n"/>
-      <c r="L44" s="125" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="129" t="n"/>
-      <c r="B45" s="129" t="n"/>
-      <c r="C45" s="129" t="n"/>
-      <c r="D45" s="130" t="n"/>
-      <c r="E45" s="129" t="n"/>
-      <c r="F45" s="171" t="n"/>
-      <c r="G45" s="129" t="n"/>
-      <c r="H45" s="129" t="n"/>
-      <c r="I45" s="129" t="n"/>
-      <c r="J45" s="129" t="n"/>
-      <c r="K45" s="129" t="n"/>
-      <c r="L45" s="129" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="125" t="n"/>
-      <c r="B46" s="125" t="n"/>
-      <c r="C46" s="125" t="n"/>
-      <c r="D46" s="126" t="n"/>
-      <c r="E46" s="125" t="n"/>
-      <c r="F46" s="158" t="n"/>
-      <c r="G46" s="125" t="n"/>
-      <c r="H46" s="125" t="n"/>
-      <c r="I46" s="125" t="n"/>
-      <c r="J46" s="125" t="n"/>
-      <c r="K46" s="125" t="n"/>
-      <c r="L46" s="125" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="129" t="n"/>
-      <c r="B47" s="129" t="n"/>
-      <c r="C47" s="129" t="n"/>
-      <c r="D47" s="130" t="n"/>
-      <c r="E47" s="129" t="n"/>
-      <c r="F47" s="134" t="n"/>
-      <c r="G47" s="129" t="n"/>
-      <c r="H47" s="129" t="n"/>
-      <c r="I47" s="129" t="n"/>
-      <c r="J47" s="129" t="n"/>
-      <c r="K47" s="129" t="n"/>
-      <c r="L47" s="129" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="125" t="n"/>
-      <c r="B48" s="125" t="n"/>
-      <c r="C48" s="125" t="n"/>
-      <c r="D48" s="126" t="n"/>
-      <c r="E48" s="125" t="n"/>
-      <c r="F48" s="134" t="n"/>
-      <c r="G48" s="125" t="n"/>
-      <c r="H48" s="125" t="n"/>
-      <c r="I48" s="125" t="n"/>
-      <c r="J48" s="125" t="n"/>
-      <c r="K48" s="125" t="n"/>
-      <c r="L48" s="125" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="129" t="n"/>
-      <c r="B49" s="129" t="n"/>
-      <c r="C49" s="129" t="n"/>
-      <c r="D49" s="130" t="n"/>
-      <c r="E49" s="129" t="n"/>
-      <c r="F49" s="134" t="n"/>
-      <c r="G49" s="129" t="n"/>
-      <c r="H49" s="129" t="n"/>
-      <c r="I49" s="129" t="n"/>
-      <c r="J49" s="129" t="n"/>
-      <c r="K49" s="129" t="n"/>
-      <c r="L49" s="129" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="125" t="n"/>
-      <c r="B50" s="125" t="n"/>
-      <c r="C50" s="125" t="n"/>
-      <c r="D50" s="126" t="n"/>
-      <c r="E50" s="125" t="n"/>
-      <c r="F50" s="134" t="n"/>
-      <c r="G50" s="125" t="n"/>
-      <c r="H50" s="125" t="n"/>
-      <c r="I50" s="125" t="n"/>
-      <c r="J50" s="125" t="n"/>
-      <c r="K50" s="125" t="n"/>
-      <c r="L50" s="125" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="129" t="n"/>
-      <c r="B51" s="129" t="n"/>
-      <c r="C51" s="129" t="n"/>
-      <c r="D51" s="130" t="n"/>
-      <c r="E51" s="129" t="n"/>
-      <c r="F51" s="134" t="n"/>
-      <c r="G51" s="129" t="n"/>
-      <c r="H51" s="129" t="n"/>
-      <c r="I51" s="129" t="n"/>
-      <c r="J51" s="129" t="n"/>
-      <c r="K51" s="129" t="n"/>
-      <c r="L51" s="129" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="125" t="n"/>
-      <c r="B52" s="125" t="n"/>
-      <c r="C52" s="125" t="n"/>
-      <c r="D52" s="126" t="n"/>
-      <c r="E52" s="125" t="n"/>
-      <c r="F52" s="134" t="n"/>
-      <c r="G52" s="125" t="n"/>
-      <c r="H52" s="125" t="n"/>
-      <c r="I52" s="125" t="n"/>
-      <c r="J52" s="125" t="n"/>
-      <c r="K52" s="125" t="n"/>
-      <c r="L52" s="125" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="129" t="n"/>
-      <c r="B53" s="129" t="n"/>
-      <c r="C53" s="129" t="n"/>
-      <c r="D53" s="130" t="n"/>
-      <c r="E53" s="129" t="n"/>
-      <c r="F53" s="134" t="n"/>
-      <c r="G53" s="129" t="n"/>
-      <c r="H53" s="129" t="n"/>
-      <c r="I53" s="129" t="n"/>
-      <c r="J53" s="129" t="n"/>
-      <c r="K53" s="129" t="n"/>
-      <c r="L53" s="129" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="125" t="n"/>
-      <c r="B54" s="125" t="n"/>
-      <c r="C54" s="125" t="n"/>
-      <c r="D54" s="126" t="n"/>
-      <c r="E54" s="125" t="n"/>
-      <c r="F54" s="134" t="n"/>
-      <c r="G54" s="125" t="n"/>
-      <c r="H54" s="125" t="n"/>
-      <c r="I54" s="125" t="n"/>
-      <c r="J54" s="125" t="n"/>
-      <c r="K54" s="125" t="n"/>
-      <c r="L54" s="125" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="129" t="n"/>
-      <c r="B55" s="129" t="n"/>
-      <c r="C55" s="129" t="n"/>
-      <c r="D55" s="130" t="n"/>
-      <c r="E55" s="129" t="n"/>
-      <c r="F55" s="134" t="n"/>
-      <c r="G55" s="129" t="n"/>
-      <c r="H55" s="129" t="n"/>
-      <c r="I55" s="129" t="n"/>
-      <c r="J55" s="129" t="n"/>
-      <c r="K55" s="129" t="n"/>
-      <c r="L55" s="129" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="125" t="n"/>
-      <c r="B56" s="125" t="n"/>
-      <c r="C56" s="125" t="n"/>
-      <c r="D56" s="126" t="n"/>
-      <c r="E56" s="125" t="n"/>
-      <c r="F56" s="134" t="n"/>
-      <c r="G56" s="125" t="n"/>
-      <c r="H56" s="125" t="n"/>
-      <c r="I56" s="125" t="n"/>
-      <c r="J56" s="125" t="n"/>
-      <c r="K56" s="125" t="n"/>
-      <c r="L56" s="125" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="129" t="n"/>
-      <c r="B57" s="129" t="n"/>
-      <c r="C57" s="129" t="n"/>
-      <c r="D57" s="130" t="n"/>
-      <c r="E57" s="129" t="n"/>
-      <c r="F57" s="171" t="n"/>
-      <c r="G57" s="129" t="n"/>
-      <c r="H57" s="129" t="n"/>
-      <c r="I57" s="129" t="n"/>
-      <c r="J57" s="129" t="n"/>
-      <c r="K57" s="129" t="n"/>
-      <c r="L57" s="129" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="125" t="n"/>
-      <c r="B58" s="125" t="n"/>
-      <c r="C58" s="125" t="n"/>
-      <c r="D58" s="126" t="n"/>
-      <c r="E58" s="125" t="n"/>
-      <c r="F58" s="171" t="n"/>
-      <c r="G58" s="125" t="n"/>
-      <c r="H58" s="125" t="n"/>
-      <c r="I58" s="125" t="n"/>
-      <c r="J58" s="125" t="n"/>
-      <c r="K58" s="125" t="n"/>
-      <c r="L58" s="125" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="129" t="n"/>
-      <c r="B59" s="129" t="n"/>
-      <c r="C59" s="129" t="n"/>
-      <c r="D59" s="130" t="n"/>
-      <c r="E59" s="129" t="n"/>
-      <c r="F59" s="158" t="n"/>
-      <c r="G59" s="129" t="n"/>
-      <c r="H59" s="129" t="n"/>
-      <c r="I59" s="129" t="n"/>
-      <c r="J59" s="129" t="n"/>
-      <c r="K59" s="129" t="n"/>
-      <c r="L59" s="129" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="125" t="n"/>
-      <c r="B60" s="125" t="n"/>
-      <c r="C60" s="125" t="n"/>
-      <c r="D60" s="126" t="n"/>
-      <c r="E60" s="125" t="n"/>
-      <c r="F60" s="158" t="n"/>
-      <c r="G60" s="125" t="n"/>
-      <c r="H60" s="125" t="n"/>
-      <c r="I60" s="125" t="n"/>
-      <c r="J60" s="125" t="n"/>
-      <c r="K60" s="125" t="n"/>
-      <c r="L60" s="125" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="129" t="n"/>
-      <c r="B61" s="129" t="n"/>
-      <c r="C61" s="129" t="n"/>
-      <c r="D61" s="130" t="n"/>
-      <c r="E61" s="129" t="n"/>
-      <c r="F61" s="158" t="n"/>
-      <c r="G61" s="129" t="n"/>
-      <c r="H61" s="129" t="n"/>
-      <c r="I61" s="129" t="n"/>
-      <c r="J61" s="129" t="n"/>
-      <c r="K61" s="129" t="n"/>
-      <c r="L61" s="129" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="125" t="n"/>
-      <c r="B62" s="125" t="n"/>
-      <c r="C62" s="125" t="n"/>
-      <c r="D62" s="126" t="n"/>
-      <c r="E62" s="125" t="n"/>
-      <c r="F62" s="158" t="n"/>
-      <c r="G62" s="125" t="n"/>
-      <c r="H62" s="125" t="n"/>
-      <c r="I62" s="125" t="n"/>
-      <c r="J62" s="125" t="n"/>
-      <c r="K62" s="125" t="n"/>
-      <c r="L62" s="125" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="129" t="n"/>
-      <c r="B63" s="129" t="n"/>
-      <c r="C63" s="129" t="n"/>
-      <c r="D63" s="130" t="n"/>
-      <c r="E63" s="129" t="n"/>
-      <c r="F63" s="158" t="n"/>
-      <c r="G63" s="129" t="n"/>
-      <c r="H63" s="129" t="n"/>
-      <c r="I63" s="129" t="n"/>
-      <c r="J63" s="129" t="n"/>
-      <c r="K63" s="129" t="n"/>
-      <c r="L63" s="129" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="125" t="n"/>
-      <c r="B64" s="125" t="n"/>
-      <c r="C64" s="125" t="n"/>
-      <c r="D64" s="126" t="n"/>
-      <c r="E64" s="125" t="n"/>
-      <c r="F64" s="134" t="n"/>
-      <c r="G64" s="125" t="n"/>
-      <c r="H64" s="125" t="n"/>
-      <c r="I64" s="125" t="n"/>
-      <c r="J64" s="125" t="n"/>
-      <c r="K64" s="125" t="n"/>
-      <c r="L64" s="125" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="129" t="n"/>
-      <c r="B65" s="129" t="n"/>
-      <c r="C65" s="129" t="n"/>
-      <c r="D65" s="130" t="n"/>
-      <c r="E65" s="129" t="n"/>
-      <c r="F65" s="134" t="n"/>
-      <c r="G65" s="129" t="n"/>
-      <c r="H65" s="129" t="n"/>
-      <c r="I65" s="129" t="n"/>
-      <c r="J65" s="129" t="n"/>
-      <c r="K65" s="129" t="n"/>
-      <c r="L65" s="129" t="n"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="125" t="n"/>
-      <c r="B66" s="125" t="n"/>
-      <c r="C66" s="125" t="n"/>
-      <c r="D66" s="126" t="n"/>
-      <c r="E66" s="125" t="n"/>
-      <c r="F66" s="134" t="n"/>
-      <c r="G66" s="125" t="n"/>
-      <c r="H66" s="125" t="n"/>
-      <c r="I66" s="125" t="n"/>
-      <c r="J66" s="125" t="n"/>
-      <c r="K66" s="125" t="n"/>
-      <c r="L66" s="125" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="129" t="n"/>
-      <c r="B67" s="129" t="n"/>
-      <c r="C67" s="129" t="n"/>
-      <c r="D67" s="130" t="n"/>
-      <c r="E67" s="129" t="n"/>
-      <c r="F67" s="134" t="n"/>
-      <c r="G67" s="129" t="n"/>
-      <c r="H67" s="129" t="n"/>
-      <c r="I67" s="129" t="n"/>
-      <c r="J67" s="129" t="n"/>
-      <c r="K67" s="129" t="n"/>
-      <c r="L67" s="129" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="125" t="n"/>
-      <c r="B68" s="125" t="n"/>
-      <c r="C68" s="125" t="n"/>
-      <c r="D68" s="126" t="n"/>
-      <c r="E68" s="125" t="n"/>
-      <c r="F68" s="134" t="n"/>
-      <c r="G68" s="125" t="n"/>
-      <c r="H68" s="125" t="n"/>
-      <c r="I68" s="125" t="n"/>
-      <c r="J68" s="125" t="n"/>
-      <c r="K68" s="125" t="n"/>
-      <c r="L68" s="125" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="129" t="n"/>
-      <c r="B69" s="129" t="n"/>
-      <c r="C69" s="129" t="n"/>
-      <c r="D69" s="130" t="n"/>
-      <c r="E69" s="129" t="n"/>
-      <c r="F69" s="134" t="n"/>
-      <c r="G69" s="129" t="n"/>
-      <c r="H69" s="129" t="n"/>
-      <c r="I69" s="129" t="n"/>
-      <c r="J69" s="129" t="n"/>
-      <c r="K69" s="129" t="n"/>
-      <c r="L69" s="129" t="n"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="125" t="n"/>
-      <c r="B70" s="125" t="n"/>
-      <c r="C70" s="125" t="n"/>
-      <c r="D70" s="126" t="n"/>
-      <c r="E70" s="125" t="n"/>
-      <c r="F70" s="134" t="n"/>
-      <c r="G70" s="125" t="n"/>
-      <c r="H70" s="125" t="n"/>
-      <c r="I70" s="125" t="n"/>
-      <c r="J70" s="125" t="n"/>
-      <c r="K70" s="125" t="n"/>
-      <c r="L70" s="125" t="n"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="129" t="n"/>
-      <c r="B71" s="129" t="n"/>
-      <c r="C71" s="129" t="n"/>
-      <c r="D71" s="130" t="n"/>
-      <c r="E71" s="129" t="n"/>
-      <c r="F71" s="134" t="n"/>
-      <c r="G71" s="129" t="n"/>
-      <c r="H71" s="129" t="n"/>
-      <c r="I71" s="129" t="n"/>
-      <c r="J71" s="129" t="n"/>
-      <c r="K71" s="129" t="n"/>
-      <c r="L71" s="129" t="n"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="125" t="n"/>
-      <c r="B72" s="125" t="n"/>
-      <c r="C72" s="125" t="n"/>
-      <c r="D72" s="126" t="n"/>
-      <c r="E72" s="125" t="n"/>
-      <c r="F72" s="134" t="n"/>
-      <c r="G72" s="125" t="n"/>
-      <c r="H72" s="125" t="n"/>
-      <c r="I72" s="125" t="n"/>
-      <c r="J72" s="125" t="n"/>
-      <c r="K72" s="125" t="n"/>
-      <c r="L72" s="125" t="n"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="129" t="n"/>
-      <c r="B73" s="129" t="n"/>
-      <c r="C73" s="129" t="n"/>
-      <c r="D73" s="130" t="n"/>
-      <c r="E73" s="129" t="n"/>
-      <c r="F73" s="134" t="n"/>
-      <c r="G73" s="129" t="n"/>
-      <c r="H73" s="129" t="n"/>
-      <c r="I73" s="129" t="n"/>
-      <c r="J73" s="129" t="n"/>
-      <c r="K73" s="129" t="n"/>
-      <c r="L73" s="129" t="n"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="125" t="n"/>
-      <c r="B74" s="125" t="n"/>
-      <c r="C74" s="125" t="n"/>
-      <c r="D74" s="126" t="n"/>
-      <c r="E74" s="125" t="n"/>
-      <c r="F74" s="134" t="n"/>
-      <c r="G74" s="125" t="n"/>
-      <c r="H74" s="125" t="n"/>
-      <c r="I74" s="125" t="n"/>
-      <c r="J74" s="125" t="n"/>
-      <c r="K74" s="125" t="n"/>
-      <c r="L74" s="125" t="n"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="129" t="n"/>
-      <c r="B75" s="129" t="n"/>
-      <c r="C75" s="129" t="n"/>
-      <c r="D75" s="130" t="n"/>
-      <c r="E75" s="129" t="n"/>
-      <c r="F75" s="134" t="n"/>
-      <c r="G75" s="129" t="n"/>
-      <c r="H75" s="129" t="n"/>
-      <c r="I75" s="129" t="n"/>
-      <c r="J75" s="129" t="n"/>
-      <c r="K75" s="129" t="n"/>
-      <c r="L75" s="129" t="n"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="125" t="n"/>
-      <c r="B76" s="125" t="n"/>
-      <c r="C76" s="125" t="n"/>
-      <c r="D76" s="126" t="n"/>
-      <c r="E76" s="125" t="n"/>
-      <c r="F76" s="134" t="n"/>
-      <c r="G76" s="125" t="n"/>
-      <c r="H76" s="125" t="n"/>
-      <c r="I76" s="125" t="n"/>
-      <c r="J76" s="125" t="n"/>
-      <c r="K76" s="125" t="n"/>
-      <c r="L76" s="125" t="n"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="129" t="n"/>
-      <c r="B77" s="129" t="n"/>
-      <c r="C77" s="129" t="n"/>
-      <c r="D77" s="130" t="n"/>
-      <c r="E77" s="129" t="n"/>
-      <c r="F77" s="134" t="n"/>
-      <c r="G77" s="129" t="n"/>
-      <c r="H77" s="129" t="n"/>
-      <c r="I77" s="129" t="n"/>
-      <c r="J77" s="129" t="n"/>
-      <c r="K77" s="129" t="n"/>
-      <c r="L77" s="129" t="n"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="125" t="n"/>
-      <c r="B78" s="125" t="n"/>
-      <c r="C78" s="125" t="n"/>
-      <c r="D78" s="126" t="n"/>
-      <c r="E78" s="125" t="n"/>
-      <c r="F78" s="134" t="n"/>
-      <c r="G78" s="125" t="n"/>
-      <c r="H78" s="125" t="n"/>
-      <c r="I78" s="125" t="n"/>
-      <c r="J78" s="125" t="n"/>
-      <c r="K78" s="125" t="n"/>
-      <c r="L78" s="125" t="n"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="129" t="n"/>
-      <c r="B79" s="129" t="n"/>
-      <c r="C79" s="129" t="n"/>
-      <c r="D79" s="130" t="n"/>
-      <c r="E79" s="129" t="n"/>
-      <c r="F79" s="134" t="n"/>
-      <c r="G79" s="129" t="n"/>
-      <c r="H79" s="129" t="n"/>
-      <c r="I79" s="129" t="n"/>
-      <c r="J79" s="129" t="n"/>
-      <c r="K79" s="129" t="n"/>
-      <c r="L79" s="129" t="n"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="125" t="n"/>
-      <c r="B80" s="125" t="n"/>
-      <c r="C80" s="125" t="n"/>
-      <c r="D80" s="126" t="n"/>
-      <c r="E80" s="125" t="n"/>
-      <c r="F80" s="134" t="n"/>
-      <c r="G80" s="125" t="n"/>
-      <c r="H80" s="125" t="n"/>
-      <c r="I80" s="125" t="n"/>
-      <c r="J80" s="125" t="n"/>
-      <c r="K80" s="125" t="n"/>
-      <c r="L80" s="125" t="n"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="129" t="n"/>
-      <c r="B81" s="129" t="n"/>
-      <c r="C81" s="129" t="n"/>
-      <c r="D81" s="130" t="n"/>
-      <c r="E81" s="129" t="n"/>
-      <c r="F81" s="134" t="n"/>
-      <c r="G81" s="129" t="n"/>
-      <c r="H81" s="129" t="n"/>
-      <c r="I81" s="129" t="n"/>
-      <c r="J81" s="129" t="n"/>
-      <c r="K81" s="129" t="n"/>
-      <c r="L81" s="129" t="n"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="125" t="n"/>
-      <c r="B82" s="125" t="n"/>
-      <c r="C82" s="125" t="n"/>
-      <c r="D82" s="126" t="n"/>
-      <c r="E82" s="125" t="n"/>
-      <c r="F82" s="134" t="n"/>
-      <c r="G82" s="125" t="n"/>
-      <c r="H82" s="125" t="n"/>
-      <c r="I82" s="125" t="n"/>
-      <c r="J82" s="125" t="n"/>
-      <c r="K82" s="125" t="n"/>
-      <c r="L82" s="125" t="n"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="129" t="n"/>
-      <c r="B83" s="129" t="n"/>
-      <c r="C83" s="129" t="n"/>
-      <c r="D83" s="130" t="n"/>
-      <c r="E83" s="129" t="n"/>
-      <c r="F83" s="134" t="n"/>
-      <c r="G83" s="129" t="n"/>
-      <c r="H83" s="129" t="n"/>
-      <c r="I83" s="129" t="n"/>
-      <c r="J83" s="129" t="n"/>
-      <c r="K83" s="129" t="n"/>
-      <c r="L83" s="129" t="n"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="125" t="n"/>
-      <c r="B84" s="125" t="n"/>
-      <c r="C84" s="125" t="n"/>
-      <c r="D84" s="126" t="n"/>
-      <c r="E84" s="125" t="n"/>
-      <c r="F84" s="134" t="n"/>
-      <c r="G84" s="125" t="n"/>
-      <c r="H84" s="125" t="n"/>
-      <c r="I84" s="125" t="n"/>
-      <c r="J84" s="125" t="n"/>
-      <c r="K84" s="125" t="n"/>
-      <c r="L84" s="125" t="n"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="129" t="n"/>
-      <c r="B85" s="129" t="n"/>
-      <c r="C85" s="129" t="n"/>
-      <c r="D85" s="130" t="n"/>
-      <c r="E85" s="129" t="n"/>
-      <c r="F85" s="171" t="n"/>
-      <c r="G85" s="129" t="n"/>
-      <c r="H85" s="129" t="n"/>
-      <c r="I85" s="129" t="n"/>
-      <c r="J85" s="129" t="n"/>
-      <c r="K85" s="129" t="n"/>
-      <c r="L85" s="129" t="n"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="125" t="n"/>
-      <c r="B86" s="125" t="n"/>
-      <c r="C86" s="125" t="n"/>
-      <c r="D86" s="126" t="n"/>
-      <c r="E86" s="125" t="n"/>
-      <c r="F86" s="171" t="n"/>
-      <c r="G86" s="125" t="n"/>
-      <c r="H86" s="125" t="n"/>
-      <c r="I86" s="125" t="n"/>
-      <c r="J86" s="125" t="n"/>
-      <c r="K86" s="125" t="n"/>
-      <c r="L86" s="125" t="n"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="129" t="n"/>
-      <c r="B87" s="129" t="n"/>
-      <c r="C87" s="129" t="n"/>
-      <c r="D87" s="130" t="n"/>
-      <c r="E87" s="129" t="n"/>
-      <c r="F87" s="171" t="n"/>
-      <c r="G87" s="129" t="n"/>
-      <c r="H87" s="129" t="n"/>
-      <c r="I87" s="129" t="n"/>
-      <c r="J87" s="129" t="n"/>
-      <c r="K87" s="129" t="n"/>
-      <c r="L87" s="129" t="n"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="125" t="n"/>
-      <c r="B88" s="125" t="n"/>
-      <c r="C88" s="125" t="n"/>
-      <c r="D88" s="126" t="n"/>
-      <c r="E88" s="125" t="n"/>
-      <c r="F88" s="158" t="n"/>
-      <c r="G88" s="125" t="n"/>
-      <c r="H88" s="125" t="n"/>
-      <c r="I88" s="125" t="n"/>
-      <c r="J88" s="125" t="n"/>
-      <c r="K88" s="125" t="n"/>
-      <c r="L88" s="125" t="n"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="129" t="n"/>
-      <c r="B89" s="129" t="n"/>
-      <c r="C89" s="129" t="n"/>
-      <c r="D89" s="130" t="n"/>
-      <c r="E89" s="129" t="n"/>
-      <c r="F89" s="158" t="n"/>
-      <c r="G89" s="129" t="n"/>
-      <c r="H89" s="129" t="n"/>
-      <c r="I89" s="129" t="n"/>
-      <c r="J89" s="129" t="n"/>
-      <c r="K89" s="129" t="n"/>
-      <c r="L89" s="129" t="n"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="125" t="n"/>
-      <c r="B90" s="125" t="n"/>
-      <c r="C90" s="125" t="n"/>
-      <c r="D90" s="126" t="n"/>
-      <c r="E90" s="125" t="n"/>
-      <c r="F90" s="158" t="n"/>
-      <c r="G90" s="125" t="n"/>
-      <c r="H90" s="125" t="n"/>
-      <c r="I90" s="125" t="n"/>
-      <c r="J90" s="125" t="n"/>
-      <c r="K90" s="125" t="n"/>
-      <c r="L90" s="125" t="n"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="129" t="n"/>
-      <c r="B91" s="129" t="n"/>
-      <c r="C91" s="129" t="n"/>
-      <c r="D91" s="130" t="n"/>
-      <c r="E91" s="129" t="n"/>
-      <c r="F91" s="158" t="n"/>
-      <c r="G91" s="129" t="n"/>
-      <c r="H91" s="129" t="n"/>
-      <c r="I91" s="129" t="n"/>
-      <c r="J91" s="129" t="n"/>
-      <c r="K91" s="129" t="n"/>
-      <c r="L91" s="129" t="n"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="125" t="n"/>
-      <c r="B92" s="125" t="n"/>
-      <c r="C92" s="125" t="n"/>
-      <c r="D92" s="126" t="n"/>
-      <c r="E92" s="125" t="n"/>
-      <c r="F92" s="158" t="n"/>
-      <c r="G92" s="125" t="n"/>
-      <c r="H92" s="125" t="n"/>
-      <c r="I92" s="125" t="n"/>
-      <c r="J92" s="125" t="n"/>
-      <c r="K92" s="125" t="n"/>
-      <c r="L92" s="125" t="n"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="129" t="n"/>
-      <c r="B93" s="129" t="n"/>
-      <c r="C93" s="129" t="n"/>
-      <c r="D93" s="130" t="n"/>
-      <c r="E93" s="129" t="n"/>
-      <c r="F93" s="158" t="n"/>
-      <c r="G93" s="129" t="n"/>
-      <c r="H93" s="129" t="n"/>
-      <c r="I93" s="129" t="n"/>
-      <c r="J93" s="129" t="n"/>
-      <c r="K93" s="129" t="n"/>
-      <c r="L93" s="129" t="n"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="125" t="n"/>
-      <c r="B94" s="125" t="n"/>
-      <c r="C94" s="125" t="n"/>
-      <c r="D94" s="126" t="n"/>
-      <c r="E94" s="125" t="n"/>
-      <c r="F94" s="158" t="n"/>
-      <c r="G94" s="125" t="n"/>
-      <c r="H94" s="125" t="n"/>
-      <c r="I94" s="125" t="n"/>
-      <c r="J94" s="125" t="n"/>
-      <c r="K94" s="125" t="n"/>
-      <c r="L94" s="125" t="n"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="129" t="n"/>
-      <c r="B95" s="129" t="n"/>
-      <c r="C95" s="129" t="n"/>
-      <c r="D95" s="130" t="n"/>
-      <c r="E95" s="129" t="n"/>
-      <c r="F95" s="158" t="n"/>
-      <c r="G95" s="129" t="n"/>
-      <c r="H95" s="129" t="n"/>
-      <c r="I95" s="129" t="n"/>
-      <c r="J95" s="129" t="n"/>
-      <c r="K95" s="129" t="n"/>
-      <c r="L95" s="129" t="n"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="125" t="n"/>
-      <c r="B96" s="125" t="n"/>
-      <c r="C96" s="125" t="n"/>
-      <c r="D96" s="126" t="n"/>
-      <c r="E96" s="125" t="n"/>
-      <c r="F96" s="158" t="n"/>
-      <c r="G96" s="125" t="n"/>
-      <c r="H96" s="125" t="n"/>
-      <c r="I96" s="125" t="n"/>
-      <c r="J96" s="125" t="n"/>
-      <c r="K96" s="125" t="n"/>
-      <c r="L96" s="125" t="n"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="129" t="n"/>
-      <c r="B97" s="129" t="n"/>
-      <c r="C97" s="129" t="n"/>
-      <c r="D97" s="130" t="n"/>
-      <c r="E97" s="129" t="n"/>
-      <c r="F97" s="158" t="n"/>
-      <c r="G97" s="129" t="n"/>
-      <c r="H97" s="129" t="n"/>
-      <c r="I97" s="129" t="n"/>
-      <c r="J97" s="129" t="n"/>
-      <c r="K97" s="129" t="n"/>
-      <c r="L97" s="129" t="n"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="125" t="n"/>
-      <c r="B98" s="125" t="n"/>
-      <c r="C98" s="125" t="n"/>
-      <c r="D98" s="126" t="n"/>
-      <c r="E98" s="125" t="n"/>
-      <c r="F98" s="158" t="n"/>
-      <c r="G98" s="125" t="n"/>
-      <c r="H98" s="125" t="n"/>
-      <c r="I98" s="125" t="n"/>
-      <c r="J98" s="125" t="n"/>
-      <c r="K98" s="125" t="n"/>
-      <c r="L98" s="125" t="n"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="129" t="n"/>
-      <c r="B99" s="129" t="n"/>
-      <c r="C99" s="129" t="n"/>
-      <c r="D99" s="130" t="n"/>
-      <c r="E99" s="129" t="n"/>
-      <c r="F99" s="158" t="n"/>
-      <c r="G99" s="129" t="n"/>
-      <c r="H99" s="129" t="n"/>
-      <c r="I99" s="129" t="n"/>
-      <c r="J99" s="129" t="n"/>
-      <c r="K99" s="129" t="n"/>
-      <c r="L99" s="129" t="n"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="125" t="n"/>
-      <c r="B100" s="125" t="n"/>
-      <c r="C100" s="125" t="n"/>
-      <c r="D100" s="126" t="n"/>
-      <c r="E100" s="125" t="n"/>
-      <c r="F100" s="158" t="n"/>
-      <c r="G100" s="125" t="n"/>
-      <c r="H100" s="125" t="n"/>
-      <c r="I100" s="125" t="n"/>
-      <c r="J100" s="125" t="n"/>
-      <c r="K100" s="125" t="n"/>
-      <c r="L100" s="125" t="n"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="129" t="n"/>
-      <c r="B101" s="129" t="n"/>
-      <c r="C101" s="129" t="n"/>
-      <c r="D101" s="130" t="n"/>
-      <c r="E101" s="129" t="n"/>
-      <c r="F101" s="134" t="n"/>
-      <c r="G101" s="129" t="n"/>
-      <c r="H101" s="129" t="n"/>
-      <c r="I101" s="129" t="n"/>
-      <c r="J101" s="129" t="n"/>
-      <c r="K101" s="129" t="n"/>
-      <c r="L101" s="129" t="n"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="125" t="n"/>
-      <c r="B102" s="125" t="n"/>
-      <c r="C102" s="125" t="n"/>
-      <c r="D102" s="126" t="n"/>
-      <c r="E102" s="125" t="n"/>
-      <c r="F102" s="134" t="n"/>
-      <c r="G102" s="125" t="n"/>
-      <c r="H102" s="125" t="n"/>
-      <c r="I102" s="125" t="n"/>
-      <c r="J102" s="125" t="n"/>
-      <c r="K102" s="125" t="n"/>
-      <c r="L102" s="125" t="n"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="129" t="n"/>
-      <c r="B103" s="129" t="n"/>
-      <c r="C103" s="129" t="n"/>
-      <c r="D103" s="130" t="n"/>
-      <c r="E103" s="129" t="n"/>
-      <c r="F103" s="134" t="n"/>
-      <c r="G103" s="129" t="n"/>
-      <c r="H103" s="129" t="n"/>
-      <c r="I103" s="129" t="n"/>
-      <c r="J103" s="129" t="n"/>
-      <c r="K103" s="129" t="n"/>
-      <c r="L103" s="129" t="n"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="125" t="n"/>
-      <c r="B104" s="125" t="n"/>
-      <c r="C104" s="125" t="n"/>
-      <c r="D104" s="126" t="n"/>
-      <c r="E104" s="125" t="n"/>
-      <c r="F104" s="134" t="n"/>
-      <c r="G104" s="125" t="n"/>
-      <c r="H104" s="125" t="n"/>
-      <c r="I104" s="125" t="n"/>
-      <c r="J104" s="125" t="n"/>
-      <c r="K104" s="125" t="n"/>
-      <c r="L104" s="125" t="n"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="129" t="n"/>
-      <c r="B105" s="129" t="n"/>
-      <c r="C105" s="129" t="n"/>
-      <c r="D105" s="130" t="n"/>
-      <c r="E105" s="129" t="n"/>
-      <c r="F105" s="171" t="n"/>
-      <c r="G105" s="129" t="n"/>
-      <c r="H105" s="129" t="n"/>
-      <c r="I105" s="129" t="n"/>
-      <c r="J105" s="129" t="n"/>
-      <c r="K105" s="129" t="n"/>
-      <c r="L105" s="129" t="n"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="125" t="n"/>
-      <c r="B106" s="125" t="n"/>
-      <c r="C106" s="125" t="n"/>
-      <c r="D106" s="126" t="n"/>
-      <c r="E106" s="125" t="n"/>
-      <c r="F106" s="158" t="n"/>
-      <c r="G106" s="125" t="n"/>
-      <c r="H106" s="125" t="n"/>
-      <c r="I106" s="125" t="n"/>
-      <c r="J106" s="125" t="n"/>
-      <c r="K106" s="125" t="n"/>
-      <c r="L106" s="125" t="n"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="129" t="n"/>
-      <c r="B107" s="129" t="n"/>
-      <c r="C107" s="129" t="n"/>
-      <c r="D107" s="130" t="n"/>
-      <c r="E107" s="129" t="n"/>
-      <c r="F107" s="158" t="n"/>
-      <c r="G107" s="129" t="n"/>
-      <c r="H107" s="129" t="n"/>
-      <c r="I107" s="129" t="n"/>
-      <c r="J107" s="129" t="n"/>
-      <c r="K107" s="129" t="n"/>
-      <c r="L107" s="129" t="n"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="125" t="n"/>
-      <c r="B108" s="125" t="n"/>
-      <c r="C108" s="125" t="n"/>
-      <c r="D108" s="126" t="n"/>
-      <c r="E108" s="125" t="n"/>
-      <c r="F108" s="134" t="n"/>
-      <c r="G108" s="125" t="n"/>
-      <c r="H108" s="125" t="n"/>
-      <c r="I108" s="125" t="n"/>
-      <c r="J108" s="125" t="n"/>
-      <c r="K108" s="125" t="n"/>
-      <c r="L108" s="125" t="n"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="129" t="n"/>
-      <c r="B109" s="129" t="n"/>
-      <c r="C109" s="129" t="n"/>
-      <c r="D109" s="130" t="n"/>
-      <c r="E109" s="129" t="n"/>
-      <c r="F109" s="134" t="n"/>
-      <c r="G109" s="129" t="n"/>
-      <c r="H109" s="129" t="n"/>
-      <c r="I109" s="129" t="n"/>
-      <c r="J109" s="129" t="n"/>
-      <c r="K109" s="129" t="n"/>
-      <c r="L109" s="129" t="n"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="125" t="n"/>
-      <c r="B110" s="125" t="n"/>
-      <c r="C110" s="125" t="n"/>
-      <c r="D110" s="126" t="n"/>
-      <c r="E110" s="125" t="n"/>
-      <c r="F110" s="134" t="n"/>
-      <c r="G110" s="125" t="n"/>
-      <c r="H110" s="125" t="n"/>
-      <c r="I110" s="125" t="n"/>
-      <c r="J110" s="125" t="n"/>
-      <c r="K110" s="125" t="n"/>
-      <c r="L110" s="125" t="n"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="129" t="n"/>
-      <c r="B111" s="129" t="n"/>
-      <c r="C111" s="129" t="n"/>
-      <c r="D111" s="130" t="n"/>
-      <c r="E111" s="129" t="n"/>
-      <c r="F111" s="134" t="n"/>
-      <c r="G111" s="129" t="n"/>
-      <c r="H111" s="129" t="n"/>
-      <c r="I111" s="129" t="n"/>
-      <c r="J111" s="129" t="n"/>
-      <c r="K111" s="129" t="n"/>
-      <c r="L111" s="129" t="n"/>
-    </row>
-    <row r="112">
-      <c r="A112" s="125" t="n"/>
-      <c r="B112" s="125" t="n"/>
-      <c r="C112" s="125" t="n"/>
-      <c r="D112" s="126" t="n"/>
-      <c r="E112" s="125" t="n"/>
-      <c r="F112" s="134" t="n"/>
-      <c r="G112" s="125" t="n"/>
-      <c r="H112" s="125" t="n"/>
-      <c r="I112" s="125" t="n"/>
-      <c r="J112" s="125" t="n"/>
-      <c r="K112" s="125" t="n"/>
-      <c r="L112" s="125" t="n"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="129" t="n"/>
-      <c r="B113" s="129" t="n"/>
-      <c r="C113" s="129" t="n"/>
-      <c r="D113" s="130" t="n"/>
-      <c r="E113" s="129" t="n"/>
-      <c r="F113" s="134" t="n"/>
-      <c r="G113" s="129" t="n"/>
-      <c r="H113" s="129" t="n"/>
-      <c r="I113" s="129" t="n"/>
-      <c r="J113" s="129" t="n"/>
-      <c r="K113" s="129" t="n"/>
-      <c r="L113" s="129" t="n"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="125" t="n"/>
-      <c r="B114" s="125" t="n"/>
-      <c r="C114" s="125" t="n"/>
-      <c r="D114" s="126" t="n"/>
-      <c r="E114" s="125" t="n"/>
-      <c r="F114" s="158" t="n"/>
-      <c r="G114" s="125" t="n"/>
-      <c r="H114" s="125" t="n"/>
-      <c r="I114" s="125" t="n"/>
-      <c r="J114" s="125" t="n"/>
-      <c r="K114" s="125" t="n"/>
-      <c r="L114" s="125" t="n"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="129" t="n"/>
-      <c r="B115" s="129" t="n"/>
-      <c r="C115" s="129" t="n"/>
-      <c r="D115" s="130" t="n"/>
-      <c r="E115" s="129" t="n"/>
-      <c r="F115" s="158" t="n"/>
-      <c r="G115" s="129" t="n"/>
-      <c r="H115" s="129" t="n"/>
-      <c r="I115" s="129" t="n"/>
-      <c r="J115" s="129" t="n"/>
-      <c r="K115" s="129" t="n"/>
-      <c r="L115" s="129" t="n"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="125" t="n"/>
-      <c r="B116" s="125" t="n"/>
-      <c r="C116" s="125" t="n"/>
-      <c r="D116" s="126" t="n"/>
-      <c r="E116" s="125" t="n"/>
-      <c r="F116" s="158" t="n"/>
-      <c r="G116" s="125" t="n"/>
-      <c r="H116" s="125" t="n"/>
-      <c r="I116" s="125" t="n"/>
-      <c r="J116" s="125" t="n"/>
-      <c r="K116" s="125" t="n"/>
-      <c r="L116" s="125" t="n"/>
-    </row>
-    <row r="117">
-      <c r="A117" s="129" t="n"/>
-      <c r="B117" s="129" t="n"/>
-      <c r="C117" s="129" t="n"/>
-      <c r="D117" s="130" t="n"/>
-      <c r="E117" s="129" t="n"/>
-      <c r="F117" s="134" t="n"/>
-      <c r="G117" s="129" t="n"/>
-      <c r="H117" s="129" t="n"/>
-      <c r="I117" s="129" t="n"/>
-      <c r="J117" s="129" t="n"/>
-      <c r="K117" s="129" t="n"/>
-      <c r="L117" s="129" t="n"/>
-    </row>
-    <row r="118">
-      <c r="A118" s="125" t="n"/>
-      <c r="B118" s="125" t="n"/>
-      <c r="C118" s="125" t="n"/>
-      <c r="D118" s="126" t="n"/>
-      <c r="E118" s="125" t="n"/>
-      <c r="F118" s="134" t="n"/>
-      <c r="G118" s="125" t="n"/>
-      <c r="H118" s="125" t="n"/>
-      <c r="I118" s="125" t="n"/>
-      <c r="J118" s="125" t="n"/>
-      <c r="K118" s="125" t="n"/>
-      <c r="L118" s="125" t="n"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="129" t="n"/>
-      <c r="B119" s="129" t="n"/>
-      <c r="C119" s="129" t="n"/>
-      <c r="D119" s="130" t="n"/>
-      <c r="E119" s="129" t="n"/>
-      <c r="F119" s="134" t="n"/>
-      <c r="G119" s="129" t="n"/>
-      <c r="H119" s="129" t="n"/>
-      <c r="I119" s="129" t="n"/>
-      <c r="J119" s="129" t="n"/>
-      <c r="K119" s="129" t="n"/>
-      <c r="L119" s="129" t="n"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="125" t="n"/>
-      <c r="B120" s="125" t="n"/>
-      <c r="C120" s="125" t="n"/>
-      <c r="D120" s="126" t="n"/>
-      <c r="E120" s="125" t="n"/>
-      <c r="F120" s="134" t="n"/>
-      <c r="G120" s="125" t="n"/>
-      <c r="H120" s="125" t="n"/>
-      <c r="I120" s="125" t="n"/>
-      <c r="J120" s="125" t="n"/>
-      <c r="K120" s="125" t="n"/>
-      <c r="L120" s="125" t="n"/>
-    </row>
-    <row r="121">
-      <c r="A121" s="129" t="n"/>
-      <c r="B121" s="129" t="n"/>
-      <c r="C121" s="129" t="n"/>
-      <c r="D121" s="130" t="n"/>
-      <c r="E121" s="129" t="n"/>
-      <c r="F121" s="171" t="n"/>
-      <c r="G121" s="129" t="n"/>
-      <c r="H121" s="129" t="n"/>
-      <c r="I121" s="129" t="n"/>
-      <c r="J121" s="129" t="n"/>
-      <c r="K121" s="129" t="n"/>
-      <c r="L121" s="129" t="n"/>
-    </row>
-    <row r="122">
-      <c r="A122" s="125" t="n"/>
-      <c r="B122" s="125" t="n"/>
-      <c r="C122" s="125" t="n"/>
-      <c r="D122" s="126" t="n"/>
-      <c r="E122" s="125" t="n"/>
-      <c r="F122" s="171" t="n"/>
-      <c r="G122" s="125" t="n"/>
-      <c r="H122" s="125" t="n"/>
-      <c r="I122" s="125" t="n"/>
-      <c r="J122" s="125" t="n"/>
-      <c r="K122" s="125" t="n"/>
-      <c r="L122" s="125" t="n"/>
-    </row>
-    <row r="123">
-      <c r="A123" s="129" t="n"/>
-      <c r="B123" s="129" t="n"/>
-      <c r="C123" s="129" t="n"/>
-      <c r="D123" s="130" t="n"/>
-      <c r="E123" s="129" t="n"/>
-      <c r="F123" s="158" t="n"/>
-      <c r="G123" s="129" t="n"/>
-      <c r="H123" s="129" t="n"/>
-      <c r="I123" s="129" t="n"/>
-      <c r="J123" s="129" t="n"/>
-      <c r="K123" s="129" t="n"/>
-      <c r="L123" s="129" t="n"/>
-    </row>
-    <row r="124">
-      <c r="A124" s="125" t="n"/>
-      <c r="B124" s="125" t="n"/>
-      <c r="C124" s="125" t="n"/>
-      <c r="D124" s="126" t="n"/>
-      <c r="E124" s="125" t="n"/>
-      <c r="F124" s="134" t="n"/>
-      <c r="G124" s="125" t="n"/>
-      <c r="H124" s="125" t="n"/>
-      <c r="I124" s="125" t="n"/>
-      <c r="J124" s="125" t="n"/>
-      <c r="K124" s="125" t="n"/>
-      <c r="L124" s="125" t="n"/>
-    </row>
-    <row r="125">
-      <c r="A125" s="129" t="n"/>
-      <c r="B125" s="129" t="n"/>
-      <c r="C125" s="129" t="n"/>
-      <c r="D125" s="130" t="n"/>
-      <c r="E125" s="129" t="n"/>
-      <c r="F125" s="134" t="n"/>
-      <c r="G125" s="129" t="n"/>
-      <c r="H125" s="129" t="n"/>
-      <c r="I125" s="129" t="n"/>
-      <c r="J125" s="129" t="n"/>
-      <c r="K125" s="129" t="n"/>
-      <c r="L125" s="129" t="n"/>
-    </row>
-    <row r="126">
-      <c r="A126" s="125" t="n"/>
-      <c r="B126" s="125" t="n"/>
-      <c r="C126" s="125" t="n"/>
-      <c r="D126" s="126" t="n"/>
-      <c r="E126" s="125" t="n"/>
-      <c r="F126" s="134" t="n"/>
-      <c r="G126" s="125" t="n"/>
-      <c r="H126" s="125" t="n"/>
-      <c r="I126" s="125" t="n"/>
-      <c r="J126" s="125" t="n"/>
-      <c r="K126" s="125" t="n"/>
-      <c r="L126" s="125" t="n"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="129" t="n"/>
-      <c r="B127" s="129" t="n"/>
-      <c r="C127" s="129" t="n"/>
-      <c r="D127" s="130" t="n"/>
-      <c r="E127" s="129" t="n"/>
-      <c r="F127" s="171" t="n"/>
-      <c r="G127" s="129" t="n"/>
-      <c r="H127" s="129" t="n"/>
-      <c r="I127" s="129" t="n"/>
-      <c r="J127" s="129" t="n"/>
-      <c r="K127" s="129" t="n"/>
-      <c r="L127" s="129" t="n"/>
-    </row>
-    <row r="128">
-      <c r="A128" s="125" t="n"/>
-      <c r="B128" s="125" t="n"/>
-      <c r="C128" s="125" t="n"/>
-      <c r="D128" s="126" t="n"/>
-      <c r="E128" s="125" t="n"/>
-      <c r="F128" s="171" t="n"/>
-      <c r="G128" s="125" t="n"/>
-      <c r="H128" s="125" t="n"/>
-      <c r="I128" s="125" t="n"/>
-      <c r="J128" s="125" t="n"/>
-      <c r="K128" s="125" t="n"/>
-      <c r="L128" s="125" t="n"/>
-    </row>
-    <row r="129">
-      <c r="A129" s="129" t="n"/>
-      <c r="B129" s="129" t="n"/>
-      <c r="C129" s="129" t="n"/>
-      <c r="D129" s="130" t="n"/>
-      <c r="E129" s="129" t="n"/>
-      <c r="F129" s="171" t="n"/>
-      <c r="G129" s="129" t="n"/>
-      <c r="H129" s="129" t="n"/>
-      <c r="I129" s="129" t="n"/>
-      <c r="J129" s="129" t="n"/>
-      <c r="K129" s="129" t="n"/>
-      <c r="L129" s="129" t="n"/>
-    </row>
-    <row r="130">
-      <c r="A130" s="125" t="n"/>
-      <c r="B130" s="125" t="n"/>
-      <c r="C130" s="125" t="n"/>
-      <c r="D130" s="126" t="n"/>
-      <c r="E130" s="125" t="n"/>
-      <c r="F130" s="158" t="n"/>
-      <c r="G130" s="125" t="n"/>
-      <c r="H130" s="125" t="n"/>
-      <c r="I130" s="125" t="n"/>
-      <c r="J130" s="125" t="n"/>
-      <c r="K130" s="125" t="n"/>
-      <c r="L130" s="125" t="n"/>
-    </row>
-    <row r="131">
-      <c r="A131" s="129" t="n"/>
-      <c r="B131" s="129" t="n"/>
-      <c r="C131" s="129" t="n"/>
-      <c r="D131" s="130" t="n"/>
-      <c r="E131" s="129" t="n"/>
-      <c r="F131" s="158" t="n"/>
-      <c r="G131" s="129" t="n"/>
-      <c r="H131" s="129" t="n"/>
-      <c r="I131" s="129" t="n"/>
-      <c r="J131" s="129" t="n"/>
-      <c r="K131" s="129" t="n"/>
-      <c r="L131" s="129" t="n"/>
-    </row>
-    <row r="132">
-      <c r="A132" s="125" t="n"/>
-      <c r="B132" s="125" t="n"/>
-      <c r="C132" s="125" t="n"/>
-      <c r="D132" s="126" t="n"/>
-      <c r="E132" s="125" t="n"/>
-      <c r="F132" s="158" t="n"/>
-      <c r="G132" s="125" t="n"/>
-      <c r="H132" s="125" t="n"/>
-      <c r="I132" s="125" t="n"/>
-      <c r="J132" s="125" t="n"/>
-      <c r="K132" s="125" t="n"/>
-      <c r="L132" s="125" t="n"/>
-    </row>
-    <row r="133">
-      <c r="A133" s="129" t="n"/>
-      <c r="B133" s="129" t="n"/>
-      <c r="C133" s="129" t="n"/>
-      <c r="D133" s="130" t="n"/>
-      <c r="E133" s="129" t="n"/>
-      <c r="F133" s="134" t="n"/>
-      <c r="G133" s="129" t="n"/>
-      <c r="H133" s="129" t="n"/>
-      <c r="I133" s="129" t="n"/>
-      <c r="J133" s="129" t="n"/>
-      <c r="K133" s="129" t="n"/>
-      <c r="L133" s="129" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A32:M32"/>
-    <mergeCell ref="A2:M2"/>
-    <mergeCell ref="A1:M1"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink ref="A1" location="'Start Here'!A1" display="🏠 Start Here"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
@@ -21565,7 +15870,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -22743,7 +17048,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -23045,7 +17350,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -23298,7 +17603,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -23866,6 +18171,760 @@
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L21"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" style="230" min="1" max="1"/>
+    <col width="10" customWidth="1" style="230" min="2" max="2"/>
+    <col width="11" customWidth="1" style="230" min="3" max="3"/>
+    <col width="32" customWidth="1" style="230" min="4" max="4"/>
+    <col width="18" customWidth="1" style="230" min="5" max="5"/>
+    <col width="14" customWidth="1" style="230" min="6" max="7"/>
+    <col width="22" customWidth="1" style="230" min="8" max="8"/>
+    <col width="16" customWidth="1" style="230" min="9" max="9"/>
+    <col width="38" customWidth="1" style="230" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1" s="230">
+      <c r="A1" s="229" t="inlineStr">
+        <is>
+          <t>🏠 Start Here</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1" s="230">
+      <c r="A2" s="296" t="inlineStr">
+        <is>
+          <t>Research Date: May 3, 2026  |  Goal: Clear aging inventory this week to make room for new arrivals  |  Bold = IMMEDIATE ACTION</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1" s="230">
+      <c r="A3" s="300" t="inlineStr">
+        <is>
+          <t>🔴 DROP NOW</t>
+        </is>
+      </c>
+      <c r="C3" s="314" t="inlineStr">
+        <is>
+          <t>🟠 OVERPRICED</t>
+        </is>
+      </c>
+      <c r="E3" s="316" t="inlineStr">
+        <is>
+          <t>🟡 FAIR / STUCK</t>
+        </is>
+      </c>
+      <c r="G3" s="301" t="inlineStr">
+        <is>
+          <t>🟢 UNDERPRICED</t>
+        </is>
+      </c>
+      <c r="I3" s="302" t="inlineStr">
+        <is>
+          <t>🔵 CONSIGN DC87</t>
+        </is>
+      </c>
+      <c r="K3" s="317" t="inlineStr">
+        <is>
+          <t>⚪ HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1" s="230">
+      <c r="A4" s="172" t="inlineStr">
+        <is>
+          <t>Card Description</t>
+        </is>
+      </c>
+      <c r="B4" s="172" t="inlineStr">
+        <is>
+          <t>Listed $</t>
+        </is>
+      </c>
+      <c r="C4" s="172" t="inlineStr">
+        <is>
+          <t>Days Listed</t>
+        </is>
+      </c>
+      <c r="D4" s="172" t="inlineStr">
+        <is>
+          <t>Comp Range (Sold)</t>
+        </is>
+      </c>
+      <c r="E4" s="172" t="inlineStr">
+        <is>
+          <t>Market Verdict</t>
+        </is>
+      </c>
+      <c r="F4" s="172" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="G4" s="172" t="inlineStr">
+        <is>
+          <t>Fast-Sell Price</t>
+        </is>
+      </c>
+      <c r="H4" s="172" t="inlineStr">
+        <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="I4" s="172" t="inlineStr">
+        <is>
+          <t>Action Priority</t>
+        </is>
+      </c>
+      <c r="J4" s="172" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="52" customHeight="1" s="230">
+      <c r="A5" s="173" t="n"/>
+      <c r="B5" s="313" t="n"/>
+      <c r="C5" s="313" t="n"/>
+      <c r="D5" s="313" t="n"/>
+      <c r="E5" s="175" t="n"/>
+      <c r="F5" s="176" t="n"/>
+      <c r="G5" s="177" t="n"/>
+      <c r="H5" s="313" t="n"/>
+      <c r="I5" s="178" t="n"/>
+      <c r="J5" s="313" t="n"/>
+    </row>
+    <row r="6" ht="52" customHeight="1" s="230">
+      <c r="A6" s="179" t="n"/>
+      <c r="B6" s="309" t="n"/>
+      <c r="C6" s="309" t="n"/>
+      <c r="D6" s="309" t="n"/>
+      <c r="E6" s="181" t="n"/>
+      <c r="F6" s="182" t="n"/>
+      <c r="G6" s="183" t="n"/>
+      <c r="H6" s="309" t="n"/>
+      <c r="I6" s="184" t="n"/>
+      <c r="J6" s="309" t="n"/>
+    </row>
+    <row r="7" ht="52" customHeight="1" s="230">
+      <c r="A7" s="179" t="n"/>
+      <c r="B7" s="309" t="n"/>
+      <c r="C7" s="309" t="n"/>
+      <c r="D7" s="309" t="n"/>
+      <c r="E7" s="181" t="n"/>
+      <c r="F7" s="182" t="n"/>
+      <c r="G7" s="183" t="n"/>
+      <c r="H7" s="309" t="n"/>
+      <c r="I7" s="184" t="n"/>
+      <c r="J7" s="309" t="n"/>
+    </row>
+    <row r="8" ht="52" customHeight="1" s="230">
+      <c r="A8" s="185" t="n"/>
+      <c r="B8" s="315" t="n"/>
+      <c r="C8" s="315" t="n"/>
+      <c r="D8" s="315" t="n"/>
+      <c r="E8" s="187" t="n"/>
+      <c r="F8" s="188" t="n"/>
+      <c r="G8" s="189" t="n"/>
+      <c r="H8" s="315" t="n"/>
+      <c r="I8" s="190" t="n"/>
+      <c r="J8" s="315" t="n"/>
+    </row>
+    <row r="9" ht="52" customHeight="1" s="230">
+      <c r="A9" s="173" t="n"/>
+      <c r="B9" s="313" t="n"/>
+      <c r="C9" s="313" t="n"/>
+      <c r="D9" s="313" t="n"/>
+      <c r="E9" s="191" t="n"/>
+      <c r="F9" s="192" t="n"/>
+      <c r="G9" s="177" t="n"/>
+      <c r="H9" s="313" t="n"/>
+      <c r="I9" s="193" t="n"/>
+      <c r="J9" s="313" t="n"/>
+    </row>
+    <row r="10" ht="52" customHeight="1" s="230">
+      <c r="A10" s="194" t="n"/>
+      <c r="B10" s="297" t="n"/>
+      <c r="C10" s="297" t="n"/>
+      <c r="D10" s="297" t="n"/>
+      <c r="E10" s="196" t="n"/>
+      <c r="F10" s="197" t="n"/>
+      <c r="G10" s="198" t="n"/>
+      <c r="H10" s="297" t="n"/>
+      <c r="I10" s="199" t="n"/>
+      <c r="J10" s="297" t="n"/>
+    </row>
+    <row r="11" ht="52" customHeight="1" s="230">
+      <c r="A11" s="200" t="n"/>
+      <c r="B11" s="304" t="n"/>
+      <c r="C11" s="304" t="n"/>
+      <c r="D11" s="304" t="n"/>
+      <c r="E11" s="202" t="n"/>
+      <c r="F11" s="203" t="n"/>
+      <c r="G11" s="204" t="n"/>
+      <c r="H11" s="304" t="n"/>
+      <c r="I11" s="205" t="n"/>
+      <c r="J11" s="304" t="n"/>
+    </row>
+    <row r="12" ht="52" customHeight="1" s="230">
+      <c r="A12" s="200" t="n"/>
+      <c r="B12" s="304" t="n"/>
+      <c r="C12" s="304" t="n"/>
+      <c r="D12" s="304" t="n"/>
+      <c r="E12" s="202" t="n"/>
+      <c r="F12" s="203" t="n"/>
+      <c r="G12" s="204" t="n"/>
+      <c r="H12" s="304" t="n"/>
+      <c r="I12" s="205" t="n"/>
+      <c r="J12" s="304" t="n"/>
+    </row>
+    <row r="13" ht="52" customHeight="1" s="230">
+      <c r="A13" s="194" t="n"/>
+      <c r="B13" s="297" t="n"/>
+      <c r="C13" s="297" t="n"/>
+      <c r="D13" s="297" t="n"/>
+      <c r="E13" s="196" t="n"/>
+      <c r="F13" s="197" t="n"/>
+      <c r="G13" s="198" t="n"/>
+      <c r="H13" s="297" t="n"/>
+      <c r="I13" s="199" t="n"/>
+      <c r="J13" s="297" t="n"/>
+    </row>
+    <row r="14" ht="52" customHeight="1" s="230">
+      <c r="A14" s="200" t="n"/>
+      <c r="B14" s="304" t="n"/>
+      <c r="C14" s="304" t="n"/>
+      <c r="D14" s="304" t="n"/>
+      <c r="E14" s="202" t="n"/>
+      <c r="F14" s="203" t="n"/>
+      <c r="G14" s="204" t="n"/>
+      <c r="H14" s="304" t="n"/>
+      <c r="I14" s="205" t="n"/>
+      <c r="J14" s="304" t="n"/>
+    </row>
+    <row r="16" ht="20" customHeight="1" s="230">
+      <c r="A16" s="307" t="n"/>
+    </row>
+    <row r="17" ht="28" customHeight="1" s="230">
+      <c r="A17" s="308" t="n"/>
+      <c r="B17" s="295" t="n"/>
+      <c r="C17" s="309" t="n"/>
+      <c r="D17" s="294" t="n"/>
+      <c r="E17" s="294" t="n"/>
+      <c r="F17" s="294" t="n"/>
+      <c r="G17" s="295" t="n"/>
+      <c r="H17" s="293" t="n"/>
+      <c r="I17" s="294" t="n"/>
+      <c r="J17" s="295" t="n"/>
+    </row>
+    <row r="18" ht="28" customHeight="1" s="230">
+      <c r="A18" s="299" t="n"/>
+      <c r="B18" s="295" t="n"/>
+      <c r="C18" s="315" t="n"/>
+      <c r="D18" s="294" t="n"/>
+      <c r="E18" s="294" t="n"/>
+      <c r="F18" s="294" t="n"/>
+      <c r="G18" s="295" t="n"/>
+      <c r="H18" s="305" t="n"/>
+      <c r="I18" s="294" t="n"/>
+      <c r="J18" s="295" t="n"/>
+    </row>
+    <row r="19" ht="28" customHeight="1" s="230">
+      <c r="A19" s="312" t="n"/>
+      <c r="B19" s="295" t="n"/>
+      <c r="C19" s="313" t="n"/>
+      <c r="D19" s="294" t="n"/>
+      <c r="E19" s="294" t="n"/>
+      <c r="F19" s="294" t="n"/>
+      <c r="G19" s="295" t="n"/>
+      <c r="H19" s="298" t="n"/>
+      <c r="I19" s="294" t="n"/>
+      <c r="J19" s="295" t="n"/>
+    </row>
+    <row r="20" ht="28" customHeight="1" s="230">
+      <c r="A20" s="311" t="n"/>
+      <c r="B20" s="295" t="n"/>
+      <c r="C20" s="297" t="n"/>
+      <c r="D20" s="294" t="n"/>
+      <c r="E20" s="294" t="n"/>
+      <c r="F20" s="294" t="n"/>
+      <c r="G20" s="295" t="n"/>
+      <c r="H20" s="310" t="n"/>
+      <c r="I20" s="294" t="n"/>
+      <c r="J20" s="295" t="n"/>
+    </row>
+    <row r="21" ht="28" customHeight="1" s="230">
+      <c r="A21" s="303" t="n"/>
+      <c r="B21" s="295" t="n"/>
+      <c r="C21" s="304" t="n"/>
+      <c r="D21" s="294" t="n"/>
+      <c r="E21" s="294" t="n"/>
+      <c r="F21" s="294" t="n"/>
+      <c r="G21" s="295" t="n"/>
+      <c r="H21" s="306" t="n"/>
+      <c r="I21" s="294" t="n"/>
+      <c r="J21" s="295" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="24">
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="A16:J16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="K3:L3"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="A1" location="'Start Here'!A1" display="🏠 Start Here"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" style="230" min="1" max="1"/>
+    <col width="26" customWidth="1" style="230" min="2" max="2"/>
+    <col width="12" customWidth="1" style="230" min="3" max="3"/>
+    <col width="18" customWidth="1" style="230" min="4" max="4"/>
+    <col width="20" customWidth="1" style="230" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="36" customHeight="1" s="230">
+      <c r="A1" s="360" t="inlineStr">
+        <is>
+          <t>PSA Grading Fee Schedule — 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="6" customHeight="1" s="230"/>
+    <row r="3" ht="22" customHeight="1" s="230">
+      <c r="A3" s="361" t="inlineStr">
+        <is>
+          <t>Tier</t>
+        </is>
+      </c>
+      <c r="B3" s="361" t="inlineStr">
+        <is>
+          <t>Turnaround</t>
+        </is>
+      </c>
+      <c r="C3" s="361" t="inlineStr">
+        <is>
+          <t>Fee ($)</t>
+        </is>
+      </c>
+      <c r="D3" s="361" t="inlineStr">
+        <is>
+          <t>eBay Fee (13.25%)</t>
+        </is>
+      </c>
+      <c r="E3" s="361" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1" s="230">
+      <c r="A4" s="362" t="inlineStr">
+        <is>
+          <t>Value Bulk</t>
+        </is>
+      </c>
+      <c r="B4" s="363" t="inlineStr">
+        <is>
+          <t>~75 days</t>
+        </is>
+      </c>
+      <c r="C4" s="364" t="n">
+        <v>32.99</v>
+      </c>
+      <c r="D4" s="364">
+        <f>C4*0.1325</f>
+        <v/>
+      </c>
+      <c r="E4" s="365" t="inlineStr">
+        <is>
+          <t>Non-membership</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1" s="230">
+      <c r="A5" s="366" t="inlineStr">
+        <is>
+          <t>Value Plus</t>
+        </is>
+      </c>
+      <c r="B5" s="367" t="inlineStr">
+        <is>
+          <t>~45 days</t>
+        </is>
+      </c>
+      <c r="C5" s="368" t="n">
+        <v>49.99</v>
+      </c>
+      <c r="D5" s="368">
+        <f>C5*0.1325</f>
+        <v/>
+      </c>
+      <c r="E5" s="369" t="inlineStr">
+        <is>
+          <t>Non-membership</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1" s="230">
+      <c r="A6" s="362" t="inlineStr">
+        <is>
+          <t>Value Max</t>
+        </is>
+      </c>
+      <c r="B6" s="363" t="inlineStr">
+        <is>
+          <t>~35 days</t>
+        </is>
+      </c>
+      <c r="C6" s="364" t="n">
+        <v>64.98999999999999</v>
+      </c>
+      <c r="D6" s="364">
+        <f>C6*0.1325</f>
+        <v/>
+      </c>
+      <c r="E6" s="365" t="inlineStr">
+        <is>
+          <t>Non-membership</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1" s="230">
+      <c r="A7" s="366" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="B7" s="367" t="inlineStr">
+        <is>
+          <t>~25 days</t>
+        </is>
+      </c>
+      <c r="C7" s="368" t="n">
+        <v>79.98999999999999</v>
+      </c>
+      <c r="D7" s="368">
+        <f>C7*0.1325</f>
+        <v/>
+      </c>
+      <c r="E7" s="369" t="inlineStr">
+        <is>
+          <t>Non-membership</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1" s="230">
+      <c r="A8" s="362" t="inlineStr">
+        <is>
+          <t>Express</t>
+        </is>
+      </c>
+      <c r="B8" s="363" t="inlineStr">
+        <is>
+          <t>~15 days</t>
+        </is>
+      </c>
+      <c r="C8" s="364" t="n">
+        <v>149</v>
+      </c>
+      <c r="D8" s="364">
+        <f>C8*0.1325</f>
+        <v/>
+      </c>
+      <c r="E8" s="365" t="inlineStr">
+        <is>
+          <t>Non-membership</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1" s="230">
+      <c r="A9" s="366" t="inlineStr">
+        <is>
+          <t>Super Express</t>
+        </is>
+      </c>
+      <c r="B9" s="367" t="inlineStr">
+        <is>
+          <t>~7 days</t>
+        </is>
+      </c>
+      <c r="C9" s="368" t="n">
+        <v>299</v>
+      </c>
+      <c r="D9" s="368">
+        <f>C9*0.1325</f>
+        <v/>
+      </c>
+      <c r="E9" s="369" t="inlineStr">
+        <is>
+          <t>Non-membership</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1" s="230">
+      <c r="A10" s="362" t="inlineStr">
+        <is>
+          <t>Walk-Through</t>
+        </is>
+      </c>
+      <c r="B10" s="363" t="inlineStr">
+        <is>
+          <t>~7 days ($10k insured)</t>
+        </is>
+      </c>
+      <c r="C10" s="364" t="n">
+        <v>599</v>
+      </c>
+      <c r="D10" s="364">
+        <f>C10*0.1325</f>
+        <v/>
+      </c>
+      <c r="E10" s="365" t="inlineStr">
+        <is>
+          <t>Non-membership</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="370" t="inlineStr">
+        <is>
+          <t>eBay final value fee: 13.25% of sale price</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" style="230" min="1" max="1"/>
+    <col width="22" customWidth="1" style="230" min="2" max="2"/>
+    <col width="30" customWidth="1" style="230" min="3" max="3"/>
+    <col width="14" customWidth="1" style="230" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="36" customHeight="1" s="230">
+      <c r="A1" s="360" t="inlineStr">
+        <is>
+          <t>Grading ROI Calculator</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1" s="230">
+      <c r="A2" s="371" t="inlineStr">
+        <is>
+          <t>INPUTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1" s="230">
+      <c r="A4" s="372" t="inlineStr">
+        <is>
+          <t>Raw Buy Price ($)</t>
+        </is>
+      </c>
+      <c r="B4" s="373" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1" s="230">
+      <c r="A5" s="372" t="inlineStr">
+        <is>
+          <t>PSA Tier</t>
+        </is>
+      </c>
+      <c r="B5" s="374" t="inlineStr">
+        <is>
+          <t>Value Bulk</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1" s="230">
+      <c r="A6" s="372" t="inlineStr">
+        <is>
+          <t>PSA Fee ($)</t>
+        </is>
+      </c>
+      <c r="B6" s="373" t="n">
+        <v>32.99</v>
+      </c>
+      <c r="C6" s="375" t="inlineStr">
+        <is>
+          <t>Enter fee from "PSA Fee Schedule" tab</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1" s="230">
+      <c r="A7" s="372" t="inlineStr">
+        <is>
+          <t>Gem Rate (%)</t>
+        </is>
+      </c>
+      <c r="B7" s="376" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1" s="230">
+      <c r="A8" s="372" t="inlineStr">
+        <is>
+          <t>PSA 10 Avg Price ($)</t>
+        </is>
+      </c>
+      <c r="B8" s="373" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1" s="230">
+      <c r="A9" s="372" t="inlineStr">
+        <is>
+          <t>ROI Target (×)</t>
+        </is>
+      </c>
+      <c r="B9" s="374" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" ht="8" customHeight="1" s="230"/>
+    <row r="11" ht="20" customHeight="1" s="230">
+      <c r="A11" s="371" t="inlineStr">
+        <is>
+          <t>OUTPUTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1" s="230">
+      <c r="A12" s="372" t="inlineStr">
+        <is>
+          <t>eBay Fee ($)</t>
+        </is>
+      </c>
+      <c r="B12" s="377">
+        <f>B8*0.1325</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1" s="230">
+      <c r="A13" s="372" t="inlineStr">
+        <is>
+          <t>Target PSA 10 Price ($)</t>
+        </is>
+      </c>
+      <c r="B13" s="377">
+        <f>(B4*B9+B6)/(1-0.1325)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1" s="230">
+      <c r="A14" s="372" t="inlineStr">
+        <is>
+          <t>Est. Net Profit ($)</t>
+        </is>
+      </c>
+      <c r="B14" s="377">
+        <f>B8*(1-0.1325)-B6-B4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1" s="230">
+      <c r="A15" s="372" t="inlineStr">
+        <is>
+          <t>Est. ROI (%)</t>
+        </is>
+      </c>
+      <c r="B15" s="378">
+        <f>IF(B4&gt;0,(B14/B4)*100,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1" s="230">
+      <c r="A16" s="372" t="inlineStr">
+        <is>
+          <t>GO / NO-GO</t>
+        </is>
+      </c>
+      <c r="B16" s="379">
+        <f>IF(B7&lt;40,"❌ NO-GO — Gem rate below 40% floor",IF(B8&gt;=B13,"✅ GO — Clears target price","❌ NO-GO — Price below target"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="8" customHeight="1" s="230"/>
+    <row r="18">
+      <c r="A18" s="380" t="inlineStr">
+        <is>
+          <t>4× ROI formula: (Raw Cost × ROI Target + PSA Fee) ÷ (1 − 0.1325)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B16:D16"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="B5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"Value Bulk,Value Plus,Value Max,Regular,Express,Super Express,Walk-Through"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -24144,760 +19203,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
-  <cols>
-    <col width="42" customWidth="1" style="230" min="1" max="1"/>
-    <col width="10" customWidth="1" style="230" min="2" max="2"/>
-    <col width="11" customWidth="1" style="230" min="3" max="3"/>
-    <col width="32" customWidth="1" style="230" min="4" max="4"/>
-    <col width="18" customWidth="1" style="230" min="5" max="5"/>
-    <col width="14" customWidth="1" style="230" min="6" max="7"/>
-    <col width="22" customWidth="1" style="230" min="8" max="8"/>
-    <col width="16" customWidth="1" style="230" min="9" max="9"/>
-    <col width="38" customWidth="1" style="230" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1" s="230">
-      <c r="A1" s="229" t="inlineStr">
-        <is>
-          <t>🏠 Start Here</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="16" customHeight="1" s="230">
-      <c r="A2" s="296" t="inlineStr">
-        <is>
-          <t>Research Date: May 3, 2026  |  Goal: Clear aging inventory this week to make room for new arrivals  |  Bold = IMMEDIATE ACTION</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18" customHeight="1" s="230">
-      <c r="A3" s="300" t="inlineStr">
-        <is>
-          <t>🔴 DROP NOW</t>
-        </is>
-      </c>
-      <c r="C3" s="314" t="inlineStr">
-        <is>
-          <t>🟠 OVERPRICED</t>
-        </is>
-      </c>
-      <c r="E3" s="316" t="inlineStr">
-        <is>
-          <t>🟡 FAIR / STUCK</t>
-        </is>
-      </c>
-      <c r="G3" s="301" t="inlineStr">
-        <is>
-          <t>🟢 UNDERPRICED</t>
-        </is>
-      </c>
-      <c r="I3" s="302" t="inlineStr">
-        <is>
-          <t>🔵 CONSIGN DC87</t>
-        </is>
-      </c>
-      <c r="K3" s="317" t="inlineStr">
-        <is>
-          <t>⚪ HOLD</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="22" customHeight="1" s="230">
-      <c r="A4" s="172" t="inlineStr">
-        <is>
-          <t>Card Description</t>
-        </is>
-      </c>
-      <c r="B4" s="172" t="inlineStr">
-        <is>
-          <t>Listed $</t>
-        </is>
-      </c>
-      <c r="C4" s="172" t="inlineStr">
-        <is>
-          <t>Days Listed</t>
-        </is>
-      </c>
-      <c r="D4" s="172" t="inlineStr">
-        <is>
-          <t>Comp Range (Sold)</t>
-        </is>
-      </c>
-      <c r="E4" s="172" t="inlineStr">
-        <is>
-          <t>Market Verdict</t>
-        </is>
-      </c>
-      <c r="F4" s="172" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="G4" s="172" t="inlineStr">
-        <is>
-          <t>Fast-Sell Price</t>
-        </is>
-      </c>
-      <c r="H4" s="172" t="inlineStr">
-        <is>
-          <t>Channel</t>
-        </is>
-      </c>
-      <c r="I4" s="172" t="inlineStr">
-        <is>
-          <t>Action Priority</t>
-        </is>
-      </c>
-      <c r="J4" s="172" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="52" customHeight="1" s="230">
-      <c r="A5" s="173" t="n"/>
-      <c r="B5" s="313" t="n"/>
-      <c r="C5" s="313" t="n"/>
-      <c r="D5" s="313" t="n"/>
-      <c r="E5" s="175" t="n"/>
-      <c r="F5" s="176" t="n"/>
-      <c r="G5" s="177" t="n"/>
-      <c r="H5" s="313" t="n"/>
-      <c r="I5" s="178" t="n"/>
-      <c r="J5" s="313" t="n"/>
-    </row>
-    <row r="6" ht="52" customHeight="1" s="230">
-      <c r="A6" s="179" t="n"/>
-      <c r="B6" s="309" t="n"/>
-      <c r="C6" s="309" t="n"/>
-      <c r="D6" s="309" t="n"/>
-      <c r="E6" s="181" t="n"/>
-      <c r="F6" s="182" t="n"/>
-      <c r="G6" s="183" t="n"/>
-      <c r="H6" s="309" t="n"/>
-      <c r="I6" s="184" t="n"/>
-      <c r="J6" s="309" t="n"/>
-    </row>
-    <row r="7" ht="52" customHeight="1" s="230">
-      <c r="A7" s="179" t="n"/>
-      <c r="B7" s="309" t="n"/>
-      <c r="C7" s="309" t="n"/>
-      <c r="D7" s="309" t="n"/>
-      <c r="E7" s="181" t="n"/>
-      <c r="F7" s="182" t="n"/>
-      <c r="G7" s="183" t="n"/>
-      <c r="H7" s="309" t="n"/>
-      <c r="I7" s="184" t="n"/>
-      <c r="J7" s="309" t="n"/>
-    </row>
-    <row r="8" ht="52" customHeight="1" s="230">
-      <c r="A8" s="185" t="n"/>
-      <c r="B8" s="315" t="n"/>
-      <c r="C8" s="315" t="n"/>
-      <c r="D8" s="315" t="n"/>
-      <c r="E8" s="187" t="n"/>
-      <c r="F8" s="188" t="n"/>
-      <c r="G8" s="189" t="n"/>
-      <c r="H8" s="315" t="n"/>
-      <c r="I8" s="190" t="n"/>
-      <c r="J8" s="315" t="n"/>
-    </row>
-    <row r="9" ht="52" customHeight="1" s="230">
-      <c r="A9" s="173" t="n"/>
-      <c r="B9" s="313" t="n"/>
-      <c r="C9" s="313" t="n"/>
-      <c r="D9" s="313" t="n"/>
-      <c r="E9" s="191" t="n"/>
-      <c r="F9" s="192" t="n"/>
-      <c r="G9" s="177" t="n"/>
-      <c r="H9" s="313" t="n"/>
-      <c r="I9" s="193" t="n"/>
-      <c r="J9" s="313" t="n"/>
-    </row>
-    <row r="10" ht="52" customHeight="1" s="230">
-      <c r="A10" s="194" t="n"/>
-      <c r="B10" s="297" t="n"/>
-      <c r="C10" s="297" t="n"/>
-      <c r="D10" s="297" t="n"/>
-      <c r="E10" s="196" t="n"/>
-      <c r="F10" s="197" t="n"/>
-      <c r="G10" s="198" t="n"/>
-      <c r="H10" s="297" t="n"/>
-      <c r="I10" s="199" t="n"/>
-      <c r="J10" s="297" t="n"/>
-    </row>
-    <row r="11" ht="52" customHeight="1" s="230">
-      <c r="A11" s="200" t="n"/>
-      <c r="B11" s="304" t="n"/>
-      <c r="C11" s="304" t="n"/>
-      <c r="D11" s="304" t="n"/>
-      <c r="E11" s="202" t="n"/>
-      <c r="F11" s="203" t="n"/>
-      <c r="G11" s="204" t="n"/>
-      <c r="H11" s="304" t="n"/>
-      <c r="I11" s="205" t="n"/>
-      <c r="J11" s="304" t="n"/>
-    </row>
-    <row r="12" ht="52" customHeight="1" s="230">
-      <c r="A12" s="200" t="n"/>
-      <c r="B12" s="304" t="n"/>
-      <c r="C12" s="304" t="n"/>
-      <c r="D12" s="304" t="n"/>
-      <c r="E12" s="202" t="n"/>
-      <c r="F12" s="203" t="n"/>
-      <c r="G12" s="204" t="n"/>
-      <c r="H12" s="304" t="n"/>
-      <c r="I12" s="205" t="n"/>
-      <c r="J12" s="304" t="n"/>
-    </row>
-    <row r="13" ht="52" customHeight="1" s="230">
-      <c r="A13" s="194" t="n"/>
-      <c r="B13" s="297" t="n"/>
-      <c r="C13" s="297" t="n"/>
-      <c r="D13" s="297" t="n"/>
-      <c r="E13" s="196" t="n"/>
-      <c r="F13" s="197" t="n"/>
-      <c r="G13" s="198" t="n"/>
-      <c r="H13" s="297" t="n"/>
-      <c r="I13" s="199" t="n"/>
-      <c r="J13" s="297" t="n"/>
-    </row>
-    <row r="14" ht="52" customHeight="1" s="230">
-      <c r="A14" s="200" t="n"/>
-      <c r="B14" s="304" t="n"/>
-      <c r="C14" s="304" t="n"/>
-      <c r="D14" s="304" t="n"/>
-      <c r="E14" s="202" t="n"/>
-      <c r="F14" s="203" t="n"/>
-      <c r="G14" s="204" t="n"/>
-      <c r="H14" s="304" t="n"/>
-      <c r="I14" s="205" t="n"/>
-      <c r="J14" s="304" t="n"/>
-    </row>
-    <row r="16" ht="20" customHeight="1" s="230">
-      <c r="A16" s="307" t="n"/>
-    </row>
-    <row r="17" ht="28" customHeight="1" s="230">
-      <c r="A17" s="308" t="n"/>
-      <c r="B17" s="295" t="n"/>
-      <c r="C17" s="309" t="n"/>
-      <c r="D17" s="294" t="n"/>
-      <c r="E17" s="294" t="n"/>
-      <c r="F17" s="294" t="n"/>
-      <c r="G17" s="295" t="n"/>
-      <c r="H17" s="293" t="n"/>
-      <c r="I17" s="294" t="n"/>
-      <c r="J17" s="295" t="n"/>
-    </row>
-    <row r="18" ht="28" customHeight="1" s="230">
-      <c r="A18" s="299" t="n"/>
-      <c r="B18" s="295" t="n"/>
-      <c r="C18" s="315" t="n"/>
-      <c r="D18" s="294" t="n"/>
-      <c r="E18" s="294" t="n"/>
-      <c r="F18" s="294" t="n"/>
-      <c r="G18" s="295" t="n"/>
-      <c r="H18" s="305" t="n"/>
-      <c r="I18" s="294" t="n"/>
-      <c r="J18" s="295" t="n"/>
-    </row>
-    <row r="19" ht="28" customHeight="1" s="230">
-      <c r="A19" s="312" t="n"/>
-      <c r="B19" s="295" t="n"/>
-      <c r="C19" s="313" t="n"/>
-      <c r="D19" s="294" t="n"/>
-      <c r="E19" s="294" t="n"/>
-      <c r="F19" s="294" t="n"/>
-      <c r="G19" s="295" t="n"/>
-      <c r="H19" s="298" t="n"/>
-      <c r="I19" s="294" t="n"/>
-      <c r="J19" s="295" t="n"/>
-    </row>
-    <row r="20" ht="28" customHeight="1" s="230">
-      <c r="A20" s="311" t="n"/>
-      <c r="B20" s="295" t="n"/>
-      <c r="C20" s="297" t="n"/>
-      <c r="D20" s="294" t="n"/>
-      <c r="E20" s="294" t="n"/>
-      <c r="F20" s="294" t="n"/>
-      <c r="G20" s="295" t="n"/>
-      <c r="H20" s="310" t="n"/>
-      <c r="I20" s="294" t="n"/>
-      <c r="J20" s="295" t="n"/>
-    </row>
-    <row r="21" ht="28" customHeight="1" s="230">
-      <c r="A21" s="303" t="n"/>
-      <c r="B21" s="295" t="n"/>
-      <c r="C21" s="304" t="n"/>
-      <c r="D21" s="294" t="n"/>
-      <c r="E21" s="294" t="n"/>
-      <c r="F21" s="294" t="n"/>
-      <c r="G21" s="295" t="n"/>
-      <c r="H21" s="306" t="n"/>
-      <c r="I21" s="294" t="n"/>
-      <c r="J21" s="295" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="24">
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="A16:J16"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="K3:L3"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink ref="A1" location="'Start Here'!A1" display="🏠 Start Here"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="18" customWidth="1" style="230" min="1" max="1"/>
-    <col width="26" customWidth="1" style="230" min="2" max="2"/>
-    <col width="12" customWidth="1" style="230" min="3" max="3"/>
-    <col width="18" customWidth="1" style="230" min="4" max="4"/>
-    <col width="20" customWidth="1" style="230" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="36" customHeight="1" s="230">
-      <c r="A1" s="360" t="inlineStr">
-        <is>
-          <t>PSA Grading Fee Schedule — 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="6" customHeight="1" s="230"/>
-    <row r="3" ht="22" customHeight="1" s="230">
-      <c r="A3" s="361" t="inlineStr">
-        <is>
-          <t>Tier</t>
-        </is>
-      </c>
-      <c r="B3" s="361" t="inlineStr">
-        <is>
-          <t>Turnaround</t>
-        </is>
-      </c>
-      <c r="C3" s="361" t="inlineStr">
-        <is>
-          <t>Fee ($)</t>
-        </is>
-      </c>
-      <c r="D3" s="361" t="inlineStr">
-        <is>
-          <t>eBay Fee (13.25%)</t>
-        </is>
-      </c>
-      <c r="E3" s="361" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="20" customHeight="1" s="230">
-      <c r="A4" s="362" t="inlineStr">
-        <is>
-          <t>Value Bulk</t>
-        </is>
-      </c>
-      <c r="B4" s="363" t="inlineStr">
-        <is>
-          <t>~75 days</t>
-        </is>
-      </c>
-      <c r="C4" s="364" t="n">
-        <v>32.99</v>
-      </c>
-      <c r="D4" s="364">
-        <f>C4*0.1325</f>
-        <v/>
-      </c>
-      <c r="E4" s="365" t="inlineStr">
-        <is>
-          <t>Non-membership</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="20" customHeight="1" s="230">
-      <c r="A5" s="366" t="inlineStr">
-        <is>
-          <t>Value Plus</t>
-        </is>
-      </c>
-      <c r="B5" s="367" t="inlineStr">
-        <is>
-          <t>~45 days</t>
-        </is>
-      </c>
-      <c r="C5" s="368" t="n">
-        <v>49.99</v>
-      </c>
-      <c r="D5" s="368">
-        <f>C5*0.1325</f>
-        <v/>
-      </c>
-      <c r="E5" s="369" t="inlineStr">
-        <is>
-          <t>Non-membership</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1" s="230">
-      <c r="A6" s="362" t="inlineStr">
-        <is>
-          <t>Value Max</t>
-        </is>
-      </c>
-      <c r="B6" s="363" t="inlineStr">
-        <is>
-          <t>~35 days</t>
-        </is>
-      </c>
-      <c r="C6" s="364" t="n">
-        <v>64.98999999999999</v>
-      </c>
-      <c r="D6" s="364">
-        <f>C6*0.1325</f>
-        <v/>
-      </c>
-      <c r="E6" s="365" t="inlineStr">
-        <is>
-          <t>Non-membership</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="20" customHeight="1" s="230">
-      <c r="A7" s="366" t="inlineStr">
-        <is>
-          <t>Regular</t>
-        </is>
-      </c>
-      <c r="B7" s="367" t="inlineStr">
-        <is>
-          <t>~25 days</t>
-        </is>
-      </c>
-      <c r="C7" s="368" t="n">
-        <v>79.98999999999999</v>
-      </c>
-      <c r="D7" s="368">
-        <f>C7*0.1325</f>
-        <v/>
-      </c>
-      <c r="E7" s="369" t="inlineStr">
-        <is>
-          <t>Non-membership</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="20" customHeight="1" s="230">
-      <c r="A8" s="362" t="inlineStr">
-        <is>
-          <t>Express</t>
-        </is>
-      </c>
-      <c r="B8" s="363" t="inlineStr">
-        <is>
-          <t>~15 days</t>
-        </is>
-      </c>
-      <c r="C8" s="364" t="n">
-        <v>149</v>
-      </c>
-      <c r="D8" s="364">
-        <f>C8*0.1325</f>
-        <v/>
-      </c>
-      <c r="E8" s="365" t="inlineStr">
-        <is>
-          <t>Non-membership</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="20" customHeight="1" s="230">
-      <c r="A9" s="366" t="inlineStr">
-        <is>
-          <t>Super Express</t>
-        </is>
-      </c>
-      <c r="B9" s="367" t="inlineStr">
-        <is>
-          <t>~7 days</t>
-        </is>
-      </c>
-      <c r="C9" s="368" t="n">
-        <v>299</v>
-      </c>
-      <c r="D9" s="368">
-        <f>C9*0.1325</f>
-        <v/>
-      </c>
-      <c r="E9" s="369" t="inlineStr">
-        <is>
-          <t>Non-membership</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="20" customHeight="1" s="230">
-      <c r="A10" s="362" t="inlineStr">
-        <is>
-          <t>Walk-Through</t>
-        </is>
-      </c>
-      <c r="B10" s="363" t="inlineStr">
-        <is>
-          <t>~7 days ($10k insured)</t>
-        </is>
-      </c>
-      <c r="C10" s="364" t="n">
-        <v>599</v>
-      </c>
-      <c r="D10" s="364">
-        <f>C10*0.1325</f>
-        <v/>
-      </c>
-      <c r="E10" s="365" t="inlineStr">
-        <is>
-          <t>Non-membership</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="370" t="inlineStr">
-        <is>
-          <t>eBay final value fee: 13.25% of sale price</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A11:E11"/>
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="28" customWidth="1" style="230" min="1" max="1"/>
-    <col width="22" customWidth="1" style="230" min="2" max="2"/>
-    <col width="30" customWidth="1" style="230" min="3" max="3"/>
-    <col width="14" customWidth="1" style="230" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="36" customHeight="1" s="230">
-      <c r="A1" s="360" t="inlineStr">
-        <is>
-          <t>Grading ROI Calculator</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1" s="230">
-      <c r="A2" s="371" t="inlineStr">
-        <is>
-          <t>INPUTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="20" customHeight="1" s="230">
-      <c r="A4" s="372" t="inlineStr">
-        <is>
-          <t>Raw Buy Price ($)</t>
-        </is>
-      </c>
-      <c r="B4" s="373" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="5" ht="20" customHeight="1" s="230">
-      <c r="A5" s="372" t="inlineStr">
-        <is>
-          <t>PSA Tier</t>
-        </is>
-      </c>
-      <c r="B5" s="374" t="inlineStr">
-        <is>
-          <t>Value Bulk</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1" s="230">
-      <c r="A6" s="372" t="inlineStr">
-        <is>
-          <t>PSA Fee ($)</t>
-        </is>
-      </c>
-      <c r="B6" s="373" t="n">
-        <v>32.99</v>
-      </c>
-      <c r="C6" s="375" t="inlineStr">
-        <is>
-          <t>Enter fee from "PSA Fee Schedule" tab</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="20" customHeight="1" s="230">
-      <c r="A7" s="372" t="inlineStr">
-        <is>
-          <t>Gem Rate (%)</t>
-        </is>
-      </c>
-      <c r="B7" s="376" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="8" ht="20" customHeight="1" s="230">
-      <c r="A8" s="372" t="inlineStr">
-        <is>
-          <t>PSA 10 Avg Price ($)</t>
-        </is>
-      </c>
-      <c r="B8" s="373" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" ht="20" customHeight="1" s="230">
-      <c r="A9" s="372" t="inlineStr">
-        <is>
-          <t>ROI Target (×)</t>
-        </is>
-      </c>
-      <c r="B9" s="374" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" ht="8" customHeight="1" s="230"/>
-    <row r="11" ht="20" customHeight="1" s="230">
-      <c r="A11" s="371" t="inlineStr">
-        <is>
-          <t>OUTPUTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="22" customHeight="1" s="230">
-      <c r="A12" s="372" t="inlineStr">
-        <is>
-          <t>eBay Fee ($)</t>
-        </is>
-      </c>
-      <c r="B12" s="377">
-        <f>B8*0.1325</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1" s="230">
-      <c r="A13" s="372" t="inlineStr">
-        <is>
-          <t>Target PSA 10 Price ($)</t>
-        </is>
-      </c>
-      <c r="B13" s="377">
-        <f>(B4*B9+B6)/(1-0.1325)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="22" customHeight="1" s="230">
-      <c r="A14" s="372" t="inlineStr">
-        <is>
-          <t>Est. Net Profit ($)</t>
-        </is>
-      </c>
-      <c r="B14" s="377">
-        <f>B8*(1-0.1325)-B6-B4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="22" customHeight="1" s="230">
-      <c r="A15" s="372" t="inlineStr">
-        <is>
-          <t>Est. ROI (%)</t>
-        </is>
-      </c>
-      <c r="B15" s="378">
-        <f>IF(B4&gt;0,(B14/B4)*100,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="28" customHeight="1" s="230">
-      <c r="A16" s="372" t="inlineStr">
-        <is>
-          <t>GO / NO-GO</t>
-        </is>
-      </c>
-      <c r="B16" s="379">
-        <f>IF(B7&lt;40,"❌ NO-GO — Gem rate below 40% floor",IF(B8&gt;=B13,"✅ GO — Clears target price","❌ NO-GO — Price below target"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="8" customHeight="1" s="230"/>
-    <row r="18">
-      <c r="A18" s="380" t="inlineStr">
-        <is>
-          <t>4× ROI formula: (Raw Cost × ROI Target + PSA Fee) ÷ (1 − 0.1325)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B16:D16"/>
-  </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="B5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"Value Bulk,Value Plus,Value Max,Regular,Express,Super Express,Walk-Through"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:U58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -25295,7 +19600,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
